--- a/activitereelgueudet-2026.xlsx
+++ b/activitereelgueudet-2026.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15122314-25CD-4127-8DA3-0B1D881235E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37C09EA-5C8C-4DA6-8CC2-3FE5E474DD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gueudet" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Gueudet!$A$1:$S$317</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4252" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5391" uniqueCount="632">
   <si>
     <t>codePlaque</t>
   </si>
@@ -1629,6 +1632,306 @@
   </si>
   <si>
     <t>Mars</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>TEAM CAPIN SEBASTIEN</t>
+  </si>
+  <si>
+    <t>3.23</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>12.76</t>
+  </si>
+  <si>
+    <t>27.79</t>
+  </si>
+  <si>
+    <t>31.08</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1348 33                 </t>
+  </si>
+  <si>
+    <t>A1348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINECUT P4000 150 MM          </t>
+  </si>
+  <si>
+    <t>14/04/2026</t>
+  </si>
+  <si>
+    <t>11.23</t>
+  </si>
+  <si>
+    <t>15.02</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>12.83</t>
+  </si>
+  <si>
+    <t>16.94</t>
+  </si>
+  <si>
+    <t>26.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1465 33                 </t>
+  </si>
+  <si>
+    <t>A1465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUL. DE FINITION NYLON GRIS  </t>
+  </si>
+  <si>
+    <t>25.65</t>
+  </si>
+  <si>
+    <t>16/04/2026</t>
+  </si>
+  <si>
+    <t>38.66</t>
+  </si>
+  <si>
+    <t>21.97</t>
+  </si>
+  <si>
+    <t>20.05</t>
+  </si>
+  <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86665 22                 </t>
+  </si>
+  <si>
+    <t>86665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE FACE EXTRA FORT 19MM   </t>
+  </si>
+  <si>
+    <t>13.52</t>
+  </si>
+  <si>
+    <t>19.31</t>
+  </si>
+  <si>
+    <t>14.19</t>
+  </si>
+  <si>
+    <t>14.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84702 22                 </t>
+  </si>
+  <si>
+    <t>84702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESINE DE FINITION 2 ML       </t>
+  </si>
+  <si>
+    <t>25.37</t>
+  </si>
+  <si>
+    <t>16.17</t>
+  </si>
+  <si>
+    <t>17/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86144 00                 </t>
+  </si>
+  <si>
+    <t>86144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANDE ADHESIVE ETANCHE        </t>
+  </si>
+  <si>
+    <t>22.05</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>24.54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86850 10                 </t>
+  </si>
+  <si>
+    <t>86850</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAPID BOND BLACK 5 MIN        </t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>28/04/2026</t>
+  </si>
+  <si>
+    <t>13/04/2026</t>
+  </si>
+  <si>
+    <t>28.38</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>12.97</t>
+  </si>
+  <si>
+    <t>940098</t>
+  </si>
+  <si>
+    <t>GARAGE PASQUIER</t>
+  </si>
+  <si>
+    <t>BEAUMONT LE ROGER</t>
+  </si>
+  <si>
+    <t>27170</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V2185 11                 </t>
+  </si>
+  <si>
+    <t>V2185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUBAN DE MASQUAGE 80 Deg C    </t>
+  </si>
+  <si>
+    <t>44.96</t>
+  </si>
+  <si>
+    <t>940130</t>
+  </si>
+  <si>
+    <t>COIGNARD SA</t>
+  </si>
+  <si>
+    <t>EPAIGNES</t>
+  </si>
+  <si>
+    <t>27260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1189 33                 </t>
+  </si>
+  <si>
+    <t>A1189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MD3 DISQUES EPONGES MICROFINS </t>
+  </si>
+  <si>
+    <t>20.77</t>
+  </si>
+  <si>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>15.16</t>
+  </si>
+  <si>
+    <t>24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86245 10                 </t>
+  </si>
+  <si>
+    <t>86245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEINTURE ACRYLIQUE NOIR MAT   </t>
+  </si>
+  <si>
+    <t>8.77</t>
+  </si>
+  <si>
+    <t>24.57</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>27.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1352 33                 </t>
+  </si>
+  <si>
+    <t>A1352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERFACE FINECUT MEDIUM 10MM </t>
+  </si>
+  <si>
+    <t>7.94</t>
+  </si>
+  <si>
+    <t>28.03</t>
+  </si>
+  <si>
+    <t>21.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1331 22                 </t>
+  </si>
+  <si>
+    <t>A1331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISQUES DURALITE 150MM P1000  </t>
+  </si>
+  <si>
+    <t>9.98</t>
+  </si>
+  <si>
+    <t>34.41</t>
+  </si>
+  <si>
+    <t>Avril</t>
   </si>
 </sst>
 </file>
@@ -2000,7 +2303,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}">
-  <dimension ref="A1:S250"/>
+  <dimension ref="A1:S317"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -16753,18 +17056,3768 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>206</v>
+      </c>
+      <c r="B251" t="s">
+        <v>207</v>
+      </c>
+      <c r="C251" t="s">
+        <v>215</v>
+      </c>
+      <c r="D251" t="s">
+        <v>216</v>
+      </c>
+      <c r="E251" t="s">
+        <v>32</v>
+      </c>
+      <c r="F251" t="s">
+        <v>33</v>
+      </c>
+      <c r="G251" t="s">
+        <v>532</v>
+      </c>
+      <c r="H251" t="s">
+        <v>292</v>
+      </c>
+      <c r="I251" t="s">
+        <v>293</v>
+      </c>
+      <c r="J251">
+        <v>3.23</v>
+      </c>
+      <c r="K251" t="s">
+        <v>23</v>
+      </c>
+      <c r="L251" t="s">
+        <v>533</v>
+      </c>
+      <c r="M251" t="s">
+        <v>18</v>
+      </c>
+      <c r="N251" t="s">
+        <v>534</v>
+      </c>
+      <c r="O251" t="s">
+        <v>20</v>
+      </c>
+      <c r="P251" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>535</v>
+      </c>
+      <c r="R251" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>206</v>
+      </c>
+      <c r="B252" t="s">
+        <v>207</v>
+      </c>
+      <c r="C252" t="s">
+        <v>215</v>
+      </c>
+      <c r="D252" t="s">
+        <v>216</v>
+      </c>
+      <c r="E252" t="s">
+        <v>32</v>
+      </c>
+      <c r="F252" t="s">
+        <v>33</v>
+      </c>
+      <c r="G252" t="s">
+        <v>536</v>
+      </c>
+      <c r="H252" t="s">
+        <v>171</v>
+      </c>
+      <c r="I252" t="s">
+        <v>172</v>
+      </c>
+      <c r="J252">
+        <v>12.76</v>
+      </c>
+      <c r="K252" t="s">
+        <v>23</v>
+      </c>
+      <c r="L252" t="s">
+        <v>533</v>
+      </c>
+      <c r="M252" t="s">
+        <v>18</v>
+      </c>
+      <c r="N252" t="s">
+        <v>534</v>
+      </c>
+      <c r="O252" t="s">
+        <v>20</v>
+      </c>
+      <c r="P252" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>537</v>
+      </c>
+      <c r="R252" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>206</v>
+      </c>
+      <c r="B253" t="s">
+        <v>207</v>
+      </c>
+      <c r="C253" t="s">
+        <v>215</v>
+      </c>
+      <c r="D253" t="s">
+        <v>216</v>
+      </c>
+      <c r="E253" t="s">
+        <v>32</v>
+      </c>
+      <c r="F253" t="s">
+        <v>33</v>
+      </c>
+      <c r="G253" t="s">
+        <v>536</v>
+      </c>
+      <c r="H253" t="s">
+        <v>126</v>
+      </c>
+      <c r="I253" t="s">
+        <v>127</v>
+      </c>
+      <c r="J253">
+        <v>27.79</v>
+      </c>
+      <c r="K253" t="s">
+        <v>23</v>
+      </c>
+      <c r="L253" t="s">
+        <v>533</v>
+      </c>
+      <c r="M253" t="s">
+        <v>18</v>
+      </c>
+      <c r="N253" t="s">
+        <v>534</v>
+      </c>
+      <c r="O253" t="s">
+        <v>20</v>
+      </c>
+      <c r="P253" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>538</v>
+      </c>
+      <c r="R253" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>206</v>
+      </c>
+      <c r="B254" t="s">
+        <v>207</v>
+      </c>
+      <c r="C254" t="s">
+        <v>215</v>
+      </c>
+      <c r="D254" t="s">
+        <v>216</v>
+      </c>
+      <c r="E254" t="s">
+        <v>32</v>
+      </c>
+      <c r="F254" t="s">
+        <v>33</v>
+      </c>
+      <c r="G254" t="s">
+        <v>536</v>
+      </c>
+      <c r="H254" t="s">
+        <v>186</v>
+      </c>
+      <c r="I254" t="s">
+        <v>187</v>
+      </c>
+      <c r="J254">
+        <v>31.08</v>
+      </c>
+      <c r="K254" t="s">
+        <v>23</v>
+      </c>
+      <c r="L254" t="s">
+        <v>533</v>
+      </c>
+      <c r="M254" t="s">
+        <v>18</v>
+      </c>
+      <c r="N254" t="s">
+        <v>534</v>
+      </c>
+      <c r="O254" t="s">
+        <v>20</v>
+      </c>
+      <c r="P254" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>539</v>
+      </c>
+      <c r="R254" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>206</v>
+      </c>
+      <c r="B255" t="s">
+        <v>207</v>
+      </c>
+      <c r="C255" t="s">
+        <v>215</v>
+      </c>
+      <c r="D255" t="s">
+        <v>216</v>
+      </c>
+      <c r="E255" t="s">
+        <v>32</v>
+      </c>
+      <c r="F255" t="s">
+        <v>33</v>
+      </c>
+      <c r="G255" t="s">
+        <v>536</v>
+      </c>
+      <c r="H255" t="s">
+        <v>507</v>
+      </c>
+      <c r="I255" t="s">
+        <v>508</v>
+      </c>
+      <c r="J255">
+        <v>30.8</v>
+      </c>
+      <c r="K255" t="s">
+        <v>23</v>
+      </c>
+      <c r="L255" t="s">
+        <v>533</v>
+      </c>
+      <c r="M255" t="s">
+        <v>18</v>
+      </c>
+      <c r="N255" t="s">
+        <v>534</v>
+      </c>
+      <c r="O255" t="s">
+        <v>20</v>
+      </c>
+      <c r="P255" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>540</v>
+      </c>
+      <c r="R255" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>206</v>
+      </c>
+      <c r="B256" t="s">
+        <v>207</v>
+      </c>
+      <c r="C256" t="s">
+        <v>215</v>
+      </c>
+      <c r="D256" t="s">
+        <v>216</v>
+      </c>
+      <c r="E256" t="s">
+        <v>32</v>
+      </c>
+      <c r="F256" t="s">
+        <v>33</v>
+      </c>
+      <c r="G256" t="s">
+        <v>536</v>
+      </c>
+      <c r="H256" t="s">
+        <v>541</v>
+      </c>
+      <c r="I256" t="s">
+        <v>542</v>
+      </c>
+      <c r="J256">
+        <v>30.4</v>
+      </c>
+      <c r="K256" t="s">
+        <v>23</v>
+      </c>
+      <c r="L256" t="s">
+        <v>533</v>
+      </c>
+      <c r="M256" t="s">
+        <v>18</v>
+      </c>
+      <c r="N256" t="s">
+        <v>534</v>
+      </c>
+      <c r="O256" t="s">
+        <v>20</v>
+      </c>
+      <c r="P256" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>282</v>
+      </c>
+      <c r="R256" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>206</v>
+      </c>
+      <c r="B257" t="s">
+        <v>207</v>
+      </c>
+      <c r="C257" t="s">
+        <v>215</v>
+      </c>
+      <c r="D257" t="s">
+        <v>216</v>
+      </c>
+      <c r="E257" t="s">
+        <v>32</v>
+      </c>
+      <c r="F257" t="s">
+        <v>33</v>
+      </c>
+      <c r="G257" t="s">
+        <v>544</v>
+      </c>
+      <c r="H257" t="s">
+        <v>34</v>
+      </c>
+      <c r="I257" t="s">
+        <v>35</v>
+      </c>
+      <c r="J257">
+        <v>33.69</v>
+      </c>
+      <c r="K257" t="s">
+        <v>50</v>
+      </c>
+      <c r="L257" t="s">
+        <v>533</v>
+      </c>
+      <c r="M257" t="s">
+        <v>18</v>
+      </c>
+      <c r="N257" t="s">
+        <v>534</v>
+      </c>
+      <c r="O257" t="s">
+        <v>20</v>
+      </c>
+      <c r="P257" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>545</v>
+      </c>
+      <c r="R257" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>206</v>
+      </c>
+      <c r="B258" t="s">
+        <v>207</v>
+      </c>
+      <c r="C258" t="s">
+        <v>215</v>
+      </c>
+      <c r="D258" t="s">
+        <v>216</v>
+      </c>
+      <c r="E258" t="s">
+        <v>32</v>
+      </c>
+      <c r="F258" t="s">
+        <v>33</v>
+      </c>
+      <c r="G258" t="s">
+        <v>536</v>
+      </c>
+      <c r="H258" t="s">
+        <v>76</v>
+      </c>
+      <c r="I258" t="s">
+        <v>77</v>
+      </c>
+      <c r="J258">
+        <v>30.04</v>
+      </c>
+      <c r="K258" t="s">
+        <v>22</v>
+      </c>
+      <c r="L258" t="s">
+        <v>533</v>
+      </c>
+      <c r="M258" t="s">
+        <v>18</v>
+      </c>
+      <c r="N258" t="s">
+        <v>534</v>
+      </c>
+      <c r="O258" t="s">
+        <v>20</v>
+      </c>
+      <c r="P258" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>546</v>
+      </c>
+      <c r="R258" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>206</v>
+      </c>
+      <c r="B259" t="s">
+        <v>207</v>
+      </c>
+      <c r="C259" t="s">
+        <v>215</v>
+      </c>
+      <c r="D259" t="s">
+        <v>216</v>
+      </c>
+      <c r="E259" t="s">
+        <v>32</v>
+      </c>
+      <c r="F259" t="s">
+        <v>33</v>
+      </c>
+      <c r="G259" t="s">
+        <v>547</v>
+      </c>
+      <c r="H259" t="s">
+        <v>148</v>
+      </c>
+      <c r="I259" t="s">
+        <v>149</v>
+      </c>
+      <c r="J259">
+        <v>64.150000000000006</v>
+      </c>
+      <c r="K259" t="s">
+        <v>329</v>
+      </c>
+      <c r="L259" t="s">
+        <v>533</v>
+      </c>
+      <c r="M259" t="s">
+        <v>18</v>
+      </c>
+      <c r="N259" t="s">
+        <v>534</v>
+      </c>
+      <c r="O259" t="s">
+        <v>20</v>
+      </c>
+      <c r="P259" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>548</v>
+      </c>
+      <c r="R259" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>206</v>
+      </c>
+      <c r="B260" t="s">
+        <v>207</v>
+      </c>
+      <c r="C260" t="s">
+        <v>215</v>
+      </c>
+      <c r="D260" t="s">
+        <v>216</v>
+      </c>
+      <c r="E260" t="s">
+        <v>32</v>
+      </c>
+      <c r="F260" t="s">
+        <v>33</v>
+      </c>
+      <c r="G260" t="s">
+        <v>536</v>
+      </c>
+      <c r="H260" t="s">
+        <v>73</v>
+      </c>
+      <c r="I260" t="s">
+        <v>74</v>
+      </c>
+      <c r="J260">
+        <v>84.7</v>
+      </c>
+      <c r="K260" t="s">
+        <v>329</v>
+      </c>
+      <c r="L260" t="s">
+        <v>533</v>
+      </c>
+      <c r="M260" t="s">
+        <v>18</v>
+      </c>
+      <c r="N260" t="s">
+        <v>534</v>
+      </c>
+      <c r="O260" t="s">
+        <v>20</v>
+      </c>
+      <c r="P260" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>549</v>
+      </c>
+      <c r="R260" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>206</v>
+      </c>
+      <c r="B261" t="s">
+        <v>207</v>
+      </c>
+      <c r="C261" t="s">
+        <v>215</v>
+      </c>
+      <c r="D261" t="s">
+        <v>216</v>
+      </c>
+      <c r="E261" t="s">
+        <v>32</v>
+      </c>
+      <c r="F261" t="s">
+        <v>33</v>
+      </c>
+      <c r="G261" t="s">
+        <v>536</v>
+      </c>
+      <c r="H261" t="s">
+        <v>195</v>
+      </c>
+      <c r="I261" t="s">
+        <v>196</v>
+      </c>
+      <c r="J261">
+        <v>26.54</v>
+      </c>
+      <c r="K261" t="s">
+        <v>23</v>
+      </c>
+      <c r="L261" t="s">
+        <v>533</v>
+      </c>
+      <c r="M261" t="s">
+        <v>18</v>
+      </c>
+      <c r="N261" t="s">
+        <v>534</v>
+      </c>
+      <c r="O261" t="s">
+        <v>20</v>
+      </c>
+      <c r="P261" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>550</v>
+      </c>
+      <c r="R261" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>206</v>
+      </c>
+      <c r="B262" t="s">
+        <v>207</v>
+      </c>
+      <c r="C262" t="s">
+        <v>215</v>
+      </c>
+      <c r="D262" t="s">
+        <v>216</v>
+      </c>
+      <c r="E262" t="s">
+        <v>32</v>
+      </c>
+      <c r="F262" t="s">
+        <v>33</v>
+      </c>
+      <c r="G262" t="s">
+        <v>536</v>
+      </c>
+      <c r="H262" t="s">
+        <v>551</v>
+      </c>
+      <c r="I262" t="s">
+        <v>552</v>
+      </c>
+      <c r="J262">
+        <v>25.65</v>
+      </c>
+      <c r="K262" t="s">
+        <v>23</v>
+      </c>
+      <c r="L262" t="s">
+        <v>533</v>
+      </c>
+      <c r="M262" t="s">
+        <v>18</v>
+      </c>
+      <c r="N262" t="s">
+        <v>534</v>
+      </c>
+      <c r="O262" t="s">
+        <v>20</v>
+      </c>
+      <c r="P262" t="s">
+        <v>553</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>554</v>
+      </c>
+      <c r="R262" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>206</v>
+      </c>
+      <c r="B263" t="s">
+        <v>207</v>
+      </c>
+      <c r="C263" t="s">
+        <v>215</v>
+      </c>
+      <c r="D263" t="s">
+        <v>216</v>
+      </c>
+      <c r="E263" t="s">
+        <v>32</v>
+      </c>
+      <c r="F263" t="s">
+        <v>33</v>
+      </c>
+      <c r="G263" t="s">
+        <v>555</v>
+      </c>
+      <c r="H263" t="s">
+        <v>333</v>
+      </c>
+      <c r="I263" t="s">
+        <v>334</v>
+      </c>
+      <c r="J263">
+        <v>38.659999999999997</v>
+      </c>
+      <c r="K263" t="s">
+        <v>23</v>
+      </c>
+      <c r="L263" t="s">
+        <v>533</v>
+      </c>
+      <c r="M263" t="s">
+        <v>18</v>
+      </c>
+      <c r="N263" t="s">
+        <v>534</v>
+      </c>
+      <c r="O263" t="s">
+        <v>20</v>
+      </c>
+      <c r="P263" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>556</v>
+      </c>
+      <c r="R263" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>206</v>
+      </c>
+      <c r="B264" t="s">
+        <v>207</v>
+      </c>
+      <c r="C264" t="s">
+        <v>215</v>
+      </c>
+      <c r="D264" t="s">
+        <v>216</v>
+      </c>
+      <c r="E264" t="s">
+        <v>32</v>
+      </c>
+      <c r="F264" t="s">
+        <v>33</v>
+      </c>
+      <c r="G264" t="s">
+        <v>536</v>
+      </c>
+      <c r="H264" t="s">
+        <v>28</v>
+      </c>
+      <c r="I264" t="s">
+        <v>29</v>
+      </c>
+      <c r="J264">
+        <v>21.97</v>
+      </c>
+      <c r="K264" t="s">
+        <v>23</v>
+      </c>
+      <c r="L264" t="s">
+        <v>533</v>
+      </c>
+      <c r="M264" t="s">
+        <v>18</v>
+      </c>
+      <c r="N264" t="s">
+        <v>534</v>
+      </c>
+      <c r="O264" t="s">
+        <v>20</v>
+      </c>
+      <c r="P264" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>557</v>
+      </c>
+      <c r="R264" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>206</v>
+      </c>
+      <c r="B265" t="s">
+        <v>207</v>
+      </c>
+      <c r="C265" t="s">
+        <v>215</v>
+      </c>
+      <c r="D265" t="s">
+        <v>216</v>
+      </c>
+      <c r="E265" t="s">
+        <v>32</v>
+      </c>
+      <c r="F265" t="s">
+        <v>33</v>
+      </c>
+      <c r="G265" t="s">
+        <v>536</v>
+      </c>
+      <c r="H265" t="s">
+        <v>132</v>
+      </c>
+      <c r="I265" t="s">
+        <v>133</v>
+      </c>
+      <c r="J265">
+        <v>60.15</v>
+      </c>
+      <c r="K265" t="s">
+        <v>50</v>
+      </c>
+      <c r="L265" t="s">
+        <v>533</v>
+      </c>
+      <c r="M265" t="s">
+        <v>18</v>
+      </c>
+      <c r="N265" t="s">
+        <v>534</v>
+      </c>
+      <c r="O265" t="s">
+        <v>20</v>
+      </c>
+      <c r="P265" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>558</v>
+      </c>
+      <c r="R265" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>206</v>
+      </c>
+      <c r="B266" t="s">
+        <v>207</v>
+      </c>
+      <c r="C266" t="s">
+        <v>215</v>
+      </c>
+      <c r="D266" t="s">
+        <v>216</v>
+      </c>
+      <c r="E266" t="s">
+        <v>32</v>
+      </c>
+      <c r="F266" t="s">
+        <v>33</v>
+      </c>
+      <c r="G266" t="s">
+        <v>559</v>
+      </c>
+      <c r="H266" t="s">
+        <v>560</v>
+      </c>
+      <c r="I266" t="s">
+        <v>561</v>
+      </c>
+      <c r="J266">
+        <v>13.52</v>
+      </c>
+      <c r="K266" t="s">
+        <v>23</v>
+      </c>
+      <c r="L266" t="s">
+        <v>533</v>
+      </c>
+      <c r="M266" t="s">
+        <v>18</v>
+      </c>
+      <c r="N266" t="s">
+        <v>534</v>
+      </c>
+      <c r="O266" t="s">
+        <v>20</v>
+      </c>
+      <c r="P266" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>563</v>
+      </c>
+      <c r="R266" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>206</v>
+      </c>
+      <c r="B267" t="s">
+        <v>207</v>
+      </c>
+      <c r="C267" t="s">
+        <v>215</v>
+      </c>
+      <c r="D267" t="s">
+        <v>216</v>
+      </c>
+      <c r="E267" t="s">
+        <v>32</v>
+      </c>
+      <c r="F267" t="s">
+        <v>33</v>
+      </c>
+      <c r="G267" t="s">
+        <v>536</v>
+      </c>
+      <c r="H267" t="s">
+        <v>38</v>
+      </c>
+      <c r="I267" t="s">
+        <v>39</v>
+      </c>
+      <c r="J267">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="K267" t="s">
+        <v>23</v>
+      </c>
+      <c r="L267" t="s">
+        <v>533</v>
+      </c>
+      <c r="M267" t="s">
+        <v>18</v>
+      </c>
+      <c r="N267" t="s">
+        <v>534</v>
+      </c>
+      <c r="O267" t="s">
+        <v>20</v>
+      </c>
+      <c r="P267" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>564</v>
+      </c>
+      <c r="R267" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>206</v>
+      </c>
+      <c r="B268" t="s">
+        <v>207</v>
+      </c>
+      <c r="C268" t="s">
+        <v>215</v>
+      </c>
+      <c r="D268" t="s">
+        <v>216</v>
+      </c>
+      <c r="E268" t="s">
+        <v>32</v>
+      </c>
+      <c r="F268" t="s">
+        <v>33</v>
+      </c>
+      <c r="G268" t="s">
+        <v>536</v>
+      </c>
+      <c r="H268" t="s">
+        <v>92</v>
+      </c>
+      <c r="I268" t="s">
+        <v>93</v>
+      </c>
+      <c r="J268">
+        <v>28.38</v>
+      </c>
+      <c r="K268" t="s">
+        <v>22</v>
+      </c>
+      <c r="L268" t="s">
+        <v>533</v>
+      </c>
+      <c r="M268" t="s">
+        <v>18</v>
+      </c>
+      <c r="N268" t="s">
+        <v>534</v>
+      </c>
+      <c r="O268" t="s">
+        <v>20</v>
+      </c>
+      <c r="P268" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>565</v>
+      </c>
+      <c r="R268" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>206</v>
+      </c>
+      <c r="B269" t="s">
+        <v>207</v>
+      </c>
+      <c r="C269" t="s">
+        <v>215</v>
+      </c>
+      <c r="D269" t="s">
+        <v>216</v>
+      </c>
+      <c r="E269" t="s">
+        <v>32</v>
+      </c>
+      <c r="F269" t="s">
+        <v>33</v>
+      </c>
+      <c r="G269" t="s">
+        <v>536</v>
+      </c>
+      <c r="H269" t="s">
+        <v>43</v>
+      </c>
+      <c r="I269" t="s">
+        <v>44</v>
+      </c>
+      <c r="J269">
+        <v>28.62</v>
+      </c>
+      <c r="K269" t="s">
+        <v>22</v>
+      </c>
+      <c r="L269" t="s">
+        <v>533</v>
+      </c>
+      <c r="M269" t="s">
+        <v>18</v>
+      </c>
+      <c r="N269" t="s">
+        <v>534</v>
+      </c>
+      <c r="O269" t="s">
+        <v>20</v>
+      </c>
+      <c r="P269" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>566</v>
+      </c>
+      <c r="R269" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>206</v>
+      </c>
+      <c r="B270" t="s">
+        <v>207</v>
+      </c>
+      <c r="C270" t="s">
+        <v>215</v>
+      </c>
+      <c r="D270" t="s">
+        <v>216</v>
+      </c>
+      <c r="E270" t="s">
+        <v>32</v>
+      </c>
+      <c r="F270" t="s">
+        <v>33</v>
+      </c>
+      <c r="G270" t="s">
+        <v>536</v>
+      </c>
+      <c r="H270" t="s">
+        <v>567</v>
+      </c>
+      <c r="I270" t="s">
+        <v>568</v>
+      </c>
+      <c r="J270">
+        <v>25.37</v>
+      </c>
+      <c r="K270" t="s">
+        <v>23</v>
+      </c>
+      <c r="L270" t="s">
+        <v>533</v>
+      </c>
+      <c r="M270" t="s">
+        <v>18</v>
+      </c>
+      <c r="N270" t="s">
+        <v>534</v>
+      </c>
+      <c r="O270" t="s">
+        <v>20</v>
+      </c>
+      <c r="P270" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>570</v>
+      </c>
+      <c r="R270" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>206</v>
+      </c>
+      <c r="B271" t="s">
+        <v>207</v>
+      </c>
+      <c r="C271" t="s">
+        <v>215</v>
+      </c>
+      <c r="D271" t="s">
+        <v>216</v>
+      </c>
+      <c r="E271" t="s">
+        <v>32</v>
+      </c>
+      <c r="F271" t="s">
+        <v>33</v>
+      </c>
+      <c r="G271" t="s">
+        <v>536</v>
+      </c>
+      <c r="H271" t="s">
+        <v>153</v>
+      </c>
+      <c r="I271" t="s">
+        <v>154</v>
+      </c>
+      <c r="J271">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="K271" t="s">
+        <v>23</v>
+      </c>
+      <c r="L271" t="s">
+        <v>533</v>
+      </c>
+      <c r="M271" t="s">
+        <v>18</v>
+      </c>
+      <c r="N271" t="s">
+        <v>534</v>
+      </c>
+      <c r="O271" t="s">
+        <v>20</v>
+      </c>
+      <c r="P271" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>571</v>
+      </c>
+      <c r="R271" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>206</v>
+      </c>
+      <c r="B272" t="s">
+        <v>207</v>
+      </c>
+      <c r="C272" t="s">
+        <v>221</v>
+      </c>
+      <c r="D272" t="s">
+        <v>222</v>
+      </c>
+      <c r="E272" t="s">
+        <v>223</v>
+      </c>
+      <c r="F272" t="s">
+        <v>151</v>
+      </c>
+      <c r="G272" t="s">
+        <v>572</v>
+      </c>
+      <c r="H272" t="s">
+        <v>573</v>
+      </c>
+      <c r="I272" t="s">
+        <v>574</v>
+      </c>
+      <c r="J272">
+        <v>22.05</v>
+      </c>
+      <c r="K272" t="s">
+        <v>23</v>
+      </c>
+      <c r="L272" t="s">
+        <v>533</v>
+      </c>
+      <c r="M272" t="s">
+        <v>18</v>
+      </c>
+      <c r="N272" t="s">
+        <v>534</v>
+      </c>
+      <c r="O272" t="s">
+        <v>20</v>
+      </c>
+      <c r="P272" t="s">
+        <v>575</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>576</v>
+      </c>
+      <c r="R272" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>206</v>
+      </c>
+      <c r="B273" t="s">
+        <v>207</v>
+      </c>
+      <c r="C273" t="s">
+        <v>221</v>
+      </c>
+      <c r="D273" t="s">
+        <v>222</v>
+      </c>
+      <c r="E273" t="s">
+        <v>223</v>
+      </c>
+      <c r="F273" t="s">
+        <v>151</v>
+      </c>
+      <c r="G273" t="s">
+        <v>403</v>
+      </c>
+      <c r="H273" t="s">
+        <v>148</v>
+      </c>
+      <c r="I273" t="s">
+        <v>149</v>
+      </c>
+      <c r="J273">
+        <v>25.66</v>
+      </c>
+      <c r="K273" t="s">
+        <v>22</v>
+      </c>
+      <c r="L273" t="s">
+        <v>533</v>
+      </c>
+      <c r="M273" t="s">
+        <v>18</v>
+      </c>
+      <c r="N273" t="s">
+        <v>534</v>
+      </c>
+      <c r="O273" t="s">
+        <v>20</v>
+      </c>
+      <c r="P273" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>548</v>
+      </c>
+      <c r="R273" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>206</v>
+      </c>
+      <c r="B274" t="s">
+        <v>207</v>
+      </c>
+      <c r="C274" t="s">
+        <v>221</v>
+      </c>
+      <c r="D274" t="s">
+        <v>222</v>
+      </c>
+      <c r="E274" t="s">
+        <v>223</v>
+      </c>
+      <c r="F274" t="s">
+        <v>151</v>
+      </c>
+      <c r="G274" t="s">
+        <v>577</v>
+      </c>
+      <c r="H274" t="s">
+        <v>189</v>
+      </c>
+      <c r="I274" t="s">
+        <v>190</v>
+      </c>
+      <c r="J274">
+        <v>24.54</v>
+      </c>
+      <c r="K274" t="s">
+        <v>23</v>
+      </c>
+      <c r="L274" t="s">
+        <v>533</v>
+      </c>
+      <c r="M274" t="s">
+        <v>18</v>
+      </c>
+      <c r="N274" t="s">
+        <v>534</v>
+      </c>
+      <c r="O274" t="s">
+        <v>20</v>
+      </c>
+      <c r="P274" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>578</v>
+      </c>
+      <c r="R274" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>206</v>
+      </c>
+      <c r="B275" t="s">
+        <v>207</v>
+      </c>
+      <c r="C275" t="s">
+        <v>221</v>
+      </c>
+      <c r="D275" t="s">
+        <v>222</v>
+      </c>
+      <c r="E275" t="s">
+        <v>223</v>
+      </c>
+      <c r="F275" t="s">
+        <v>151</v>
+      </c>
+      <c r="G275" t="s">
+        <v>544</v>
+      </c>
+      <c r="H275" t="s">
+        <v>579</v>
+      </c>
+      <c r="I275" t="s">
+        <v>580</v>
+      </c>
+      <c r="J275">
+        <v>-16.5</v>
+      </c>
+      <c r="K275" t="s">
+        <v>581</v>
+      </c>
+      <c r="L275" t="s">
+        <v>533</v>
+      </c>
+      <c r="M275" t="s">
+        <v>18</v>
+      </c>
+      <c r="N275" t="s">
+        <v>534</v>
+      </c>
+      <c r="O275" t="s">
+        <v>20</v>
+      </c>
+      <c r="P275" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>342</v>
+      </c>
+      <c r="R275" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>206</v>
+      </c>
+      <c r="B276" t="s">
+        <v>207</v>
+      </c>
+      <c r="C276" t="s">
+        <v>221</v>
+      </c>
+      <c r="D276" t="s">
+        <v>222</v>
+      </c>
+      <c r="E276" t="s">
+        <v>223</v>
+      </c>
+      <c r="F276" t="s">
+        <v>151</v>
+      </c>
+      <c r="G276" t="s">
+        <v>559</v>
+      </c>
+      <c r="H276" t="s">
+        <v>579</v>
+      </c>
+      <c r="I276" t="s">
+        <v>580</v>
+      </c>
+      <c r="J276">
+        <v>16.5</v>
+      </c>
+      <c r="K276" t="s">
+        <v>23</v>
+      </c>
+      <c r="L276" t="s">
+        <v>533</v>
+      </c>
+      <c r="M276" t="s">
+        <v>18</v>
+      </c>
+      <c r="N276" t="s">
+        <v>534</v>
+      </c>
+      <c r="O276" t="s">
+        <v>20</v>
+      </c>
+      <c r="P276" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>342</v>
+      </c>
+      <c r="R276" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>206</v>
+      </c>
+      <c r="B277" t="s">
+        <v>207</v>
+      </c>
+      <c r="C277" t="s">
+        <v>221</v>
+      </c>
+      <c r="D277" t="s">
+        <v>222</v>
+      </c>
+      <c r="E277" t="s">
+        <v>223</v>
+      </c>
+      <c r="F277" t="s">
+        <v>151</v>
+      </c>
+      <c r="G277" t="s">
+        <v>583</v>
+      </c>
+      <c r="H277" t="s">
+        <v>579</v>
+      </c>
+      <c r="I277" t="s">
+        <v>580</v>
+      </c>
+      <c r="J277">
+        <v>16.5</v>
+      </c>
+      <c r="K277" t="s">
+        <v>23</v>
+      </c>
+      <c r="L277" t="s">
+        <v>533</v>
+      </c>
+      <c r="M277" t="s">
+        <v>18</v>
+      </c>
+      <c r="N277" t="s">
+        <v>534</v>
+      </c>
+      <c r="O277" t="s">
+        <v>20</v>
+      </c>
+      <c r="P277" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>342</v>
+      </c>
+      <c r="R277" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>206</v>
+      </c>
+      <c r="B278" t="s">
+        <v>207</v>
+      </c>
+      <c r="C278" t="s">
+        <v>208</v>
+      </c>
+      <c r="D278" t="s">
+        <v>209</v>
+      </c>
+      <c r="E278" t="s">
+        <v>210</v>
+      </c>
+      <c r="F278" t="s">
+        <v>118</v>
+      </c>
+      <c r="G278" t="s">
+        <v>555</v>
+      </c>
+      <c r="H278" t="s">
+        <v>245</v>
+      </c>
+      <c r="I278" t="s">
+        <v>246</v>
+      </c>
+      <c r="J278">
+        <v>9.5</v>
+      </c>
+      <c r="K278" t="s">
+        <v>23</v>
+      </c>
+      <c r="L278" t="s">
+        <v>533</v>
+      </c>
+      <c r="M278" t="s">
+        <v>18</v>
+      </c>
+      <c r="N278" t="s">
+        <v>534</v>
+      </c>
+      <c r="O278" t="s">
+        <v>20</v>
+      </c>
+      <c r="P278" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>584</v>
+      </c>
+      <c r="R278" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>206</v>
+      </c>
+      <c r="B279" t="s">
+        <v>207</v>
+      </c>
+      <c r="C279" t="s">
+        <v>208</v>
+      </c>
+      <c r="D279" t="s">
+        <v>209</v>
+      </c>
+      <c r="E279" t="s">
+        <v>210</v>
+      </c>
+      <c r="F279" t="s">
+        <v>118</v>
+      </c>
+      <c r="G279" t="s">
+        <v>533</v>
+      </c>
+      <c r="H279" t="s">
+        <v>141</v>
+      </c>
+      <c r="I279" t="s">
+        <v>142</v>
+      </c>
+      <c r="J279">
+        <v>38.4</v>
+      </c>
+      <c r="K279" t="s">
+        <v>50</v>
+      </c>
+      <c r="L279" t="s">
+        <v>533</v>
+      </c>
+      <c r="M279" t="s">
+        <v>18</v>
+      </c>
+      <c r="N279" t="s">
+        <v>534</v>
+      </c>
+      <c r="O279" t="s">
+        <v>20</v>
+      </c>
+      <c r="P279" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>585</v>
+      </c>
+      <c r="R279" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>206</v>
+      </c>
+      <c r="B280" t="s">
+        <v>207</v>
+      </c>
+      <c r="C280" t="s">
+        <v>208</v>
+      </c>
+      <c r="D280" t="s">
+        <v>209</v>
+      </c>
+      <c r="E280" t="s">
+        <v>210</v>
+      </c>
+      <c r="F280" t="s">
+        <v>118</v>
+      </c>
+      <c r="G280" t="s">
+        <v>559</v>
+      </c>
+      <c r="H280" t="s">
+        <v>148</v>
+      </c>
+      <c r="I280" t="s">
+        <v>149</v>
+      </c>
+      <c r="J280">
+        <v>25.66</v>
+      </c>
+      <c r="K280" t="s">
+        <v>22</v>
+      </c>
+      <c r="L280" t="s">
+        <v>533</v>
+      </c>
+      <c r="M280" t="s">
+        <v>18</v>
+      </c>
+      <c r="N280" t="s">
+        <v>534</v>
+      </c>
+      <c r="O280" t="s">
+        <v>20</v>
+      </c>
+      <c r="P280" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>548</v>
+      </c>
+      <c r="R280" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>206</v>
+      </c>
+      <c r="B281" t="s">
+        <v>207</v>
+      </c>
+      <c r="C281" t="s">
+        <v>208</v>
+      </c>
+      <c r="D281" t="s">
+        <v>209</v>
+      </c>
+      <c r="E281" t="s">
+        <v>210</v>
+      </c>
+      <c r="F281" t="s">
+        <v>118</v>
+      </c>
+      <c r="G281" t="s">
+        <v>583</v>
+      </c>
+      <c r="H281" t="s">
+        <v>148</v>
+      </c>
+      <c r="I281" t="s">
+        <v>149</v>
+      </c>
+      <c r="J281">
+        <v>25.66</v>
+      </c>
+      <c r="K281" t="s">
+        <v>22</v>
+      </c>
+      <c r="L281" t="s">
+        <v>533</v>
+      </c>
+      <c r="M281" t="s">
+        <v>18</v>
+      </c>
+      <c r="N281" t="s">
+        <v>534</v>
+      </c>
+      <c r="O281" t="s">
+        <v>20</v>
+      </c>
+      <c r="P281" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>548</v>
+      </c>
+      <c r="R281" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>206</v>
+      </c>
+      <c r="B282" t="s">
+        <v>207</v>
+      </c>
+      <c r="C282" t="s">
+        <v>208</v>
+      </c>
+      <c r="D282" t="s">
+        <v>209</v>
+      </c>
+      <c r="E282" t="s">
+        <v>210</v>
+      </c>
+      <c r="F282" t="s">
+        <v>118</v>
+      </c>
+      <c r="G282" t="s">
+        <v>583</v>
+      </c>
+      <c r="H282" t="s">
+        <v>189</v>
+      </c>
+      <c r="I282" t="s">
+        <v>190</v>
+      </c>
+      <c r="J282">
+        <v>24.54</v>
+      </c>
+      <c r="K282" t="s">
+        <v>23</v>
+      </c>
+      <c r="L282" t="s">
+        <v>533</v>
+      </c>
+      <c r="M282" t="s">
+        <v>18</v>
+      </c>
+      <c r="N282" t="s">
+        <v>534</v>
+      </c>
+      <c r="O282" t="s">
+        <v>20</v>
+      </c>
+      <c r="P282" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>578</v>
+      </c>
+      <c r="R282" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>206</v>
+      </c>
+      <c r="B283" t="s">
+        <v>207</v>
+      </c>
+      <c r="C283" t="s">
+        <v>208</v>
+      </c>
+      <c r="D283" t="s">
+        <v>209</v>
+      </c>
+      <c r="E283" t="s">
+        <v>210</v>
+      </c>
+      <c r="F283" t="s">
+        <v>118</v>
+      </c>
+      <c r="G283" t="s">
+        <v>586</v>
+      </c>
+      <c r="H283" t="s">
+        <v>73</v>
+      </c>
+      <c r="I283" t="s">
+        <v>74</v>
+      </c>
+      <c r="J283">
+        <v>16.940000000000001</v>
+      </c>
+      <c r="K283" t="s">
+        <v>23</v>
+      </c>
+      <c r="L283" t="s">
+        <v>533</v>
+      </c>
+      <c r="M283" t="s">
+        <v>18</v>
+      </c>
+      <c r="N283" t="s">
+        <v>534</v>
+      </c>
+      <c r="O283" t="s">
+        <v>20</v>
+      </c>
+      <c r="P283" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>549</v>
+      </c>
+      <c r="R283" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>206</v>
+      </c>
+      <c r="B284" t="s">
+        <v>207</v>
+      </c>
+      <c r="C284" t="s">
+        <v>208</v>
+      </c>
+      <c r="D284" t="s">
+        <v>209</v>
+      </c>
+      <c r="E284" t="s">
+        <v>210</v>
+      </c>
+      <c r="F284" t="s">
+        <v>118</v>
+      </c>
+      <c r="G284" t="s">
+        <v>583</v>
+      </c>
+      <c r="H284" t="s">
+        <v>132</v>
+      </c>
+      <c r="I284" t="s">
+        <v>133</v>
+      </c>
+      <c r="J284">
+        <v>40.1</v>
+      </c>
+      <c r="K284" t="s">
+        <v>22</v>
+      </c>
+      <c r="L284" t="s">
+        <v>533</v>
+      </c>
+      <c r="M284" t="s">
+        <v>18</v>
+      </c>
+      <c r="N284" t="s">
+        <v>534</v>
+      </c>
+      <c r="O284" t="s">
+        <v>20</v>
+      </c>
+      <c r="P284" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>558</v>
+      </c>
+      <c r="R284" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>206</v>
+      </c>
+      <c r="B285" t="s">
+        <v>207</v>
+      </c>
+      <c r="C285" t="s">
+        <v>208</v>
+      </c>
+      <c r="D285" t="s">
+        <v>209</v>
+      </c>
+      <c r="E285" t="s">
+        <v>210</v>
+      </c>
+      <c r="F285" t="s">
+        <v>118</v>
+      </c>
+      <c r="G285" t="s">
+        <v>587</v>
+      </c>
+      <c r="H285" t="s">
+        <v>132</v>
+      </c>
+      <c r="I285" t="s">
+        <v>133</v>
+      </c>
+      <c r="J285">
+        <v>40.1</v>
+      </c>
+      <c r="K285" t="s">
+        <v>22</v>
+      </c>
+      <c r="L285" t="s">
+        <v>533</v>
+      </c>
+      <c r="M285" t="s">
+        <v>18</v>
+      </c>
+      <c r="N285" t="s">
+        <v>534</v>
+      </c>
+      <c r="O285" t="s">
+        <v>20</v>
+      </c>
+      <c r="P285" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>558</v>
+      </c>
+      <c r="R285" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>206</v>
+      </c>
+      <c r="B286" t="s">
+        <v>207</v>
+      </c>
+      <c r="C286" t="s">
+        <v>208</v>
+      </c>
+      <c r="D286" t="s">
+        <v>209</v>
+      </c>
+      <c r="E286" t="s">
+        <v>210</v>
+      </c>
+      <c r="F286" t="s">
+        <v>118</v>
+      </c>
+      <c r="G286" t="s">
+        <v>588</v>
+      </c>
+      <c r="H286" t="s">
+        <v>132</v>
+      </c>
+      <c r="I286" t="s">
+        <v>133</v>
+      </c>
+      <c r="J286">
+        <v>80.2</v>
+      </c>
+      <c r="K286" t="s">
+        <v>40</v>
+      </c>
+      <c r="L286" t="s">
+        <v>533</v>
+      </c>
+      <c r="M286" t="s">
+        <v>18</v>
+      </c>
+      <c r="N286" t="s">
+        <v>534</v>
+      </c>
+      <c r="O286" t="s">
+        <v>20</v>
+      </c>
+      <c r="P286" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>558</v>
+      </c>
+      <c r="R286" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>206</v>
+      </c>
+      <c r="B287" t="s">
+        <v>207</v>
+      </c>
+      <c r="C287" t="s">
+        <v>208</v>
+      </c>
+      <c r="D287" t="s">
+        <v>209</v>
+      </c>
+      <c r="E287" t="s">
+        <v>210</v>
+      </c>
+      <c r="F287" t="s">
+        <v>118</v>
+      </c>
+      <c r="G287" t="s">
+        <v>589</v>
+      </c>
+      <c r="H287" t="s">
+        <v>38</v>
+      </c>
+      <c r="I287" t="s">
+        <v>39</v>
+      </c>
+      <c r="J287">
+        <v>19.309999999999999</v>
+      </c>
+      <c r="K287" t="s">
+        <v>23</v>
+      </c>
+      <c r="L287" t="s">
+        <v>533</v>
+      </c>
+      <c r="M287" t="s">
+        <v>18</v>
+      </c>
+      <c r="N287" t="s">
+        <v>534</v>
+      </c>
+      <c r="O287" t="s">
+        <v>20</v>
+      </c>
+      <c r="P287" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>564</v>
+      </c>
+      <c r="R287" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>206</v>
+      </c>
+      <c r="B288" t="s">
+        <v>207</v>
+      </c>
+      <c r="C288" t="s">
+        <v>208</v>
+      </c>
+      <c r="D288" t="s">
+        <v>209</v>
+      </c>
+      <c r="E288" t="s">
+        <v>210</v>
+      </c>
+      <c r="F288" t="s">
+        <v>118</v>
+      </c>
+      <c r="G288" t="s">
+        <v>547</v>
+      </c>
+      <c r="H288" t="s">
+        <v>38</v>
+      </c>
+      <c r="I288" t="s">
+        <v>39</v>
+      </c>
+      <c r="J288">
+        <v>38.619999999999997</v>
+      </c>
+      <c r="K288" t="s">
+        <v>22</v>
+      </c>
+      <c r="L288" t="s">
+        <v>533</v>
+      </c>
+      <c r="M288" t="s">
+        <v>18</v>
+      </c>
+      <c r="N288" t="s">
+        <v>534</v>
+      </c>
+      <c r="O288" t="s">
+        <v>20</v>
+      </c>
+      <c r="P288" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>564</v>
+      </c>
+      <c r="R288" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>206</v>
+      </c>
+      <c r="B289" t="s">
+        <v>207</v>
+      </c>
+      <c r="C289" t="s">
+        <v>208</v>
+      </c>
+      <c r="D289" t="s">
+        <v>209</v>
+      </c>
+      <c r="E289" t="s">
+        <v>210</v>
+      </c>
+      <c r="F289" t="s">
+        <v>118</v>
+      </c>
+      <c r="G289" t="s">
+        <v>589</v>
+      </c>
+      <c r="H289" t="s">
+        <v>53</v>
+      </c>
+      <c r="I289" t="s">
+        <v>54</v>
+      </c>
+      <c r="J289">
+        <v>28.38</v>
+      </c>
+      <c r="K289" t="s">
+        <v>23</v>
+      </c>
+      <c r="L289" t="s">
+        <v>533</v>
+      </c>
+      <c r="M289" t="s">
+        <v>18</v>
+      </c>
+      <c r="N289" t="s">
+        <v>534</v>
+      </c>
+      <c r="O289" t="s">
+        <v>20</v>
+      </c>
+      <c r="P289" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>590</v>
+      </c>
+      <c r="R289" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>206</v>
+      </c>
+      <c r="B290" t="s">
+        <v>207</v>
+      </c>
+      <c r="C290" t="s">
+        <v>208</v>
+      </c>
+      <c r="D290" t="s">
+        <v>209</v>
+      </c>
+      <c r="E290" t="s">
+        <v>210</v>
+      </c>
+      <c r="F290" t="s">
+        <v>118</v>
+      </c>
+      <c r="G290" t="s">
+        <v>587</v>
+      </c>
+      <c r="H290" t="s">
+        <v>53</v>
+      </c>
+      <c r="I290" t="s">
+        <v>54</v>
+      </c>
+      <c r="J290">
+        <v>28.38</v>
+      </c>
+      <c r="K290" t="s">
+        <v>23</v>
+      </c>
+      <c r="L290" t="s">
+        <v>533</v>
+      </c>
+      <c r="M290" t="s">
+        <v>18</v>
+      </c>
+      <c r="N290" t="s">
+        <v>534</v>
+      </c>
+      <c r="O290" t="s">
+        <v>20</v>
+      </c>
+      <c r="P290" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>590</v>
+      </c>
+      <c r="R290" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>206</v>
+      </c>
+      <c r="B291" t="s">
+        <v>207</v>
+      </c>
+      <c r="C291" t="s">
+        <v>208</v>
+      </c>
+      <c r="D291" t="s">
+        <v>209</v>
+      </c>
+      <c r="E291" t="s">
+        <v>210</v>
+      </c>
+      <c r="F291" t="s">
+        <v>118</v>
+      </c>
+      <c r="G291" t="s">
+        <v>591</v>
+      </c>
+      <c r="H291" t="s">
+        <v>183</v>
+      </c>
+      <c r="I291" t="s">
+        <v>184</v>
+      </c>
+      <c r="J291">
+        <v>12.97</v>
+      </c>
+      <c r="K291" t="s">
+        <v>23</v>
+      </c>
+      <c r="L291" t="s">
+        <v>533</v>
+      </c>
+      <c r="M291" t="s">
+        <v>18</v>
+      </c>
+      <c r="N291" t="s">
+        <v>534</v>
+      </c>
+      <c r="O291" t="s">
+        <v>20</v>
+      </c>
+      <c r="P291" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>592</v>
+      </c>
+      <c r="R291" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>206</v>
+      </c>
+      <c r="B292" t="s">
+        <v>207</v>
+      </c>
+      <c r="C292" t="s">
+        <v>593</v>
+      </c>
+      <c r="D292" t="s">
+        <v>594</v>
+      </c>
+      <c r="E292" t="s">
+        <v>595</v>
+      </c>
+      <c r="F292" t="s">
+        <v>596</v>
+      </c>
+      <c r="G292" t="s">
+        <v>597</v>
+      </c>
+      <c r="H292" t="s">
+        <v>598</v>
+      </c>
+      <c r="I292" t="s">
+        <v>599</v>
+      </c>
+      <c r="J292">
+        <v>89.92</v>
+      </c>
+      <c r="K292" t="s">
+        <v>22</v>
+      </c>
+      <c r="L292" t="s">
+        <v>533</v>
+      </c>
+      <c r="M292" t="s">
+        <v>18</v>
+      </c>
+      <c r="N292" t="s">
+        <v>534</v>
+      </c>
+      <c r="O292" t="s">
+        <v>20</v>
+      </c>
+      <c r="P292" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>601</v>
+      </c>
+      <c r="R292" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>206</v>
+      </c>
+      <c r="B293" t="s">
+        <v>207</v>
+      </c>
+      <c r="C293" t="s">
+        <v>593</v>
+      </c>
+      <c r="D293" t="s">
+        <v>594</v>
+      </c>
+      <c r="E293" t="s">
+        <v>595</v>
+      </c>
+      <c r="F293" t="s">
+        <v>596</v>
+      </c>
+      <c r="G293" t="s">
+        <v>597</v>
+      </c>
+      <c r="H293" t="s">
+        <v>28</v>
+      </c>
+      <c r="I293" t="s">
+        <v>29</v>
+      </c>
+      <c r="J293">
+        <v>21.97</v>
+      </c>
+      <c r="K293" t="s">
+        <v>23</v>
+      </c>
+      <c r="L293" t="s">
+        <v>533</v>
+      </c>
+      <c r="M293" t="s">
+        <v>18</v>
+      </c>
+      <c r="N293" t="s">
+        <v>534</v>
+      </c>
+      <c r="O293" t="s">
+        <v>20</v>
+      </c>
+      <c r="P293" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>557</v>
+      </c>
+      <c r="R293" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>206</v>
+      </c>
+      <c r="B294" t="s">
+        <v>207</v>
+      </c>
+      <c r="C294" t="s">
+        <v>602</v>
+      </c>
+      <c r="D294" t="s">
+        <v>603</v>
+      </c>
+      <c r="E294" t="s">
+        <v>604</v>
+      </c>
+      <c r="F294" t="s">
+        <v>605</v>
+      </c>
+      <c r="G294" t="s">
+        <v>577</v>
+      </c>
+      <c r="H294" t="s">
+        <v>606</v>
+      </c>
+      <c r="I294" t="s">
+        <v>607</v>
+      </c>
+      <c r="J294">
+        <v>62.31</v>
+      </c>
+      <c r="K294" t="s">
+        <v>50</v>
+      </c>
+      <c r="L294" t="s">
+        <v>533</v>
+      </c>
+      <c r="M294" t="s">
+        <v>18</v>
+      </c>
+      <c r="N294" t="s">
+        <v>534</v>
+      </c>
+      <c r="O294" t="s">
+        <v>20</v>
+      </c>
+      <c r="P294" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>609</v>
+      </c>
+      <c r="R294" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>206</v>
+      </c>
+      <c r="B295" t="s">
+        <v>207</v>
+      </c>
+      <c r="C295" t="s">
+        <v>251</v>
+      </c>
+      <c r="D295" t="s">
+        <v>252</v>
+      </c>
+      <c r="E295" t="s">
+        <v>198</v>
+      </c>
+      <c r="F295" t="s">
+        <v>119</v>
+      </c>
+      <c r="G295" t="s">
+        <v>591</v>
+      </c>
+      <c r="H295" t="s">
+        <v>148</v>
+      </c>
+      <c r="I295" t="s">
+        <v>149</v>
+      </c>
+      <c r="J295">
+        <v>51.32</v>
+      </c>
+      <c r="K295" t="s">
+        <v>40</v>
+      </c>
+      <c r="L295" t="s">
+        <v>533</v>
+      </c>
+      <c r="M295" t="s">
+        <v>18</v>
+      </c>
+      <c r="N295" t="s">
+        <v>534</v>
+      </c>
+      <c r="O295" t="s">
+        <v>20</v>
+      </c>
+      <c r="P295" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>548</v>
+      </c>
+      <c r="R295" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>206</v>
+      </c>
+      <c r="B296" t="s">
+        <v>207</v>
+      </c>
+      <c r="C296" t="s">
+        <v>251</v>
+      </c>
+      <c r="D296" t="s">
+        <v>252</v>
+      </c>
+      <c r="E296" t="s">
+        <v>198</v>
+      </c>
+      <c r="F296" t="s">
+        <v>119</v>
+      </c>
+      <c r="G296" t="s">
+        <v>610</v>
+      </c>
+      <c r="H296" t="s">
+        <v>73</v>
+      </c>
+      <c r="I296" t="s">
+        <v>74</v>
+      </c>
+      <c r="J296">
+        <v>50.82</v>
+      </c>
+      <c r="K296" t="s">
+        <v>50</v>
+      </c>
+      <c r="L296" t="s">
+        <v>533</v>
+      </c>
+      <c r="M296" t="s">
+        <v>18</v>
+      </c>
+      <c r="N296" t="s">
+        <v>534</v>
+      </c>
+      <c r="O296" t="s">
+        <v>20</v>
+      </c>
+      <c r="P296" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>549</v>
+      </c>
+      <c r="R296" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>206</v>
+      </c>
+      <c r="B297" t="s">
+        <v>207</v>
+      </c>
+      <c r="C297" t="s">
+        <v>251</v>
+      </c>
+      <c r="D297" t="s">
+        <v>252</v>
+      </c>
+      <c r="E297" t="s">
+        <v>198</v>
+      </c>
+      <c r="F297" t="s">
+        <v>119</v>
+      </c>
+      <c r="G297" t="s">
+        <v>591</v>
+      </c>
+      <c r="H297" t="s">
+        <v>433</v>
+      </c>
+      <c r="I297" t="s">
+        <v>434</v>
+      </c>
+      <c r="J297">
+        <v>15.16</v>
+      </c>
+      <c r="K297" t="s">
+        <v>23</v>
+      </c>
+      <c r="L297" t="s">
+        <v>533</v>
+      </c>
+      <c r="M297" t="s">
+        <v>18</v>
+      </c>
+      <c r="N297" t="s">
+        <v>534</v>
+      </c>
+      <c r="O297" t="s">
+        <v>20</v>
+      </c>
+      <c r="P297" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>611</v>
+      </c>
+      <c r="R297" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>206</v>
+      </c>
+      <c r="B298" t="s">
+        <v>207</v>
+      </c>
+      <c r="C298" t="s">
+        <v>251</v>
+      </c>
+      <c r="D298" t="s">
+        <v>252</v>
+      </c>
+      <c r="E298" t="s">
+        <v>198</v>
+      </c>
+      <c r="F298" t="s">
+        <v>119</v>
+      </c>
+      <c r="G298" t="s">
+        <v>612</v>
+      </c>
+      <c r="H298" t="s">
+        <v>433</v>
+      </c>
+      <c r="I298" t="s">
+        <v>434</v>
+      </c>
+      <c r="J298">
+        <v>15.16</v>
+      </c>
+      <c r="K298" t="s">
+        <v>23</v>
+      </c>
+      <c r="L298" t="s">
+        <v>533</v>
+      </c>
+      <c r="M298" t="s">
+        <v>18</v>
+      </c>
+      <c r="N298" t="s">
+        <v>534</v>
+      </c>
+      <c r="O298" t="s">
+        <v>20</v>
+      </c>
+      <c r="P298" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>611</v>
+      </c>
+      <c r="R298" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>206</v>
+      </c>
+      <c r="B299" t="s">
+        <v>207</v>
+      </c>
+      <c r="C299" t="s">
+        <v>251</v>
+      </c>
+      <c r="D299" t="s">
+        <v>252</v>
+      </c>
+      <c r="E299" t="s">
+        <v>198</v>
+      </c>
+      <c r="F299" t="s">
+        <v>119</v>
+      </c>
+      <c r="G299" t="s">
+        <v>591</v>
+      </c>
+      <c r="H299" t="s">
+        <v>613</v>
+      </c>
+      <c r="I299" t="s">
+        <v>614</v>
+      </c>
+      <c r="J299">
+        <v>8.77</v>
+      </c>
+      <c r="K299" t="s">
+        <v>23</v>
+      </c>
+      <c r="L299" t="s">
+        <v>533</v>
+      </c>
+      <c r="M299" t="s">
+        <v>18</v>
+      </c>
+      <c r="N299" t="s">
+        <v>534</v>
+      </c>
+      <c r="O299" t="s">
+        <v>20</v>
+      </c>
+      <c r="P299" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>616</v>
+      </c>
+      <c r="R299" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>206</v>
+      </c>
+      <c r="B300" t="s">
+        <v>207</v>
+      </c>
+      <c r="C300" t="s">
+        <v>251</v>
+      </c>
+      <c r="D300" t="s">
+        <v>252</v>
+      </c>
+      <c r="E300" t="s">
+        <v>198</v>
+      </c>
+      <c r="F300" t="s">
+        <v>119</v>
+      </c>
+      <c r="G300" t="s">
+        <v>583</v>
+      </c>
+      <c r="H300" t="s">
+        <v>613</v>
+      </c>
+      <c r="I300" t="s">
+        <v>614</v>
+      </c>
+      <c r="J300">
+        <v>8.77</v>
+      </c>
+      <c r="K300" t="s">
+        <v>23</v>
+      </c>
+      <c r="L300" t="s">
+        <v>533</v>
+      </c>
+      <c r="M300" t="s">
+        <v>18</v>
+      </c>
+      <c r="N300" t="s">
+        <v>534</v>
+      </c>
+      <c r="O300" t="s">
+        <v>20</v>
+      </c>
+      <c r="P300" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q300" t="s">
+        <v>616</v>
+      </c>
+      <c r="R300" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>206</v>
+      </c>
+      <c r="B301" t="s">
+        <v>207</v>
+      </c>
+      <c r="C301" t="s">
+        <v>251</v>
+      </c>
+      <c r="D301" t="s">
+        <v>252</v>
+      </c>
+      <c r="E301" t="s">
+        <v>198</v>
+      </c>
+      <c r="F301" t="s">
+        <v>119</v>
+      </c>
+      <c r="G301" t="s">
+        <v>559</v>
+      </c>
+      <c r="H301" t="s">
+        <v>132</v>
+      </c>
+      <c r="I301" t="s">
+        <v>133</v>
+      </c>
+      <c r="J301">
+        <v>40.1</v>
+      </c>
+      <c r="K301" t="s">
+        <v>22</v>
+      </c>
+      <c r="L301" t="s">
+        <v>533</v>
+      </c>
+      <c r="M301" t="s">
+        <v>18</v>
+      </c>
+      <c r="N301" t="s">
+        <v>534</v>
+      </c>
+      <c r="O301" t="s">
+        <v>20</v>
+      </c>
+      <c r="P301" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q301" t="s">
+        <v>558</v>
+      </c>
+      <c r="R301" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>206</v>
+      </c>
+      <c r="B302" t="s">
+        <v>207</v>
+      </c>
+      <c r="C302" t="s">
+        <v>251</v>
+      </c>
+      <c r="D302" t="s">
+        <v>252</v>
+      </c>
+      <c r="E302" t="s">
+        <v>198</v>
+      </c>
+      <c r="F302" t="s">
+        <v>119</v>
+      </c>
+      <c r="G302" t="s">
+        <v>591</v>
+      </c>
+      <c r="H302" t="s">
+        <v>43</v>
+      </c>
+      <c r="I302" t="s">
+        <v>44</v>
+      </c>
+      <c r="J302">
+        <v>14.31</v>
+      </c>
+      <c r="K302" t="s">
+        <v>23</v>
+      </c>
+      <c r="L302" t="s">
+        <v>533</v>
+      </c>
+      <c r="M302" t="s">
+        <v>18</v>
+      </c>
+      <c r="N302" t="s">
+        <v>534</v>
+      </c>
+      <c r="O302" t="s">
+        <v>20</v>
+      </c>
+      <c r="P302" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q302" t="s">
+        <v>566</v>
+      </c>
+      <c r="R302" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>206</v>
+      </c>
+      <c r="B303" t="s">
+        <v>207</v>
+      </c>
+      <c r="C303" t="s">
+        <v>251</v>
+      </c>
+      <c r="D303" t="s">
+        <v>252</v>
+      </c>
+      <c r="E303" t="s">
+        <v>198</v>
+      </c>
+      <c r="F303" t="s">
+        <v>119</v>
+      </c>
+      <c r="G303" t="s">
+        <v>589</v>
+      </c>
+      <c r="H303" t="s">
+        <v>180</v>
+      </c>
+      <c r="I303" t="s">
+        <v>181</v>
+      </c>
+      <c r="J303">
+        <v>24.57</v>
+      </c>
+      <c r="K303" t="s">
+        <v>23</v>
+      </c>
+      <c r="L303" t="s">
+        <v>533</v>
+      </c>
+      <c r="M303" t="s">
+        <v>18</v>
+      </c>
+      <c r="N303" t="s">
+        <v>534</v>
+      </c>
+      <c r="O303" t="s">
+        <v>20</v>
+      </c>
+      <c r="P303" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q303" t="s">
+        <v>617</v>
+      </c>
+      <c r="R303" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>206</v>
+      </c>
+      <c r="B304" t="s">
+        <v>207</v>
+      </c>
+      <c r="C304" t="s">
+        <v>466</v>
+      </c>
+      <c r="D304" t="s">
+        <v>222</v>
+      </c>
+      <c r="E304" t="s">
+        <v>467</v>
+      </c>
+      <c r="F304" t="s">
+        <v>110</v>
+      </c>
+      <c r="G304" t="s">
+        <v>533</v>
+      </c>
+      <c r="H304" t="s">
+        <v>148</v>
+      </c>
+      <c r="I304" t="s">
+        <v>149</v>
+      </c>
+      <c r="J304">
+        <v>51.32</v>
+      </c>
+      <c r="K304" t="s">
+        <v>40</v>
+      </c>
+      <c r="L304" t="s">
+        <v>533</v>
+      </c>
+      <c r="M304" t="s">
+        <v>18</v>
+      </c>
+      <c r="N304" t="s">
+        <v>534</v>
+      </c>
+      <c r="O304" t="s">
+        <v>20</v>
+      </c>
+      <c r="P304" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q304" t="s">
+        <v>548</v>
+      </c>
+      <c r="R304" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>206</v>
+      </c>
+      <c r="B305" t="s">
+        <v>207</v>
+      </c>
+      <c r="C305" t="s">
+        <v>212</v>
+      </c>
+      <c r="D305" t="s">
+        <v>213</v>
+      </c>
+      <c r="E305" t="s">
+        <v>214</v>
+      </c>
+      <c r="F305" t="s">
+        <v>70</v>
+      </c>
+      <c r="G305" t="s">
+        <v>618</v>
+      </c>
+      <c r="H305" t="s">
+        <v>156</v>
+      </c>
+      <c r="I305" t="s">
+        <v>157</v>
+      </c>
+      <c r="J305">
+        <v>27.71</v>
+      </c>
+      <c r="K305" t="s">
+        <v>23</v>
+      </c>
+      <c r="L305" t="s">
+        <v>533</v>
+      </c>
+      <c r="M305" t="s">
+        <v>18</v>
+      </c>
+      <c r="N305" t="s">
+        <v>534</v>
+      </c>
+      <c r="O305" t="s">
+        <v>20</v>
+      </c>
+      <c r="P305" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q305" t="s">
+        <v>619</v>
+      </c>
+      <c r="R305" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>206</v>
+      </c>
+      <c r="B306" t="s">
+        <v>207</v>
+      </c>
+      <c r="C306" t="s">
+        <v>212</v>
+      </c>
+      <c r="D306" t="s">
+        <v>213</v>
+      </c>
+      <c r="E306" t="s">
+        <v>214</v>
+      </c>
+      <c r="F306" t="s">
+        <v>70</v>
+      </c>
+      <c r="G306" t="s">
+        <v>618</v>
+      </c>
+      <c r="H306" t="s">
+        <v>123</v>
+      </c>
+      <c r="I306" t="s">
+        <v>124</v>
+      </c>
+      <c r="J306">
+        <v>27.79</v>
+      </c>
+      <c r="K306" t="s">
+        <v>23</v>
+      </c>
+      <c r="L306" t="s">
+        <v>533</v>
+      </c>
+      <c r="M306" t="s">
+        <v>18</v>
+      </c>
+      <c r="N306" t="s">
+        <v>534</v>
+      </c>
+      <c r="O306" t="s">
+        <v>20</v>
+      </c>
+      <c r="P306" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q306" t="s">
+        <v>538</v>
+      </c>
+      <c r="R306" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>206</v>
+      </c>
+      <c r="B307" t="s">
+        <v>207</v>
+      </c>
+      <c r="C307" t="s">
+        <v>212</v>
+      </c>
+      <c r="D307" t="s">
+        <v>213</v>
+      </c>
+      <c r="E307" t="s">
+        <v>214</v>
+      </c>
+      <c r="F307" t="s">
+        <v>70</v>
+      </c>
+      <c r="G307" t="s">
+        <v>559</v>
+      </c>
+      <c r="H307" t="s">
+        <v>511</v>
+      </c>
+      <c r="I307" t="s">
+        <v>512</v>
+      </c>
+      <c r="J307">
+        <v>14.82</v>
+      </c>
+      <c r="K307" t="s">
+        <v>22</v>
+      </c>
+      <c r="L307" t="s">
+        <v>533</v>
+      </c>
+      <c r="M307" t="s">
+        <v>18</v>
+      </c>
+      <c r="N307" t="s">
+        <v>534</v>
+      </c>
+      <c r="O307" t="s">
+        <v>20</v>
+      </c>
+      <c r="P307" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q307" t="s">
+        <v>514</v>
+      </c>
+      <c r="R307" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>206</v>
+      </c>
+      <c r="B308" t="s">
+        <v>207</v>
+      </c>
+      <c r="C308" t="s">
+        <v>212</v>
+      </c>
+      <c r="D308" t="s">
+        <v>213</v>
+      </c>
+      <c r="E308" t="s">
+        <v>214</v>
+      </c>
+      <c r="F308" t="s">
+        <v>70</v>
+      </c>
+      <c r="G308" t="s">
+        <v>618</v>
+      </c>
+      <c r="H308" t="s">
+        <v>620</v>
+      </c>
+      <c r="I308" t="s">
+        <v>621</v>
+      </c>
+      <c r="J308">
+        <v>15.88</v>
+      </c>
+      <c r="K308" t="s">
+        <v>22</v>
+      </c>
+      <c r="L308" t="s">
+        <v>533</v>
+      </c>
+      <c r="M308" t="s">
+        <v>18</v>
+      </c>
+      <c r="N308" t="s">
+        <v>534</v>
+      </c>
+      <c r="O308" t="s">
+        <v>20</v>
+      </c>
+      <c r="P308" t="s">
+        <v>622</v>
+      </c>
+      <c r="Q308" t="s">
+        <v>623</v>
+      </c>
+      <c r="R308" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>206</v>
+      </c>
+      <c r="B309" t="s">
+        <v>207</v>
+      </c>
+      <c r="C309" t="s">
+        <v>212</v>
+      </c>
+      <c r="D309" t="s">
+        <v>213</v>
+      </c>
+      <c r="E309" t="s">
+        <v>214</v>
+      </c>
+      <c r="F309" t="s">
+        <v>70</v>
+      </c>
+      <c r="G309" t="s">
+        <v>618</v>
+      </c>
+      <c r="H309" t="s">
+        <v>129</v>
+      </c>
+      <c r="I309" t="s">
+        <v>130</v>
+      </c>
+      <c r="J309">
+        <v>28.03</v>
+      </c>
+      <c r="K309" t="s">
+        <v>23</v>
+      </c>
+      <c r="L309" t="s">
+        <v>533</v>
+      </c>
+      <c r="M309" t="s">
+        <v>18</v>
+      </c>
+      <c r="N309" t="s">
+        <v>534</v>
+      </c>
+      <c r="O309" t="s">
+        <v>20</v>
+      </c>
+      <c r="P309" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q309" t="s">
+        <v>624</v>
+      </c>
+      <c r="R309" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>206</v>
+      </c>
+      <c r="B310" t="s">
+        <v>207</v>
+      </c>
+      <c r="C310" t="s">
+        <v>212</v>
+      </c>
+      <c r="D310" t="s">
+        <v>213</v>
+      </c>
+      <c r="E310" t="s">
+        <v>214</v>
+      </c>
+      <c r="F310" t="s">
+        <v>70</v>
+      </c>
+      <c r="G310" t="s">
+        <v>536</v>
+      </c>
+      <c r="H310" t="s">
+        <v>148</v>
+      </c>
+      <c r="I310" t="s">
+        <v>149</v>
+      </c>
+      <c r="J310">
+        <v>12.83</v>
+      </c>
+      <c r="K310" t="s">
+        <v>23</v>
+      </c>
+      <c r="L310" t="s">
+        <v>533</v>
+      </c>
+      <c r="M310" t="s">
+        <v>18</v>
+      </c>
+      <c r="N310" t="s">
+        <v>534</v>
+      </c>
+      <c r="O310" t="s">
+        <v>20</v>
+      </c>
+      <c r="P310" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q310" t="s">
+        <v>548</v>
+      </c>
+      <c r="R310" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>206</v>
+      </c>
+      <c r="B311" t="s">
+        <v>207</v>
+      </c>
+      <c r="C311" t="s">
+        <v>212</v>
+      </c>
+      <c r="D311" t="s">
+        <v>213</v>
+      </c>
+      <c r="E311" t="s">
+        <v>214</v>
+      </c>
+      <c r="F311" t="s">
+        <v>70</v>
+      </c>
+      <c r="G311" t="s">
+        <v>618</v>
+      </c>
+      <c r="H311" t="s">
+        <v>79</v>
+      </c>
+      <c r="I311" t="s">
+        <v>80</v>
+      </c>
+      <c r="J311">
+        <v>64.260000000000005</v>
+      </c>
+      <c r="K311" t="s">
+        <v>50</v>
+      </c>
+      <c r="L311" t="s">
+        <v>533</v>
+      </c>
+      <c r="M311" t="s">
+        <v>18</v>
+      </c>
+      <c r="N311" t="s">
+        <v>534</v>
+      </c>
+      <c r="O311" t="s">
+        <v>20</v>
+      </c>
+      <c r="P311" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q311" t="s">
+        <v>625</v>
+      </c>
+      <c r="R311" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>206</v>
+      </c>
+      <c r="B312" t="s">
+        <v>207</v>
+      </c>
+      <c r="C312" t="s">
+        <v>212</v>
+      </c>
+      <c r="D312" t="s">
+        <v>213</v>
+      </c>
+      <c r="E312" t="s">
+        <v>214</v>
+      </c>
+      <c r="F312" t="s">
+        <v>70</v>
+      </c>
+      <c r="G312" t="s">
+        <v>618</v>
+      </c>
+      <c r="H312" t="s">
+        <v>626</v>
+      </c>
+      <c r="I312" t="s">
+        <v>627</v>
+      </c>
+      <c r="J312">
+        <v>27.58</v>
+      </c>
+      <c r="K312" t="s">
+        <v>23</v>
+      </c>
+      <c r="L312" t="s">
+        <v>533</v>
+      </c>
+      <c r="M312" t="s">
+        <v>18</v>
+      </c>
+      <c r="N312" t="s">
+        <v>534</v>
+      </c>
+      <c r="O312" t="s">
+        <v>20</v>
+      </c>
+      <c r="P312" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q312" t="s">
+        <v>501</v>
+      </c>
+      <c r="R312" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>206</v>
+      </c>
+      <c r="B313" t="s">
+        <v>207</v>
+      </c>
+      <c r="C313" t="s">
+        <v>212</v>
+      </c>
+      <c r="D313" t="s">
+        <v>213</v>
+      </c>
+      <c r="E313" t="s">
+        <v>214</v>
+      </c>
+      <c r="F313" t="s">
+        <v>70</v>
+      </c>
+      <c r="G313" t="s">
+        <v>618</v>
+      </c>
+      <c r="H313" t="s">
+        <v>135</v>
+      </c>
+      <c r="I313" t="s">
+        <v>136</v>
+      </c>
+      <c r="J313">
+        <v>9.98</v>
+      </c>
+      <c r="K313" t="s">
+        <v>23</v>
+      </c>
+      <c r="L313" t="s">
+        <v>533</v>
+      </c>
+      <c r="M313" t="s">
+        <v>18</v>
+      </c>
+      <c r="N313" t="s">
+        <v>534</v>
+      </c>
+      <c r="O313" t="s">
+        <v>20</v>
+      </c>
+      <c r="P313" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q313" t="s">
+        <v>629</v>
+      </c>
+      <c r="R313" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>206</v>
+      </c>
+      <c r="B314" t="s">
+        <v>207</v>
+      </c>
+      <c r="C314" t="s">
+        <v>212</v>
+      </c>
+      <c r="D314" t="s">
+        <v>213</v>
+      </c>
+      <c r="E314" t="s">
+        <v>214</v>
+      </c>
+      <c r="F314" t="s">
+        <v>70</v>
+      </c>
+      <c r="G314" t="s">
+        <v>618</v>
+      </c>
+      <c r="H314" t="s">
+        <v>241</v>
+      </c>
+      <c r="I314" t="s">
+        <v>242</v>
+      </c>
+      <c r="J314">
+        <v>34.409999999999997</v>
+      </c>
+      <c r="K314" t="s">
+        <v>23</v>
+      </c>
+      <c r="L314" t="s">
+        <v>533</v>
+      </c>
+      <c r="M314" t="s">
+        <v>18</v>
+      </c>
+      <c r="N314" t="s">
+        <v>534</v>
+      </c>
+      <c r="O314" t="s">
+        <v>20</v>
+      </c>
+      <c r="P314" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q314" t="s">
+        <v>630</v>
+      </c>
+      <c r="R314" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>206</v>
+      </c>
+      <c r="B315" t="s">
+        <v>207</v>
+      </c>
+      <c r="C315" t="s">
+        <v>212</v>
+      </c>
+      <c r="D315" t="s">
+        <v>213</v>
+      </c>
+      <c r="E315" t="s">
+        <v>214</v>
+      </c>
+      <c r="F315" t="s">
+        <v>70</v>
+      </c>
+      <c r="G315" t="s">
+        <v>618</v>
+      </c>
+      <c r="H315" t="s">
+        <v>567</v>
+      </c>
+      <c r="I315" t="s">
+        <v>568</v>
+      </c>
+      <c r="J315">
+        <v>50.74</v>
+      </c>
+      <c r="K315" t="s">
+        <v>22</v>
+      </c>
+      <c r="L315" t="s">
+        <v>533</v>
+      </c>
+      <c r="M315" t="s">
+        <v>18</v>
+      </c>
+      <c r="N315" t="s">
+        <v>534</v>
+      </c>
+      <c r="O315" t="s">
+        <v>20</v>
+      </c>
+      <c r="P315" t="s">
+        <v>569</v>
+      </c>
+      <c r="Q315" t="s">
+        <v>570</v>
+      </c>
+      <c r="R315" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>206</v>
+      </c>
+      <c r="B316" t="s">
+        <v>207</v>
+      </c>
+      <c r="C316" t="s">
+        <v>233</v>
+      </c>
+      <c r="D316" t="s">
+        <v>222</v>
+      </c>
+      <c r="E316" t="s">
+        <v>234</v>
+      </c>
+      <c r="F316" t="s">
+        <v>110</v>
+      </c>
+      <c r="G316" t="s">
+        <v>559</v>
+      </c>
+      <c r="H316" t="s">
+        <v>73</v>
+      </c>
+      <c r="I316" t="s">
+        <v>74</v>
+      </c>
+      <c r="J316">
+        <v>16.940000000000001</v>
+      </c>
+      <c r="K316" t="s">
+        <v>23</v>
+      </c>
+      <c r="L316" t="s">
+        <v>533</v>
+      </c>
+      <c r="M316" t="s">
+        <v>18</v>
+      </c>
+      <c r="N316" t="s">
+        <v>19</v>
+      </c>
+      <c r="O316" t="s">
+        <v>20</v>
+      </c>
+      <c r="P316" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q316" t="s">
+        <v>549</v>
+      </c>
+      <c r="R316" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>206</v>
+      </c>
+      <c r="B317" t="s">
+        <v>207</v>
+      </c>
+      <c r="C317" t="s">
+        <v>233</v>
+      </c>
+      <c r="D317" t="s">
+        <v>222</v>
+      </c>
+      <c r="E317" t="s">
+        <v>234</v>
+      </c>
+      <c r="F317" t="s">
+        <v>110</v>
+      </c>
+      <c r="G317" t="s">
+        <v>577</v>
+      </c>
+      <c r="H317" t="s">
+        <v>73</v>
+      </c>
+      <c r="I317" t="s">
+        <v>74</v>
+      </c>
+      <c r="J317">
+        <v>50.82</v>
+      </c>
+      <c r="K317" t="s">
+        <v>50</v>
+      </c>
+      <c r="L317" t="s">
+        <v>533</v>
+      </c>
+      <c r="M317" t="s">
+        <v>18</v>
+      </c>
+      <c r="N317" t="s">
+        <v>19</v>
+      </c>
+      <c r="O317" t="s">
+        <v>20</v>
+      </c>
+      <c r="P317" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q317" t="s">
+        <v>549</v>
+      </c>
+      <c r="R317" t="s">
+        <v>631</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:S317" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16906,15 +20959,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -16938,10 +20995,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/activitereelgueudet-2026.xlsx
+++ b/activitereelgueudet-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F37C09EA-5C8C-4DA6-8CC2-3FE5E474DD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44133141-0AE7-4381-B52A-A2E3E41E102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5391" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="706">
   <si>
     <t>codePlaque</t>
   </si>
@@ -1932,16 +1932,244 @@
   </si>
   <si>
     <t>Avril</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0105 00                 </t>
+  </si>
+  <si>
+    <t>E0105</t>
+  </si>
+  <si>
+    <t>31/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAQUET DE 5 LAMES 16MM        </t>
+  </si>
+  <si>
+    <t>13.72</t>
+  </si>
+  <si>
+    <t>33.32</t>
+  </si>
+  <si>
+    <t>30.86</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86190 34                 </t>
+  </si>
+  <si>
+    <t>86190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PISTOLET ANTI GRAVILLON       </t>
+  </si>
+  <si>
+    <t>18.6</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>11.31</t>
+  </si>
+  <si>
+    <t>22/05/2026</t>
+  </si>
+  <si>
+    <t>12.96</t>
+  </si>
+  <si>
+    <t>16.98</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>18.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34586 02                 </t>
+  </si>
+  <si>
+    <t>34586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIMAIRE D'ADHERENCE DOUBLE   </t>
+  </si>
+  <si>
+    <t>17.74</t>
+  </si>
+  <si>
+    <t>20.5</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87077 22                 </t>
+  </si>
+  <si>
+    <t>87077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PARTS CLEANER N HEX </t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87722 22                 </t>
+  </si>
+  <si>
+    <t>87722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTI GRAVILLON TOUGHCOAT GRIS </t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>28.61</t>
+  </si>
+  <si>
+    <t>13.08</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>24.73</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>28.11</t>
+  </si>
+  <si>
+    <t>9.72</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>8.22</t>
+  </si>
+  <si>
+    <t>28/05/2026</t>
+  </si>
+  <si>
+    <t>19.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86807 00                 </t>
+  </si>
+  <si>
+    <t>86807</t>
+  </si>
+  <si>
+    <t>12 BUSES DE MELANGE-2KMEA SFEA</t>
+  </si>
+  <si>
+    <t>57.77</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>27.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1413 33                 </t>
+  </si>
+  <si>
+    <t>A1413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">finecut 150mm P1000           </t>
+  </si>
+  <si>
+    <t>27/05/2026</t>
+  </si>
+  <si>
+    <t>31.51</t>
+  </si>
+  <si>
+    <t>15.21</t>
+  </si>
+  <si>
+    <t>8.9</t>
+  </si>
+  <si>
+    <t>27.91</t>
+  </si>
+  <si>
+    <t>21.32</t>
+  </si>
+  <si>
+    <t>28.16</t>
+  </si>
+  <si>
+    <t>23.52</t>
+  </si>
+  <si>
+    <t>21.48</t>
+  </si>
+  <si>
+    <t>26.93</t>
+  </si>
+  <si>
+    <t>22.09</t>
+  </si>
+  <si>
+    <t>22.06</t>
+  </si>
+  <si>
+    <t>27.87</t>
+  </si>
+  <si>
+    <t>33.54</t>
+  </si>
+  <si>
+    <t>19.55</t>
+  </si>
+  <si>
+    <t>Mai</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2303,7 +2531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}">
-  <dimension ref="A1:S317"/>
+  <dimension ref="A1:S374"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -20808,16 +21036,3212 @@
         <v>631</v>
       </c>
     </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>206</v>
+      </c>
+      <c r="B318" t="s">
+        <v>207</v>
+      </c>
+      <c r="C318" t="s">
+        <v>215</v>
+      </c>
+      <c r="D318" t="s">
+        <v>216</v>
+      </c>
+      <c r="E318" t="s">
+        <v>32</v>
+      </c>
+      <c r="F318" t="s">
+        <v>33</v>
+      </c>
+      <c r="G318" t="s">
+        <v>632</v>
+      </c>
+      <c r="H318" t="s">
+        <v>633</v>
+      </c>
+      <c r="I318" t="s">
+        <v>634</v>
+      </c>
+      <c r="J318">
+        <v>13.72</v>
+      </c>
+      <c r="K318" t="s">
+        <v>23</v>
+      </c>
+      <c r="L318" t="s">
+        <v>635</v>
+      </c>
+      <c r="M318" t="s">
+        <v>18</v>
+      </c>
+      <c r="N318" t="s">
+        <v>534</v>
+      </c>
+      <c r="O318" t="s">
+        <v>20</v>
+      </c>
+      <c r="P318" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q318" t="s">
+        <v>637</v>
+      </c>
+      <c r="R318" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>206</v>
+      </c>
+      <c r="B319" t="s">
+        <v>207</v>
+      </c>
+      <c r="C319" t="s">
+        <v>215</v>
+      </c>
+      <c r="D319" t="s">
+        <v>216</v>
+      </c>
+      <c r="E319" t="s">
+        <v>32</v>
+      </c>
+      <c r="F319" t="s">
+        <v>33</v>
+      </c>
+      <c r="G319" t="s">
+        <v>632</v>
+      </c>
+      <c r="H319" t="s">
+        <v>46</v>
+      </c>
+      <c r="I319" t="s">
+        <v>47</v>
+      </c>
+      <c r="J319">
+        <v>33.32</v>
+      </c>
+      <c r="K319" t="s">
+        <v>23</v>
+      </c>
+      <c r="L319" t="s">
+        <v>635</v>
+      </c>
+      <c r="M319" t="s">
+        <v>18</v>
+      </c>
+      <c r="N319" t="s">
+        <v>534</v>
+      </c>
+      <c r="O319" t="s">
+        <v>20</v>
+      </c>
+      <c r="P319" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q319" t="s">
+        <v>638</v>
+      </c>
+      <c r="R319" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>206</v>
+      </c>
+      <c r="B320" t="s">
+        <v>207</v>
+      </c>
+      <c r="C320" t="s">
+        <v>215</v>
+      </c>
+      <c r="D320" t="s">
+        <v>216</v>
+      </c>
+      <c r="E320" t="s">
+        <v>32</v>
+      </c>
+      <c r="F320" t="s">
+        <v>33</v>
+      </c>
+      <c r="G320" t="s">
+        <v>632</v>
+      </c>
+      <c r="H320" t="s">
+        <v>507</v>
+      </c>
+      <c r="I320" t="s">
+        <v>508</v>
+      </c>
+      <c r="J320">
+        <v>30.86</v>
+      </c>
+      <c r="K320" t="s">
+        <v>23</v>
+      </c>
+      <c r="L320" t="s">
+        <v>635</v>
+      </c>
+      <c r="M320" t="s">
+        <v>18</v>
+      </c>
+      <c r="N320" t="s">
+        <v>534</v>
+      </c>
+      <c r="O320" t="s">
+        <v>20</v>
+      </c>
+      <c r="P320" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q320" t="s">
+        <v>639</v>
+      </c>
+      <c r="R320" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>206</v>
+      </c>
+      <c r="B321" t="s">
+        <v>207</v>
+      </c>
+      <c r="C321" t="s">
+        <v>215</v>
+      </c>
+      <c r="D321" t="s">
+        <v>216</v>
+      </c>
+      <c r="E321" t="s">
+        <v>32</v>
+      </c>
+      <c r="F321" t="s">
+        <v>33</v>
+      </c>
+      <c r="G321" t="s">
+        <v>640</v>
+      </c>
+      <c r="H321" t="s">
+        <v>641</v>
+      </c>
+      <c r="I321" t="s">
+        <v>642</v>
+      </c>
+      <c r="J321">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="K321" t="s">
+        <v>23</v>
+      </c>
+      <c r="L321" t="s">
+        <v>635</v>
+      </c>
+      <c r="M321" t="s">
+        <v>18</v>
+      </c>
+      <c r="N321" t="s">
+        <v>534</v>
+      </c>
+      <c r="O321" t="s">
+        <v>20</v>
+      </c>
+      <c r="P321" t="s">
+        <v>643</v>
+      </c>
+      <c r="Q321" t="s">
+        <v>644</v>
+      </c>
+      <c r="R321" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>206</v>
+      </c>
+      <c r="B322" t="s">
+        <v>207</v>
+      </c>
+      <c r="C322" t="s">
+        <v>215</v>
+      </c>
+      <c r="D322" t="s">
+        <v>216</v>
+      </c>
+      <c r="E322" t="s">
+        <v>32</v>
+      </c>
+      <c r="F322" t="s">
+        <v>33</v>
+      </c>
+      <c r="G322" t="s">
+        <v>645</v>
+      </c>
+      <c r="H322" t="s">
+        <v>34</v>
+      </c>
+      <c r="I322" t="s">
+        <v>35</v>
+      </c>
+      <c r="J322">
+        <v>33.93</v>
+      </c>
+      <c r="K322" t="s">
+        <v>50</v>
+      </c>
+      <c r="L322" t="s">
+        <v>635</v>
+      </c>
+      <c r="M322" t="s">
+        <v>18</v>
+      </c>
+      <c r="N322" t="s">
+        <v>534</v>
+      </c>
+      <c r="O322" t="s">
+        <v>20</v>
+      </c>
+      <c r="P322" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q322" t="s">
+        <v>646</v>
+      </c>
+      <c r="R322" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>206</v>
+      </c>
+      <c r="B323" t="s">
+        <v>207</v>
+      </c>
+      <c r="C323" t="s">
+        <v>215</v>
+      </c>
+      <c r="D323" t="s">
+        <v>216</v>
+      </c>
+      <c r="E323" t="s">
+        <v>32</v>
+      </c>
+      <c r="F323" t="s">
+        <v>33</v>
+      </c>
+      <c r="G323" t="s">
+        <v>645</v>
+      </c>
+      <c r="H323" t="s">
+        <v>34</v>
+      </c>
+      <c r="I323" t="s">
+        <v>35</v>
+      </c>
+      <c r="J323">
+        <v>33.93</v>
+      </c>
+      <c r="K323" t="s">
+        <v>50</v>
+      </c>
+      <c r="L323" t="s">
+        <v>635</v>
+      </c>
+      <c r="M323" t="s">
+        <v>18</v>
+      </c>
+      <c r="N323" t="s">
+        <v>534</v>
+      </c>
+      <c r="O323" t="s">
+        <v>20</v>
+      </c>
+      <c r="P323" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q323" t="s">
+        <v>646</v>
+      </c>
+      <c r="R323" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>206</v>
+      </c>
+      <c r="B324" t="s">
+        <v>207</v>
+      </c>
+      <c r="C324" t="s">
+        <v>215</v>
+      </c>
+      <c r="D324" t="s">
+        <v>216</v>
+      </c>
+      <c r="E324" t="s">
+        <v>32</v>
+      </c>
+      <c r="F324" t="s">
+        <v>33</v>
+      </c>
+      <c r="G324" t="s">
+        <v>632</v>
+      </c>
+      <c r="H324" t="s">
+        <v>76</v>
+      </c>
+      <c r="I324" t="s">
+        <v>77</v>
+      </c>
+      <c r="J324">
+        <v>30.04</v>
+      </c>
+      <c r="K324" t="s">
+        <v>22</v>
+      </c>
+      <c r="L324" t="s">
+        <v>635</v>
+      </c>
+      <c r="M324" t="s">
+        <v>18</v>
+      </c>
+      <c r="N324" t="s">
+        <v>534</v>
+      </c>
+      <c r="O324" t="s">
+        <v>20</v>
+      </c>
+      <c r="P324" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q324" t="s">
+        <v>546</v>
+      </c>
+      <c r="R324" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>206</v>
+      </c>
+      <c r="B325" t="s">
+        <v>207</v>
+      </c>
+      <c r="C325" t="s">
+        <v>215</v>
+      </c>
+      <c r="D325" t="s">
+        <v>216</v>
+      </c>
+      <c r="E325" t="s">
+        <v>32</v>
+      </c>
+      <c r="F325" t="s">
+        <v>33</v>
+      </c>
+      <c r="G325" t="s">
+        <v>647</v>
+      </c>
+      <c r="H325" t="s">
+        <v>148</v>
+      </c>
+      <c r="I325" t="s">
+        <v>149</v>
+      </c>
+      <c r="J325">
+        <v>64.8</v>
+      </c>
+      <c r="K325" t="s">
+        <v>329</v>
+      </c>
+      <c r="L325" t="s">
+        <v>635</v>
+      </c>
+      <c r="M325" t="s">
+        <v>18</v>
+      </c>
+      <c r="N325" t="s">
+        <v>534</v>
+      </c>
+      <c r="O325" t="s">
+        <v>20</v>
+      </c>
+      <c r="P325" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q325" t="s">
+        <v>648</v>
+      </c>
+      <c r="R325" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>206</v>
+      </c>
+      <c r="B326" t="s">
+        <v>207</v>
+      </c>
+      <c r="C326" t="s">
+        <v>215</v>
+      </c>
+      <c r="D326" t="s">
+        <v>216</v>
+      </c>
+      <c r="E326" t="s">
+        <v>32</v>
+      </c>
+      <c r="F326" t="s">
+        <v>33</v>
+      </c>
+      <c r="G326" t="s">
+        <v>632</v>
+      </c>
+      <c r="H326" t="s">
+        <v>73</v>
+      </c>
+      <c r="I326" t="s">
+        <v>74</v>
+      </c>
+      <c r="J326">
+        <v>50.94</v>
+      </c>
+      <c r="K326" t="s">
+        <v>50</v>
+      </c>
+      <c r="L326" t="s">
+        <v>635</v>
+      </c>
+      <c r="M326" t="s">
+        <v>18</v>
+      </c>
+      <c r="N326" t="s">
+        <v>534</v>
+      </c>
+      <c r="O326" t="s">
+        <v>20</v>
+      </c>
+      <c r="P326" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q326" t="s">
+        <v>649</v>
+      </c>
+      <c r="R326" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>206</v>
+      </c>
+      <c r="B327" t="s">
+        <v>207</v>
+      </c>
+      <c r="C327" t="s">
+        <v>215</v>
+      </c>
+      <c r="D327" t="s">
+        <v>216</v>
+      </c>
+      <c r="E327" t="s">
+        <v>32</v>
+      </c>
+      <c r="F327" t="s">
+        <v>33</v>
+      </c>
+      <c r="G327" t="s">
+        <v>650</v>
+      </c>
+      <c r="H327" t="s">
+        <v>168</v>
+      </c>
+      <c r="I327" t="s">
+        <v>169</v>
+      </c>
+      <c r="J327">
+        <v>18.739999999999998</v>
+      </c>
+      <c r="K327" t="s">
+        <v>23</v>
+      </c>
+      <c r="L327" t="s">
+        <v>635</v>
+      </c>
+      <c r="M327" t="s">
+        <v>18</v>
+      </c>
+      <c r="N327" t="s">
+        <v>534</v>
+      </c>
+      <c r="O327" t="s">
+        <v>20</v>
+      </c>
+      <c r="P327" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q327" t="s">
+        <v>651</v>
+      </c>
+      <c r="R327" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>206</v>
+      </c>
+      <c r="B328" t="s">
+        <v>207</v>
+      </c>
+      <c r="C328" t="s">
+        <v>215</v>
+      </c>
+      <c r="D328" t="s">
+        <v>216</v>
+      </c>
+      <c r="E328" t="s">
+        <v>32</v>
+      </c>
+      <c r="F328" t="s">
+        <v>33</v>
+      </c>
+      <c r="G328" t="s">
+        <v>640</v>
+      </c>
+      <c r="H328" t="s">
+        <v>652</v>
+      </c>
+      <c r="I328" t="s">
+        <v>653</v>
+      </c>
+      <c r="J328">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="K328" t="s">
+        <v>23</v>
+      </c>
+      <c r="L328" t="s">
+        <v>635</v>
+      </c>
+      <c r="M328" t="s">
+        <v>18</v>
+      </c>
+      <c r="N328" t="s">
+        <v>534</v>
+      </c>
+      <c r="O328" t="s">
+        <v>20</v>
+      </c>
+      <c r="P328" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q328" t="s">
+        <v>655</v>
+      </c>
+      <c r="R328" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>206</v>
+      </c>
+      <c r="B329" t="s">
+        <v>207</v>
+      </c>
+      <c r="C329" t="s">
+        <v>215</v>
+      </c>
+      <c r="D329" t="s">
+        <v>216</v>
+      </c>
+      <c r="E329" t="s">
+        <v>32</v>
+      </c>
+      <c r="F329" t="s">
+        <v>33</v>
+      </c>
+      <c r="G329" t="s">
+        <v>632</v>
+      </c>
+      <c r="H329" t="s">
+        <v>132</v>
+      </c>
+      <c r="I329" t="s">
+        <v>133</v>
+      </c>
+      <c r="J329">
+        <v>82</v>
+      </c>
+      <c r="K329" t="s">
+        <v>40</v>
+      </c>
+      <c r="L329" t="s">
+        <v>635</v>
+      </c>
+      <c r="M329" t="s">
+        <v>18</v>
+      </c>
+      <c r="N329" t="s">
+        <v>534</v>
+      </c>
+      <c r="O329" t="s">
+        <v>20</v>
+      </c>
+      <c r="P329" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q329" t="s">
+        <v>656</v>
+      </c>
+      <c r="R329" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>206</v>
+      </c>
+      <c r="B330" t="s">
+        <v>207</v>
+      </c>
+      <c r="C330" t="s">
+        <v>215</v>
+      </c>
+      <c r="D330" t="s">
+        <v>216</v>
+      </c>
+      <c r="E330" t="s">
+        <v>32</v>
+      </c>
+      <c r="F330" t="s">
+        <v>33</v>
+      </c>
+      <c r="G330" t="s">
+        <v>632</v>
+      </c>
+      <c r="H330" t="s">
+        <v>43</v>
+      </c>
+      <c r="I330" t="s">
+        <v>44</v>
+      </c>
+      <c r="J330">
+        <v>14</v>
+      </c>
+      <c r="K330" t="s">
+        <v>23</v>
+      </c>
+      <c r="L330" t="s">
+        <v>635</v>
+      </c>
+      <c r="M330" t="s">
+        <v>18</v>
+      </c>
+      <c r="N330" t="s">
+        <v>534</v>
+      </c>
+      <c r="O330" t="s">
+        <v>20</v>
+      </c>
+      <c r="P330" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q330" t="s">
+        <v>657</v>
+      </c>
+      <c r="R330" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>206</v>
+      </c>
+      <c r="B331" t="s">
+        <v>207</v>
+      </c>
+      <c r="C331" t="s">
+        <v>215</v>
+      </c>
+      <c r="D331" t="s">
+        <v>216</v>
+      </c>
+      <c r="E331" t="s">
+        <v>32</v>
+      </c>
+      <c r="F331" t="s">
+        <v>33</v>
+      </c>
+      <c r="G331" t="s">
+        <v>640</v>
+      </c>
+      <c r="H331" t="s">
+        <v>658</v>
+      </c>
+      <c r="I331" t="s">
+        <v>659</v>
+      </c>
+      <c r="J331">
+        <v>39.36</v>
+      </c>
+      <c r="K331" t="s">
+        <v>27</v>
+      </c>
+      <c r="L331" t="s">
+        <v>635</v>
+      </c>
+      <c r="M331" t="s">
+        <v>18</v>
+      </c>
+      <c r="N331" t="s">
+        <v>534</v>
+      </c>
+      <c r="O331" t="s">
+        <v>20</v>
+      </c>
+      <c r="P331" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q331" t="s">
+        <v>661</v>
+      </c>
+      <c r="R331" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>206</v>
+      </c>
+      <c r="B332" t="s">
+        <v>207</v>
+      </c>
+      <c r="C332" t="s">
+        <v>215</v>
+      </c>
+      <c r="D332" t="s">
+        <v>216</v>
+      </c>
+      <c r="E332" t="s">
+        <v>32</v>
+      </c>
+      <c r="F332" t="s">
+        <v>33</v>
+      </c>
+      <c r="G332" t="s">
+        <v>640</v>
+      </c>
+      <c r="H332" t="s">
+        <v>662</v>
+      </c>
+      <c r="I332" t="s">
+        <v>663</v>
+      </c>
+      <c r="J332">
+        <v>26.8</v>
+      </c>
+      <c r="K332" t="s">
+        <v>22</v>
+      </c>
+      <c r="L332" t="s">
+        <v>635</v>
+      </c>
+      <c r="M332" t="s">
+        <v>18</v>
+      </c>
+      <c r="N332" t="s">
+        <v>534</v>
+      </c>
+      <c r="O332" t="s">
+        <v>20</v>
+      </c>
+      <c r="P332" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q332" t="s">
+        <v>665</v>
+      </c>
+      <c r="R332" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>206</v>
+      </c>
+      <c r="B333" t="s">
+        <v>207</v>
+      </c>
+      <c r="C333" t="s">
+        <v>215</v>
+      </c>
+      <c r="D333" t="s">
+        <v>216</v>
+      </c>
+      <c r="E333" t="s">
+        <v>32</v>
+      </c>
+      <c r="F333" t="s">
+        <v>33</v>
+      </c>
+      <c r="G333" t="s">
+        <v>632</v>
+      </c>
+      <c r="H333" t="s">
+        <v>53</v>
+      </c>
+      <c r="I333" t="s">
+        <v>54</v>
+      </c>
+      <c r="J333">
+        <v>28.61</v>
+      </c>
+      <c r="K333" t="s">
+        <v>23</v>
+      </c>
+      <c r="L333" t="s">
+        <v>635</v>
+      </c>
+      <c r="M333" t="s">
+        <v>18</v>
+      </c>
+      <c r="N333" t="s">
+        <v>534</v>
+      </c>
+      <c r="O333" t="s">
+        <v>20</v>
+      </c>
+      <c r="P333" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q333" t="s">
+        <v>666</v>
+      </c>
+      <c r="R333" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>206</v>
+      </c>
+      <c r="B334" t="s">
+        <v>207</v>
+      </c>
+      <c r="C334" t="s">
+        <v>221</v>
+      </c>
+      <c r="D334" t="s">
+        <v>222</v>
+      </c>
+      <c r="E334" t="s">
+        <v>223</v>
+      </c>
+      <c r="F334" t="s">
+        <v>151</v>
+      </c>
+      <c r="G334" t="s">
+        <v>650</v>
+      </c>
+      <c r="H334" t="s">
+        <v>141</v>
+      </c>
+      <c r="I334" t="s">
+        <v>142</v>
+      </c>
+      <c r="J334">
+        <v>13.08</v>
+      </c>
+      <c r="K334" t="s">
+        <v>23</v>
+      </c>
+      <c r="L334" t="s">
+        <v>635</v>
+      </c>
+      <c r="M334" t="s">
+        <v>18</v>
+      </c>
+      <c r="N334" t="s">
+        <v>534</v>
+      </c>
+      <c r="O334" t="s">
+        <v>20</v>
+      </c>
+      <c r="P334" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q334" t="s">
+        <v>667</v>
+      </c>
+      <c r="R334" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>206</v>
+      </c>
+      <c r="B335" t="s">
+        <v>207</v>
+      </c>
+      <c r="C335" t="s">
+        <v>221</v>
+      </c>
+      <c r="D335" t="s">
+        <v>222</v>
+      </c>
+      <c r="E335" t="s">
+        <v>223</v>
+      </c>
+      <c r="F335" t="s">
+        <v>151</v>
+      </c>
+      <c r="G335" t="s">
+        <v>668</v>
+      </c>
+      <c r="H335" t="s">
+        <v>141</v>
+      </c>
+      <c r="I335" t="s">
+        <v>142</v>
+      </c>
+      <c r="J335">
+        <v>78.48</v>
+      </c>
+      <c r="K335" t="s">
+        <v>471</v>
+      </c>
+      <c r="L335" t="s">
+        <v>635</v>
+      </c>
+      <c r="M335" t="s">
+        <v>18</v>
+      </c>
+      <c r="N335" t="s">
+        <v>534</v>
+      </c>
+      <c r="O335" t="s">
+        <v>20</v>
+      </c>
+      <c r="P335" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q335" t="s">
+        <v>667</v>
+      </c>
+      <c r="R335" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>206</v>
+      </c>
+      <c r="B336" t="s">
+        <v>207</v>
+      </c>
+      <c r="C336" t="s">
+        <v>221</v>
+      </c>
+      <c r="D336" t="s">
+        <v>222</v>
+      </c>
+      <c r="E336" t="s">
+        <v>223</v>
+      </c>
+      <c r="F336" t="s">
+        <v>151</v>
+      </c>
+      <c r="G336" t="s">
+        <v>669</v>
+      </c>
+      <c r="H336" t="s">
+        <v>148</v>
+      </c>
+      <c r="I336" t="s">
+        <v>149</v>
+      </c>
+      <c r="J336">
+        <v>12.96</v>
+      </c>
+      <c r="K336" t="s">
+        <v>23</v>
+      </c>
+      <c r="L336" t="s">
+        <v>635</v>
+      </c>
+      <c r="M336" t="s">
+        <v>18</v>
+      </c>
+      <c r="N336" t="s">
+        <v>534</v>
+      </c>
+      <c r="O336" t="s">
+        <v>20</v>
+      </c>
+      <c r="P336" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q336" t="s">
+        <v>648</v>
+      </c>
+      <c r="R336" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>206</v>
+      </c>
+      <c r="B337" t="s">
+        <v>207</v>
+      </c>
+      <c r="C337" t="s">
+        <v>221</v>
+      </c>
+      <c r="D337" t="s">
+        <v>222</v>
+      </c>
+      <c r="E337" t="s">
+        <v>223</v>
+      </c>
+      <c r="F337" t="s">
+        <v>151</v>
+      </c>
+      <c r="G337" t="s">
+        <v>670</v>
+      </c>
+      <c r="H337" t="s">
+        <v>189</v>
+      </c>
+      <c r="I337" t="s">
+        <v>190</v>
+      </c>
+      <c r="J337">
+        <v>49.46</v>
+      </c>
+      <c r="K337" t="s">
+        <v>22</v>
+      </c>
+      <c r="L337" t="s">
+        <v>635</v>
+      </c>
+      <c r="M337" t="s">
+        <v>18</v>
+      </c>
+      <c r="N337" t="s">
+        <v>534</v>
+      </c>
+      <c r="O337" t="s">
+        <v>20</v>
+      </c>
+      <c r="P337" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q337" t="s">
+        <v>671</v>
+      </c>
+      <c r="R337" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>206</v>
+      </c>
+      <c r="B338" t="s">
+        <v>207</v>
+      </c>
+      <c r="C338" t="s">
+        <v>221</v>
+      </c>
+      <c r="D338" t="s">
+        <v>222</v>
+      </c>
+      <c r="E338" t="s">
+        <v>223</v>
+      </c>
+      <c r="F338" t="s">
+        <v>151</v>
+      </c>
+      <c r="G338" t="s">
+        <v>672</v>
+      </c>
+      <c r="H338" t="s">
+        <v>165</v>
+      </c>
+      <c r="I338" t="s">
+        <v>166</v>
+      </c>
+      <c r="J338">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="K338" t="s">
+        <v>23</v>
+      </c>
+      <c r="L338" t="s">
+        <v>635</v>
+      </c>
+      <c r="M338" t="s">
+        <v>18</v>
+      </c>
+      <c r="N338" t="s">
+        <v>534</v>
+      </c>
+      <c r="O338" t="s">
+        <v>20</v>
+      </c>
+      <c r="P338" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q338" t="s">
+        <v>232</v>
+      </c>
+      <c r="R338" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>206</v>
+      </c>
+      <c r="B339" t="s">
+        <v>207</v>
+      </c>
+      <c r="C339" t="s">
+        <v>221</v>
+      </c>
+      <c r="D339" t="s">
+        <v>222</v>
+      </c>
+      <c r="E339" t="s">
+        <v>223</v>
+      </c>
+      <c r="F339" t="s">
+        <v>151</v>
+      </c>
+      <c r="G339" t="s">
+        <v>673</v>
+      </c>
+      <c r="H339" t="s">
+        <v>560</v>
+      </c>
+      <c r="I339" t="s">
+        <v>561</v>
+      </c>
+      <c r="J339">
+        <v>13.7</v>
+      </c>
+      <c r="K339" t="s">
+        <v>23</v>
+      </c>
+      <c r="L339" t="s">
+        <v>635</v>
+      </c>
+      <c r="M339" t="s">
+        <v>18</v>
+      </c>
+      <c r="N339" t="s">
+        <v>534</v>
+      </c>
+      <c r="O339" t="s">
+        <v>20</v>
+      </c>
+      <c r="P339" t="s">
+        <v>562</v>
+      </c>
+      <c r="Q339" t="s">
+        <v>674</v>
+      </c>
+      <c r="R339" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>206</v>
+      </c>
+      <c r="B340" t="s">
+        <v>207</v>
+      </c>
+      <c r="C340" t="s">
+        <v>208</v>
+      </c>
+      <c r="D340" t="s">
+        <v>209</v>
+      </c>
+      <c r="E340" t="s">
+        <v>210</v>
+      </c>
+      <c r="F340" t="s">
+        <v>118</v>
+      </c>
+      <c r="G340" t="s">
+        <v>640</v>
+      </c>
+      <c r="H340" t="s">
+        <v>159</v>
+      </c>
+      <c r="I340" t="s">
+        <v>160</v>
+      </c>
+      <c r="J340">
+        <v>28.11</v>
+      </c>
+      <c r="K340" t="s">
+        <v>23</v>
+      </c>
+      <c r="L340" t="s">
+        <v>635</v>
+      </c>
+      <c r="M340" t="s">
+        <v>18</v>
+      </c>
+      <c r="N340" t="s">
+        <v>534</v>
+      </c>
+      <c r="O340" t="s">
+        <v>20</v>
+      </c>
+      <c r="P340" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q340" t="s">
+        <v>675</v>
+      </c>
+      <c r="R340" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>206</v>
+      </c>
+      <c r="B341" t="s">
+        <v>207</v>
+      </c>
+      <c r="C341" t="s">
+        <v>208</v>
+      </c>
+      <c r="D341" t="s">
+        <v>209</v>
+      </c>
+      <c r="E341" t="s">
+        <v>210</v>
+      </c>
+      <c r="F341" t="s">
+        <v>118</v>
+      </c>
+      <c r="G341" t="s">
+        <v>672</v>
+      </c>
+      <c r="H341" t="s">
+        <v>245</v>
+      </c>
+      <c r="I341" t="s">
+        <v>246</v>
+      </c>
+      <c r="J341">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="K341" t="s">
+        <v>23</v>
+      </c>
+      <c r="L341" t="s">
+        <v>635</v>
+      </c>
+      <c r="M341" t="s">
+        <v>18</v>
+      </c>
+      <c r="N341" t="s">
+        <v>534</v>
+      </c>
+      <c r="O341" t="s">
+        <v>20</v>
+      </c>
+      <c r="P341" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q341" t="s">
+        <v>676</v>
+      </c>
+      <c r="R341" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>206</v>
+      </c>
+      <c r="B342" t="s">
+        <v>207</v>
+      </c>
+      <c r="C342" t="s">
+        <v>208</v>
+      </c>
+      <c r="D342" t="s">
+        <v>209</v>
+      </c>
+      <c r="E342" t="s">
+        <v>210</v>
+      </c>
+      <c r="F342" t="s">
+        <v>118</v>
+      </c>
+      <c r="G342" t="s">
+        <v>677</v>
+      </c>
+      <c r="H342" t="s">
+        <v>420</v>
+      </c>
+      <c r="I342" t="s">
+        <v>421</v>
+      </c>
+      <c r="J342">
+        <v>26.34</v>
+      </c>
+      <c r="K342" t="s">
+        <v>22</v>
+      </c>
+      <c r="L342" t="s">
+        <v>635</v>
+      </c>
+      <c r="M342" t="s">
+        <v>18</v>
+      </c>
+      <c r="N342" t="s">
+        <v>534</v>
+      </c>
+      <c r="O342" t="s">
+        <v>20</v>
+      </c>
+      <c r="P342" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q342" t="s">
+        <v>423</v>
+      </c>
+      <c r="R342" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>206</v>
+      </c>
+      <c r="B343" t="s">
+        <v>207</v>
+      </c>
+      <c r="C343" t="s">
+        <v>208</v>
+      </c>
+      <c r="D343" t="s">
+        <v>209</v>
+      </c>
+      <c r="E343" t="s">
+        <v>210</v>
+      </c>
+      <c r="F343" t="s">
+        <v>118</v>
+      </c>
+      <c r="G343" t="s">
+        <v>632</v>
+      </c>
+      <c r="H343" t="s">
+        <v>85</v>
+      </c>
+      <c r="I343" t="s">
+        <v>86</v>
+      </c>
+      <c r="J343">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="K343" t="s">
+        <v>23</v>
+      </c>
+      <c r="L343" t="s">
+        <v>635</v>
+      </c>
+      <c r="M343" t="s">
+        <v>18</v>
+      </c>
+      <c r="N343" t="s">
+        <v>534</v>
+      </c>
+      <c r="O343" t="s">
+        <v>20</v>
+      </c>
+      <c r="P343" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q343" t="s">
+        <v>678</v>
+      </c>
+      <c r="R343" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>206</v>
+      </c>
+      <c r="B344" t="s">
+        <v>207</v>
+      </c>
+      <c r="C344" t="s">
+        <v>208</v>
+      </c>
+      <c r="D344" t="s">
+        <v>209</v>
+      </c>
+      <c r="E344" t="s">
+        <v>210</v>
+      </c>
+      <c r="F344" t="s">
+        <v>118</v>
+      </c>
+      <c r="G344" t="s">
+        <v>679</v>
+      </c>
+      <c r="H344" t="s">
+        <v>132</v>
+      </c>
+      <c r="I344" t="s">
+        <v>133</v>
+      </c>
+      <c r="J344">
+        <v>82</v>
+      </c>
+      <c r="K344" t="s">
+        <v>40</v>
+      </c>
+      <c r="L344" t="s">
+        <v>635</v>
+      </c>
+      <c r="M344" t="s">
+        <v>18</v>
+      </c>
+      <c r="N344" t="s">
+        <v>534</v>
+      </c>
+      <c r="O344" t="s">
+        <v>20</v>
+      </c>
+      <c r="P344" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q344" t="s">
+        <v>656</v>
+      </c>
+      <c r="R344" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>206</v>
+      </c>
+      <c r="B345" t="s">
+        <v>207</v>
+      </c>
+      <c r="C345" t="s">
+        <v>208</v>
+      </c>
+      <c r="D345" t="s">
+        <v>209</v>
+      </c>
+      <c r="E345" t="s">
+        <v>210</v>
+      </c>
+      <c r="F345" t="s">
+        <v>118</v>
+      </c>
+      <c r="G345" t="s">
+        <v>640</v>
+      </c>
+      <c r="H345" t="s">
+        <v>38</v>
+      </c>
+      <c r="I345" t="s">
+        <v>39</v>
+      </c>
+      <c r="J345">
+        <v>19.48</v>
+      </c>
+      <c r="K345" t="s">
+        <v>23</v>
+      </c>
+      <c r="L345" t="s">
+        <v>635</v>
+      </c>
+      <c r="M345" t="s">
+        <v>18</v>
+      </c>
+      <c r="N345" t="s">
+        <v>534</v>
+      </c>
+      <c r="O345" t="s">
+        <v>20</v>
+      </c>
+      <c r="P345" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q345" t="s">
+        <v>680</v>
+      </c>
+      <c r="R345" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>206</v>
+      </c>
+      <c r="B346" t="s">
+        <v>207</v>
+      </c>
+      <c r="C346" t="s">
+        <v>208</v>
+      </c>
+      <c r="D346" t="s">
+        <v>209</v>
+      </c>
+      <c r="E346" t="s">
+        <v>210</v>
+      </c>
+      <c r="F346" t="s">
+        <v>118</v>
+      </c>
+      <c r="G346" t="s">
+        <v>670</v>
+      </c>
+      <c r="H346" t="s">
+        <v>38</v>
+      </c>
+      <c r="I346" t="s">
+        <v>39</v>
+      </c>
+      <c r="J346">
+        <v>19.48</v>
+      </c>
+      <c r="K346" t="s">
+        <v>23</v>
+      </c>
+      <c r="L346" t="s">
+        <v>635</v>
+      </c>
+      <c r="M346" t="s">
+        <v>18</v>
+      </c>
+      <c r="N346" t="s">
+        <v>534</v>
+      </c>
+      <c r="O346" t="s">
+        <v>20</v>
+      </c>
+      <c r="P346" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q346" t="s">
+        <v>680</v>
+      </c>
+      <c r="R346" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="347" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>206</v>
+      </c>
+      <c r="B347" t="s">
+        <v>207</v>
+      </c>
+      <c r="C347" t="s">
+        <v>208</v>
+      </c>
+      <c r="D347" t="s">
+        <v>209</v>
+      </c>
+      <c r="E347" t="s">
+        <v>210</v>
+      </c>
+      <c r="F347" t="s">
+        <v>118</v>
+      </c>
+      <c r="G347" t="s">
+        <v>673</v>
+      </c>
+      <c r="H347" t="s">
+        <v>681</v>
+      </c>
+      <c r="I347" t="s">
+        <v>682</v>
+      </c>
+      <c r="J347">
+        <v>9.7200000000000006</v>
+      </c>
+      <c r="K347" t="s">
+        <v>23</v>
+      </c>
+      <c r="L347" t="s">
+        <v>635</v>
+      </c>
+      <c r="M347" t="s">
+        <v>18</v>
+      </c>
+      <c r="N347" t="s">
+        <v>534</v>
+      </c>
+      <c r="O347" t="s">
+        <v>20</v>
+      </c>
+      <c r="P347" t="s">
+        <v>683</v>
+      </c>
+      <c r="Q347" t="s">
+        <v>676</v>
+      </c>
+      <c r="R347" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="348" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>206</v>
+      </c>
+      <c r="B348" t="s">
+        <v>207</v>
+      </c>
+      <c r="C348" t="s">
+        <v>208</v>
+      </c>
+      <c r="D348" t="s">
+        <v>209</v>
+      </c>
+      <c r="E348" t="s">
+        <v>210</v>
+      </c>
+      <c r="F348" t="s">
+        <v>118</v>
+      </c>
+      <c r="G348" t="s">
+        <v>640</v>
+      </c>
+      <c r="H348" t="s">
+        <v>192</v>
+      </c>
+      <c r="I348" t="s">
+        <v>193</v>
+      </c>
+      <c r="J348">
+        <v>57.77</v>
+      </c>
+      <c r="K348" t="s">
+        <v>23</v>
+      </c>
+      <c r="L348" t="s">
+        <v>635</v>
+      </c>
+      <c r="M348" t="s">
+        <v>18</v>
+      </c>
+      <c r="N348" t="s">
+        <v>534</v>
+      </c>
+      <c r="O348" t="s">
+        <v>20</v>
+      </c>
+      <c r="P348" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q348" t="s">
+        <v>684</v>
+      </c>
+      <c r="R348" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>206</v>
+      </c>
+      <c r="B349" t="s">
+        <v>207</v>
+      </c>
+      <c r="C349" t="s">
+        <v>208</v>
+      </c>
+      <c r="D349" t="s">
+        <v>209</v>
+      </c>
+      <c r="E349" t="s">
+        <v>210</v>
+      </c>
+      <c r="F349" t="s">
+        <v>118</v>
+      </c>
+      <c r="G349" t="s">
+        <v>685</v>
+      </c>
+      <c r="H349" t="s">
+        <v>53</v>
+      </c>
+      <c r="I349" t="s">
+        <v>54</v>
+      </c>
+      <c r="J349">
+        <v>28.61</v>
+      </c>
+      <c r="K349" t="s">
+        <v>23</v>
+      </c>
+      <c r="L349" t="s">
+        <v>635</v>
+      </c>
+      <c r="M349" t="s">
+        <v>18</v>
+      </c>
+      <c r="N349" t="s">
+        <v>534</v>
+      </c>
+      <c r="O349" t="s">
+        <v>20</v>
+      </c>
+      <c r="P349" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q349" t="s">
+        <v>666</v>
+      </c>
+      <c r="R349" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="350" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>206</v>
+      </c>
+      <c r="B350" t="s">
+        <v>207</v>
+      </c>
+      <c r="C350" t="s">
+        <v>251</v>
+      </c>
+      <c r="D350" t="s">
+        <v>252</v>
+      </c>
+      <c r="E350" t="s">
+        <v>198</v>
+      </c>
+      <c r="F350" t="s">
+        <v>119</v>
+      </c>
+      <c r="G350" t="s">
+        <v>672</v>
+      </c>
+      <c r="H350" t="s">
+        <v>159</v>
+      </c>
+      <c r="I350" t="s">
+        <v>160</v>
+      </c>
+      <c r="J350">
+        <v>28.11</v>
+      </c>
+      <c r="K350" t="s">
+        <v>23</v>
+      </c>
+      <c r="L350" t="s">
+        <v>635</v>
+      </c>
+      <c r="M350" t="s">
+        <v>18</v>
+      </c>
+      <c r="N350" t="s">
+        <v>534</v>
+      </c>
+      <c r="O350" t="s">
+        <v>20</v>
+      </c>
+      <c r="P350" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q350" t="s">
+        <v>675</v>
+      </c>
+      <c r="R350" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="351" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>206</v>
+      </c>
+      <c r="B351" t="s">
+        <v>207</v>
+      </c>
+      <c r="C351" t="s">
+        <v>251</v>
+      </c>
+      <c r="D351" t="s">
+        <v>252</v>
+      </c>
+      <c r="E351" t="s">
+        <v>198</v>
+      </c>
+      <c r="F351" t="s">
+        <v>119</v>
+      </c>
+      <c r="G351" t="s">
+        <v>672</v>
+      </c>
+      <c r="H351" t="s">
+        <v>138</v>
+      </c>
+      <c r="I351" t="s">
+        <v>139</v>
+      </c>
+      <c r="J351">
+        <v>27.95</v>
+      </c>
+      <c r="K351" t="s">
+        <v>23</v>
+      </c>
+      <c r="L351" t="s">
+        <v>635</v>
+      </c>
+      <c r="M351" t="s">
+        <v>18</v>
+      </c>
+      <c r="N351" t="s">
+        <v>534</v>
+      </c>
+      <c r="O351" t="s">
+        <v>20</v>
+      </c>
+      <c r="P351" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q351" t="s">
+        <v>686</v>
+      </c>
+      <c r="R351" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="352" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>206</v>
+      </c>
+      <c r="B352" t="s">
+        <v>207</v>
+      </c>
+      <c r="C352" t="s">
+        <v>251</v>
+      </c>
+      <c r="D352" t="s">
+        <v>252</v>
+      </c>
+      <c r="E352" t="s">
+        <v>198</v>
+      </c>
+      <c r="F352" t="s">
+        <v>119</v>
+      </c>
+      <c r="G352" t="s">
+        <v>672</v>
+      </c>
+      <c r="H352" t="s">
+        <v>687</v>
+      </c>
+      <c r="I352" t="s">
+        <v>688</v>
+      </c>
+      <c r="J352">
+        <v>30.4</v>
+      </c>
+      <c r="K352" t="s">
+        <v>23</v>
+      </c>
+      <c r="L352" t="s">
+        <v>635</v>
+      </c>
+      <c r="M352" t="s">
+        <v>18</v>
+      </c>
+      <c r="N352" t="s">
+        <v>534</v>
+      </c>
+      <c r="O352" t="s">
+        <v>20</v>
+      </c>
+      <c r="P352" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q352" t="s">
+        <v>282</v>
+      </c>
+      <c r="R352" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>206</v>
+      </c>
+      <c r="B353" t="s">
+        <v>207</v>
+      </c>
+      <c r="C353" t="s">
+        <v>251</v>
+      </c>
+      <c r="D353" t="s">
+        <v>252</v>
+      </c>
+      <c r="E353" t="s">
+        <v>198</v>
+      </c>
+      <c r="F353" t="s">
+        <v>119</v>
+      </c>
+      <c r="G353" t="s">
+        <v>690</v>
+      </c>
+      <c r="H353" t="s">
+        <v>57</v>
+      </c>
+      <c r="I353" t="s">
+        <v>58</v>
+      </c>
+      <c r="J353">
+        <v>31.51</v>
+      </c>
+      <c r="K353" t="s">
+        <v>23</v>
+      </c>
+      <c r="L353" t="s">
+        <v>635</v>
+      </c>
+      <c r="M353" t="s">
+        <v>18</v>
+      </c>
+      <c r="N353" t="s">
+        <v>534</v>
+      </c>
+      <c r="O353" t="s">
+        <v>20</v>
+      </c>
+      <c r="P353" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q353" t="s">
+        <v>691</v>
+      </c>
+      <c r="R353" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>206</v>
+      </c>
+      <c r="B354" t="s">
+        <v>207</v>
+      </c>
+      <c r="C354" t="s">
+        <v>251</v>
+      </c>
+      <c r="D354" t="s">
+        <v>252</v>
+      </c>
+      <c r="E354" t="s">
+        <v>198</v>
+      </c>
+      <c r="F354" t="s">
+        <v>119</v>
+      </c>
+      <c r="G354" t="s">
+        <v>677</v>
+      </c>
+      <c r="H354" t="s">
+        <v>73</v>
+      </c>
+      <c r="I354" t="s">
+        <v>74</v>
+      </c>
+      <c r="J354">
+        <v>67.92</v>
+      </c>
+      <c r="K354" t="s">
+        <v>40</v>
+      </c>
+      <c r="L354" t="s">
+        <v>635</v>
+      </c>
+      <c r="M354" t="s">
+        <v>18</v>
+      </c>
+      <c r="N354" t="s">
+        <v>534</v>
+      </c>
+      <c r="O354" t="s">
+        <v>20</v>
+      </c>
+      <c r="P354" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q354" t="s">
+        <v>649</v>
+      </c>
+      <c r="R354" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>206</v>
+      </c>
+      <c r="B355" t="s">
+        <v>207</v>
+      </c>
+      <c r="C355" t="s">
+        <v>251</v>
+      </c>
+      <c r="D355" t="s">
+        <v>252</v>
+      </c>
+      <c r="E355" t="s">
+        <v>198</v>
+      </c>
+      <c r="F355" t="s">
+        <v>119</v>
+      </c>
+      <c r="G355" t="s">
+        <v>673</v>
+      </c>
+      <c r="H355" t="s">
+        <v>433</v>
+      </c>
+      <c r="I355" t="s">
+        <v>434</v>
+      </c>
+      <c r="J355">
+        <v>15.21</v>
+      </c>
+      <c r="K355" t="s">
+        <v>23</v>
+      </c>
+      <c r="L355" t="s">
+        <v>635</v>
+      </c>
+      <c r="M355" t="s">
+        <v>18</v>
+      </c>
+      <c r="N355" t="s">
+        <v>534</v>
+      </c>
+      <c r="O355" t="s">
+        <v>20</v>
+      </c>
+      <c r="P355" t="s">
+        <v>435</v>
+      </c>
+      <c r="Q355" t="s">
+        <v>692</v>
+      </c>
+      <c r="R355" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>206</v>
+      </c>
+      <c r="B356" t="s">
+        <v>207</v>
+      </c>
+      <c r="C356" t="s">
+        <v>251</v>
+      </c>
+      <c r="D356" t="s">
+        <v>252</v>
+      </c>
+      <c r="E356" t="s">
+        <v>198</v>
+      </c>
+      <c r="F356" t="s">
+        <v>119</v>
+      </c>
+      <c r="G356" t="s">
+        <v>645</v>
+      </c>
+      <c r="H356" t="s">
+        <v>613</v>
+      </c>
+      <c r="I356" t="s">
+        <v>614</v>
+      </c>
+      <c r="J356">
+        <v>8.9</v>
+      </c>
+      <c r="K356" t="s">
+        <v>23</v>
+      </c>
+      <c r="L356" t="s">
+        <v>635</v>
+      </c>
+      <c r="M356" t="s">
+        <v>18</v>
+      </c>
+      <c r="N356" t="s">
+        <v>534</v>
+      </c>
+      <c r="O356" t="s">
+        <v>20</v>
+      </c>
+      <c r="P356" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q356" t="s">
+        <v>693</v>
+      </c>
+      <c r="R356" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>206</v>
+      </c>
+      <c r="B357" t="s">
+        <v>207</v>
+      </c>
+      <c r="C357" t="s">
+        <v>251</v>
+      </c>
+      <c r="D357" t="s">
+        <v>252</v>
+      </c>
+      <c r="E357" t="s">
+        <v>198</v>
+      </c>
+      <c r="F357" t="s">
+        <v>119</v>
+      </c>
+      <c r="G357" t="s">
+        <v>677</v>
+      </c>
+      <c r="H357" t="s">
+        <v>613</v>
+      </c>
+      <c r="I357" t="s">
+        <v>614</v>
+      </c>
+      <c r="J357">
+        <v>8.9</v>
+      </c>
+      <c r="K357" t="s">
+        <v>23</v>
+      </c>
+      <c r="L357" t="s">
+        <v>635</v>
+      </c>
+      <c r="M357" t="s">
+        <v>18</v>
+      </c>
+      <c r="N357" t="s">
+        <v>534</v>
+      </c>
+      <c r="O357" t="s">
+        <v>20</v>
+      </c>
+      <c r="P357" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q357" t="s">
+        <v>693</v>
+      </c>
+      <c r="R357" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="358" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>206</v>
+      </c>
+      <c r="B358" t="s">
+        <v>207</v>
+      </c>
+      <c r="C358" t="s">
+        <v>251</v>
+      </c>
+      <c r="D358" t="s">
+        <v>252</v>
+      </c>
+      <c r="E358" t="s">
+        <v>198</v>
+      </c>
+      <c r="F358" t="s">
+        <v>119</v>
+      </c>
+      <c r="G358" t="s">
+        <v>672</v>
+      </c>
+      <c r="H358" t="s">
+        <v>626</v>
+      </c>
+      <c r="I358" t="s">
+        <v>627</v>
+      </c>
+      <c r="J358">
+        <v>27.91</v>
+      </c>
+      <c r="K358" t="s">
+        <v>23</v>
+      </c>
+      <c r="L358" t="s">
+        <v>635</v>
+      </c>
+      <c r="M358" t="s">
+        <v>18</v>
+      </c>
+      <c r="N358" t="s">
+        <v>534</v>
+      </c>
+      <c r="O358" t="s">
+        <v>20</v>
+      </c>
+      <c r="P358" t="s">
+        <v>628</v>
+      </c>
+      <c r="Q358" t="s">
+        <v>694</v>
+      </c>
+      <c r="R358" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="359" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>206</v>
+      </c>
+      <c r="B359" t="s">
+        <v>207</v>
+      </c>
+      <c r="C359" t="s">
+        <v>251</v>
+      </c>
+      <c r="D359" t="s">
+        <v>252</v>
+      </c>
+      <c r="E359" t="s">
+        <v>198</v>
+      </c>
+      <c r="F359" t="s">
+        <v>119</v>
+      </c>
+      <c r="G359" t="s">
+        <v>632</v>
+      </c>
+      <c r="H359" t="s">
+        <v>145</v>
+      </c>
+      <c r="I359" t="s">
+        <v>146</v>
+      </c>
+      <c r="J359">
+        <v>21.32</v>
+      </c>
+      <c r="K359" t="s">
+        <v>23</v>
+      </c>
+      <c r="L359" t="s">
+        <v>635</v>
+      </c>
+      <c r="M359" t="s">
+        <v>18</v>
+      </c>
+      <c r="N359" t="s">
+        <v>534</v>
+      </c>
+      <c r="O359" t="s">
+        <v>20</v>
+      </c>
+      <c r="P359" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q359" t="s">
+        <v>695</v>
+      </c>
+      <c r="R359" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>206</v>
+      </c>
+      <c r="B360" t="s">
+        <v>207</v>
+      </c>
+      <c r="C360" t="s">
+        <v>251</v>
+      </c>
+      <c r="D360" t="s">
+        <v>252</v>
+      </c>
+      <c r="E360" t="s">
+        <v>198</v>
+      </c>
+      <c r="F360" t="s">
+        <v>119</v>
+      </c>
+      <c r="G360" t="s">
+        <v>632</v>
+      </c>
+      <c r="H360" t="s">
+        <v>43</v>
+      </c>
+      <c r="I360" t="s">
+        <v>44</v>
+      </c>
+      <c r="J360">
+        <v>14</v>
+      </c>
+      <c r="K360" t="s">
+        <v>23</v>
+      </c>
+      <c r="L360" t="s">
+        <v>635</v>
+      </c>
+      <c r="M360" t="s">
+        <v>18</v>
+      </c>
+      <c r="N360" t="s">
+        <v>534</v>
+      </c>
+      <c r="O360" t="s">
+        <v>20</v>
+      </c>
+      <c r="P360" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q360" t="s">
+        <v>657</v>
+      </c>
+      <c r="R360" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="361" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>206</v>
+      </c>
+      <c r="B361" t="s">
+        <v>207</v>
+      </c>
+      <c r="C361" t="s">
+        <v>251</v>
+      </c>
+      <c r="D361" t="s">
+        <v>252</v>
+      </c>
+      <c r="E361" t="s">
+        <v>198</v>
+      </c>
+      <c r="F361" t="s">
+        <v>119</v>
+      </c>
+      <c r="G361" t="s">
+        <v>677</v>
+      </c>
+      <c r="H361" t="s">
+        <v>43</v>
+      </c>
+      <c r="I361" t="s">
+        <v>44</v>
+      </c>
+      <c r="J361">
+        <v>14</v>
+      </c>
+      <c r="K361" t="s">
+        <v>23</v>
+      </c>
+      <c r="L361" t="s">
+        <v>635</v>
+      </c>
+      <c r="M361" t="s">
+        <v>18</v>
+      </c>
+      <c r="N361" t="s">
+        <v>534</v>
+      </c>
+      <c r="O361" t="s">
+        <v>20</v>
+      </c>
+      <c r="P361" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q361" t="s">
+        <v>657</v>
+      </c>
+      <c r="R361" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="362" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>206</v>
+      </c>
+      <c r="B362" t="s">
+        <v>207</v>
+      </c>
+      <c r="C362" t="s">
+        <v>212</v>
+      </c>
+      <c r="D362" t="s">
+        <v>213</v>
+      </c>
+      <c r="E362" t="s">
+        <v>214</v>
+      </c>
+      <c r="F362" t="s">
+        <v>70</v>
+      </c>
+      <c r="G362" t="s">
+        <v>672</v>
+      </c>
+      <c r="H362" t="s">
+        <v>112</v>
+      </c>
+      <c r="I362" t="s">
+        <v>113</v>
+      </c>
+      <c r="J362">
+        <v>28.16</v>
+      </c>
+      <c r="K362" t="s">
+        <v>23</v>
+      </c>
+      <c r="L362" t="s">
+        <v>635</v>
+      </c>
+      <c r="M362" t="s">
+        <v>18</v>
+      </c>
+      <c r="N362" t="s">
+        <v>534</v>
+      </c>
+      <c r="O362" t="s">
+        <v>20</v>
+      </c>
+      <c r="P362" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q362" t="s">
+        <v>696</v>
+      </c>
+      <c r="R362" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="363" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>206</v>
+      </c>
+      <c r="B363" t="s">
+        <v>207</v>
+      </c>
+      <c r="C363" t="s">
+        <v>212</v>
+      </c>
+      <c r="D363" t="s">
+        <v>213</v>
+      </c>
+      <c r="E363" t="s">
+        <v>214</v>
+      </c>
+      <c r="F363" t="s">
+        <v>70</v>
+      </c>
+      <c r="G363" t="s">
+        <v>672</v>
+      </c>
+      <c r="H363" t="s">
+        <v>123</v>
+      </c>
+      <c r="I363" t="s">
+        <v>124</v>
+      </c>
+      <c r="J363">
+        <v>28.07</v>
+      </c>
+      <c r="K363" t="s">
+        <v>23</v>
+      </c>
+      <c r="L363" t="s">
+        <v>635</v>
+      </c>
+      <c r="M363" t="s">
+        <v>18</v>
+      </c>
+      <c r="N363" t="s">
+        <v>534</v>
+      </c>
+      <c r="O363" t="s">
+        <v>20</v>
+      </c>
+      <c r="P363" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q363" t="s">
+        <v>307</v>
+      </c>
+      <c r="R363" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="364" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>206</v>
+      </c>
+      <c r="B364" t="s">
+        <v>207</v>
+      </c>
+      <c r="C364" t="s">
+        <v>212</v>
+      </c>
+      <c r="D364" t="s">
+        <v>213</v>
+      </c>
+      <c r="E364" t="s">
+        <v>214</v>
+      </c>
+      <c r="F364" t="s">
+        <v>70</v>
+      </c>
+      <c r="G364" t="s">
+        <v>672</v>
+      </c>
+      <c r="H364" t="s">
+        <v>687</v>
+      </c>
+      <c r="I364" t="s">
+        <v>688</v>
+      </c>
+      <c r="J364">
+        <v>30.4</v>
+      </c>
+      <c r="K364" t="s">
+        <v>23</v>
+      </c>
+      <c r="L364" t="s">
+        <v>635</v>
+      </c>
+      <c r="M364" t="s">
+        <v>18</v>
+      </c>
+      <c r="N364" t="s">
+        <v>534</v>
+      </c>
+      <c r="O364" t="s">
+        <v>20</v>
+      </c>
+      <c r="P364" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q364" t="s">
+        <v>282</v>
+      </c>
+      <c r="R364" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="365" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>206</v>
+      </c>
+      <c r="B365" t="s">
+        <v>207</v>
+      </c>
+      <c r="C365" t="s">
+        <v>212</v>
+      </c>
+      <c r="D365" t="s">
+        <v>213</v>
+      </c>
+      <c r="E365" t="s">
+        <v>214</v>
+      </c>
+      <c r="F365" t="s">
+        <v>70</v>
+      </c>
+      <c r="G365" t="s">
+        <v>672</v>
+      </c>
+      <c r="H365" t="s">
+        <v>88</v>
+      </c>
+      <c r="I365" t="s">
+        <v>89</v>
+      </c>
+      <c r="J365">
+        <v>23.52</v>
+      </c>
+      <c r="K365" t="s">
+        <v>23</v>
+      </c>
+      <c r="L365" t="s">
+        <v>635</v>
+      </c>
+      <c r="M365" t="s">
+        <v>18</v>
+      </c>
+      <c r="N365" t="s">
+        <v>534</v>
+      </c>
+      <c r="O365" t="s">
+        <v>20</v>
+      </c>
+      <c r="P365" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q365" t="s">
+        <v>697</v>
+      </c>
+      <c r="R365" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="366" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>206</v>
+      </c>
+      <c r="B366" t="s">
+        <v>207</v>
+      </c>
+      <c r="C366" t="s">
+        <v>212</v>
+      </c>
+      <c r="D366" t="s">
+        <v>213</v>
+      </c>
+      <c r="E366" t="s">
+        <v>214</v>
+      </c>
+      <c r="F366" t="s">
+        <v>70</v>
+      </c>
+      <c r="G366" t="s">
+        <v>672</v>
+      </c>
+      <c r="H366" t="s">
+        <v>79</v>
+      </c>
+      <c r="I366" t="s">
+        <v>80</v>
+      </c>
+      <c r="J366">
+        <v>21.48</v>
+      </c>
+      <c r="K366" t="s">
+        <v>23</v>
+      </c>
+      <c r="L366" t="s">
+        <v>635</v>
+      </c>
+      <c r="M366" t="s">
+        <v>18</v>
+      </c>
+      <c r="N366" t="s">
+        <v>534</v>
+      </c>
+      <c r="O366" t="s">
+        <v>20</v>
+      </c>
+      <c r="P366" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q366" t="s">
+        <v>698</v>
+      </c>
+      <c r="R366" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="367" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>206</v>
+      </c>
+      <c r="B367" t="s">
+        <v>207</v>
+      </c>
+      <c r="C367" t="s">
+        <v>212</v>
+      </c>
+      <c r="D367" t="s">
+        <v>213</v>
+      </c>
+      <c r="E367" t="s">
+        <v>214</v>
+      </c>
+      <c r="F367" t="s">
+        <v>70</v>
+      </c>
+      <c r="G367" t="s">
+        <v>672</v>
+      </c>
+      <c r="H367" t="s">
+        <v>195</v>
+      </c>
+      <c r="I367" t="s">
+        <v>196</v>
+      </c>
+      <c r="J367">
+        <v>26.93</v>
+      </c>
+      <c r="K367" t="s">
+        <v>23</v>
+      </c>
+      <c r="L367" t="s">
+        <v>635</v>
+      </c>
+      <c r="M367" t="s">
+        <v>18</v>
+      </c>
+      <c r="N367" t="s">
+        <v>534</v>
+      </c>
+      <c r="O367" t="s">
+        <v>20</v>
+      </c>
+      <c r="P367" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q367" t="s">
+        <v>699</v>
+      </c>
+      <c r="R367" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="368" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>206</v>
+      </c>
+      <c r="B368" t="s">
+        <v>207</v>
+      </c>
+      <c r="C368" t="s">
+        <v>212</v>
+      </c>
+      <c r="D368" t="s">
+        <v>213</v>
+      </c>
+      <c r="E368" t="s">
+        <v>214</v>
+      </c>
+      <c r="F368" t="s">
+        <v>70</v>
+      </c>
+      <c r="G368" t="s">
+        <v>672</v>
+      </c>
+      <c r="H368" t="s">
+        <v>28</v>
+      </c>
+      <c r="I368" t="s">
+        <v>29</v>
+      </c>
+      <c r="J368">
+        <v>22.09</v>
+      </c>
+      <c r="K368" t="s">
+        <v>23</v>
+      </c>
+      <c r="L368" t="s">
+        <v>635</v>
+      </c>
+      <c r="M368" t="s">
+        <v>18</v>
+      </c>
+      <c r="N368" t="s">
+        <v>534</v>
+      </c>
+      <c r="O368" t="s">
+        <v>20</v>
+      </c>
+      <c r="P368" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q368" t="s">
+        <v>700</v>
+      </c>
+      <c r="R368" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="369" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>206</v>
+      </c>
+      <c r="B369" t="s">
+        <v>207</v>
+      </c>
+      <c r="C369" t="s">
+        <v>212</v>
+      </c>
+      <c r="D369" t="s">
+        <v>213</v>
+      </c>
+      <c r="E369" t="s">
+        <v>214</v>
+      </c>
+      <c r="F369" t="s">
+        <v>70</v>
+      </c>
+      <c r="G369" t="s">
+        <v>672</v>
+      </c>
+      <c r="H369" t="s">
+        <v>64</v>
+      </c>
+      <c r="I369" t="s">
+        <v>65</v>
+      </c>
+      <c r="J369">
+        <v>22.06</v>
+      </c>
+      <c r="K369" t="s">
+        <v>23</v>
+      </c>
+      <c r="L369" t="s">
+        <v>635</v>
+      </c>
+      <c r="M369" t="s">
+        <v>18</v>
+      </c>
+      <c r="N369" t="s">
+        <v>534</v>
+      </c>
+      <c r="O369" t="s">
+        <v>20</v>
+      </c>
+      <c r="P369" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q369" t="s">
+        <v>701</v>
+      </c>
+      <c r="R369" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="370" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>206</v>
+      </c>
+      <c r="B370" t="s">
+        <v>207</v>
+      </c>
+      <c r="C370" t="s">
+        <v>212</v>
+      </c>
+      <c r="D370" t="s">
+        <v>213</v>
+      </c>
+      <c r="E370" t="s">
+        <v>214</v>
+      </c>
+      <c r="F370" t="s">
+        <v>70</v>
+      </c>
+      <c r="G370" t="s">
+        <v>672</v>
+      </c>
+      <c r="H370" t="s">
+        <v>120</v>
+      </c>
+      <c r="I370" t="s">
+        <v>121</v>
+      </c>
+      <c r="J370">
+        <v>27.87</v>
+      </c>
+      <c r="K370" t="s">
+        <v>23</v>
+      </c>
+      <c r="L370" t="s">
+        <v>635</v>
+      </c>
+      <c r="M370" t="s">
+        <v>18</v>
+      </c>
+      <c r="N370" t="s">
+        <v>534</v>
+      </c>
+      <c r="O370" t="s">
+        <v>20</v>
+      </c>
+      <c r="P370" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q370" t="s">
+        <v>702</v>
+      </c>
+      <c r="R370" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="371" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>206</v>
+      </c>
+      <c r="B371" t="s">
+        <v>207</v>
+      </c>
+      <c r="C371" t="s">
+        <v>212</v>
+      </c>
+      <c r="D371" t="s">
+        <v>213</v>
+      </c>
+      <c r="E371" t="s">
+        <v>214</v>
+      </c>
+      <c r="F371" t="s">
+        <v>70</v>
+      </c>
+      <c r="G371" t="s">
+        <v>672</v>
+      </c>
+      <c r="H371" t="s">
+        <v>241</v>
+      </c>
+      <c r="I371" t="s">
+        <v>242</v>
+      </c>
+      <c r="J371">
+        <v>67.08</v>
+      </c>
+      <c r="K371" t="s">
+        <v>22</v>
+      </c>
+      <c r="L371" t="s">
+        <v>635</v>
+      </c>
+      <c r="M371" t="s">
+        <v>18</v>
+      </c>
+      <c r="N371" t="s">
+        <v>534</v>
+      </c>
+      <c r="O371" t="s">
+        <v>20</v>
+      </c>
+      <c r="P371" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q371" t="s">
+        <v>703</v>
+      </c>
+      <c r="R371" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="372" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>206</v>
+      </c>
+      <c r="B372" t="s">
+        <v>207</v>
+      </c>
+      <c r="C372" t="s">
+        <v>212</v>
+      </c>
+      <c r="D372" t="s">
+        <v>213</v>
+      </c>
+      <c r="E372" t="s">
+        <v>214</v>
+      </c>
+      <c r="F372" t="s">
+        <v>70</v>
+      </c>
+      <c r="G372" t="s">
+        <v>673</v>
+      </c>
+      <c r="H372" t="s">
+        <v>350</v>
+      </c>
+      <c r="I372" t="s">
+        <v>351</v>
+      </c>
+      <c r="J372">
+        <v>15.51</v>
+      </c>
+      <c r="K372" t="s">
+        <v>23</v>
+      </c>
+      <c r="L372" t="s">
+        <v>635</v>
+      </c>
+      <c r="M372" t="s">
+        <v>18</v>
+      </c>
+      <c r="N372" t="s">
+        <v>534</v>
+      </c>
+      <c r="O372" t="s">
+        <v>20</v>
+      </c>
+      <c r="P372" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q372" t="s">
+        <v>271</v>
+      </c>
+      <c r="R372" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="373" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>206</v>
+      </c>
+      <c r="B373" t="s">
+        <v>207</v>
+      </c>
+      <c r="C373" t="s">
+        <v>233</v>
+      </c>
+      <c r="D373" t="s">
+        <v>222</v>
+      </c>
+      <c r="E373" t="s">
+        <v>234</v>
+      </c>
+      <c r="F373" t="s">
+        <v>110</v>
+      </c>
+      <c r="G373" t="s">
+        <v>669</v>
+      </c>
+      <c r="H373" t="s">
+        <v>73</v>
+      </c>
+      <c r="I373" t="s">
+        <v>74</v>
+      </c>
+      <c r="J373">
+        <v>33.96</v>
+      </c>
+      <c r="K373" t="s">
+        <v>22</v>
+      </c>
+      <c r="L373" t="s">
+        <v>635</v>
+      </c>
+      <c r="M373" t="s">
+        <v>18</v>
+      </c>
+      <c r="N373" t="s">
+        <v>19</v>
+      </c>
+      <c r="O373" t="s">
+        <v>20</v>
+      </c>
+      <c r="P373" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q373" t="s">
+        <v>649</v>
+      </c>
+      <c r="R373" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="374" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>206</v>
+      </c>
+      <c r="B374" t="s">
+        <v>207</v>
+      </c>
+      <c r="C374" t="s">
+        <v>233</v>
+      </c>
+      <c r="D374" t="s">
+        <v>222</v>
+      </c>
+      <c r="E374" t="s">
+        <v>234</v>
+      </c>
+      <c r="F374" t="s">
+        <v>110</v>
+      </c>
+      <c r="G374" t="s">
+        <v>669</v>
+      </c>
+      <c r="H374" t="s">
+        <v>101</v>
+      </c>
+      <c r="I374" t="s">
+        <v>102</v>
+      </c>
+      <c r="J374">
+        <v>19.55</v>
+      </c>
+      <c r="K374" t="s">
+        <v>23</v>
+      </c>
+      <c r="L374" t="s">
+        <v>635</v>
+      </c>
+      <c r="M374" t="s">
+        <v>18</v>
+      </c>
+      <c r="N374" t="s">
+        <v>19</v>
+      </c>
+      <c r="O374" t="s">
+        <v>20</v>
+      </c>
+      <c r="P374" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q374" t="s">
+        <v>704</v>
+      </c>
+      <c r="R374" t="s">
+        <v>705</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S317" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20959,19 +24383,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20995,9 +24415,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/activitereelgueudet-2026.xlsx
+++ b/activitereelgueudet-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucas\OneDrive\Bureau\CODE HTML\Developpements\APP KENT VERCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44133141-0AE7-4381-B52A-A2E3E41E102F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EA26F7-7820-4C9B-9483-5241ACE2546B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8111" uniqueCount="830">
   <si>
     <t>codePlaque</t>
   </si>
@@ -2154,6 +2154,378 @@
   </si>
   <si>
     <t>Mai</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>03/06/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>23.53</t>
+  </si>
+  <si>
+    <t>04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30190 00                 </t>
+  </si>
+  <si>
+    <t>30190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PULVERISATEUR 600ml           </t>
+  </si>
+  <si>
+    <t>11.25</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>15.14</t>
+  </si>
+  <si>
+    <t>18/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83402 00                 </t>
+  </si>
+  <si>
+    <t>83402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUSE COUPEE SAUCISSE          </t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>24.89</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
+    <t>18.71</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84593 10                 </t>
+  </si>
+  <si>
+    <t>84593</t>
+  </si>
+  <si>
+    <t>GRAISSE BLANCHE EPAISSE 500 ML</t>
+  </si>
+  <si>
+    <t>19.34</t>
+  </si>
+  <si>
+    <t>17/06/2026</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>20.69</t>
+  </si>
+  <si>
+    <t>23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85265 00                 </t>
+  </si>
+  <si>
+    <t>85265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAT BEAD NOZZLE 2g Grey      </t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>18.28</t>
+  </si>
+  <si>
+    <t>09/06/2026</t>
+  </si>
+  <si>
+    <t>39.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85450 22                 </t>
+  </si>
+  <si>
+    <t>85450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NETTOYANT GARNITURES EN TISSU </t>
+  </si>
+  <si>
+    <t>42.69</t>
+  </si>
+  <si>
+    <t>10.48</t>
+  </si>
+  <si>
+    <t>16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86005 28                 </t>
+  </si>
+  <si>
+    <t>86005</t>
+  </si>
+  <si>
+    <t>LUBRIFIANT SILICONE TUBE 80 ML</t>
+  </si>
+  <si>
+    <t>19.83</t>
+  </si>
+  <si>
+    <t>6.34</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>8.91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86367 00                 </t>
+  </si>
+  <si>
+    <t>86367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SET PROTECTION TABLEAU BORD   </t>
+  </si>
+  <si>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>12.99</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>25/06/2026</t>
+  </si>
+  <si>
+    <t>12/06/2026</t>
+  </si>
+  <si>
+    <t>31.56</t>
+  </si>
+  <si>
+    <t>17.05</t>
+  </si>
+  <si>
+    <t>8.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86678 00                 </t>
+  </si>
+  <si>
+    <t>86678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANTS NITRILE A 3 COUCHES - L </t>
+  </si>
+  <si>
+    <t>21.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86680 22                 </t>
+  </si>
+  <si>
+    <t>86680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MULTI TAPE EVO - 50 MM X 50 M </t>
+  </si>
+  <si>
+    <t>19.63</t>
+  </si>
+  <si>
+    <t>19.14</t>
+  </si>
+  <si>
+    <t>19.62</t>
+  </si>
+  <si>
+    <t>16.77</t>
+  </si>
+  <si>
+    <t>24.99</t>
+  </si>
+  <si>
+    <t>20.34</t>
+  </si>
+  <si>
+    <t>13.58</t>
+  </si>
+  <si>
+    <t>13.65</t>
+  </si>
+  <si>
+    <t>-2</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>16.92</t>
+  </si>
+  <si>
+    <t>19.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87199 22                 </t>
+  </si>
+  <si>
+    <t>87199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREMIUM CAR SHAMPOO           </t>
+  </si>
+  <si>
+    <t>77.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87201 22                 </t>
+  </si>
+  <si>
+    <t>87201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRYSTAL FAST DRYER 25 L       </t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>28.19</t>
+  </si>
+  <si>
+    <t>28.17</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>28.04</t>
+  </si>
+  <si>
+    <t>31.13</t>
+  </si>
+  <si>
+    <t>31.05</t>
+  </si>
+  <si>
+    <t>7.64</t>
+  </si>
+  <si>
+    <t>30.53</t>
+  </si>
+  <si>
+    <t>22.12</t>
+  </si>
+  <si>
+    <t>22.15</t>
+  </si>
+  <si>
+    <t>22.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1475 33                 </t>
+  </si>
+  <si>
+    <t>A1475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPONGE 2S MIX (3 x 10/PK)     </t>
+  </si>
+  <si>
+    <t>22.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1481 00                 </t>
+  </si>
+  <si>
+    <t>A1481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLATEAU UNIVERSEL 10MM        </t>
+  </si>
+  <si>
+    <t>28.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0103 00                 </t>
+  </si>
+  <si>
+    <t>E0103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUPER GRATTOIR                </t>
+  </si>
+  <si>
+    <t>33.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0104 00                 </t>
+  </si>
+  <si>
+    <t>E0104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMES REMPLACEMENT 12 mm x5   </t>
+  </si>
+  <si>
+    <t>5.72</t>
+  </si>
+  <si>
+    <t>13.07</t>
+  </si>
+  <si>
+    <t>33.24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E0822 00                 </t>
+  </si>
+  <si>
+    <t>E0822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VENTOUSE PARE BRISE           </t>
+  </si>
+  <si>
+    <t>180.61</t>
+  </si>
+  <si>
+    <t>11.34</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
   </si>
 </sst>
 </file>
@@ -2531,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E505DD-DFE7-49B0-9B59-53447E0B5813}">
-  <dimension ref="A1:S374"/>
+  <dimension ref="A1:S477"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
@@ -24226,6 +24598,5774 @@
       </c>
       <c r="R374" t="s">
         <v>705</v>
+      </c>
+    </row>
+    <row r="375" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>206</v>
+      </c>
+      <c r="B375" t="s">
+        <v>207</v>
+      </c>
+      <c r="C375" t="s">
+        <v>212</v>
+      </c>
+      <c r="D375" t="s">
+        <v>213</v>
+      </c>
+      <c r="E375" t="s">
+        <v>214</v>
+      </c>
+      <c r="F375" t="s">
+        <v>70</v>
+      </c>
+      <c r="G375" t="s">
+        <v>707</v>
+      </c>
+      <c r="H375" t="s">
+        <v>88</v>
+      </c>
+      <c r="I375" t="s">
+        <v>89</v>
+      </c>
+      <c r="J375">
+        <v>23.53</v>
+      </c>
+      <c r="K375" t="s">
+        <v>23</v>
+      </c>
+      <c r="L375" t="s">
+        <v>708</v>
+      </c>
+      <c r="M375" t="s">
+        <v>18</v>
+      </c>
+      <c r="N375" t="s">
+        <v>534</v>
+      </c>
+      <c r="O375" t="s">
+        <v>20</v>
+      </c>
+      <c r="P375" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q375" t="s">
+        <v>709</v>
+      </c>
+      <c r="R375" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="376" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>206</v>
+      </c>
+      <c r="B376" t="s">
+        <v>207</v>
+      </c>
+      <c r="C376" t="s">
+        <v>208</v>
+      </c>
+      <c r="D376" t="s">
+        <v>209</v>
+      </c>
+      <c r="E376" t="s">
+        <v>210</v>
+      </c>
+      <c r="F376" t="s">
+        <v>118</v>
+      </c>
+      <c r="G376" t="s">
+        <v>710</v>
+      </c>
+      <c r="H376" t="s">
+        <v>711</v>
+      </c>
+      <c r="I376" t="s">
+        <v>712</v>
+      </c>
+      <c r="J376">
+        <v>22.5</v>
+      </c>
+      <c r="K376" t="s">
+        <v>22</v>
+      </c>
+      <c r="L376" t="s">
+        <v>708</v>
+      </c>
+      <c r="M376" t="s">
+        <v>18</v>
+      </c>
+      <c r="N376" t="s">
+        <v>534</v>
+      </c>
+      <c r="O376" t="s">
+        <v>20</v>
+      </c>
+      <c r="P376" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q376" t="s">
+        <v>714</v>
+      </c>
+      <c r="R376" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="377" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>206</v>
+      </c>
+      <c r="B377" t="s">
+        <v>207</v>
+      </c>
+      <c r="C377" t="s">
+        <v>215</v>
+      </c>
+      <c r="D377" t="s">
+        <v>216</v>
+      </c>
+      <c r="E377" t="s">
+        <v>32</v>
+      </c>
+      <c r="F377" t="s">
+        <v>33</v>
+      </c>
+      <c r="G377" t="s">
+        <v>715</v>
+      </c>
+      <c r="H377" t="s">
+        <v>76</v>
+      </c>
+      <c r="I377" t="s">
+        <v>77</v>
+      </c>
+      <c r="J377">
+        <v>15.14</v>
+      </c>
+      <c r="K377" t="s">
+        <v>23</v>
+      </c>
+      <c r="L377" t="s">
+        <v>708</v>
+      </c>
+      <c r="M377" t="s">
+        <v>18</v>
+      </c>
+      <c r="N377" t="s">
+        <v>534</v>
+      </c>
+      <c r="O377" t="s">
+        <v>20</v>
+      </c>
+      <c r="P377" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q377" t="s">
+        <v>716</v>
+      </c>
+      <c r="R377" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="378" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>206</v>
+      </c>
+      <c r="B378" t="s">
+        <v>207</v>
+      </c>
+      <c r="C378" t="s">
+        <v>221</v>
+      </c>
+      <c r="D378" t="s">
+        <v>222</v>
+      </c>
+      <c r="E378" t="s">
+        <v>223</v>
+      </c>
+      <c r="F378" t="s">
+        <v>151</v>
+      </c>
+      <c r="G378" t="s">
+        <v>717</v>
+      </c>
+      <c r="H378" t="s">
+        <v>718</v>
+      </c>
+      <c r="I378" t="s">
+        <v>719</v>
+      </c>
+      <c r="J378">
+        <v>2.64</v>
+      </c>
+      <c r="K378" t="s">
+        <v>50</v>
+      </c>
+      <c r="L378" t="s">
+        <v>708</v>
+      </c>
+      <c r="M378" t="s">
+        <v>18</v>
+      </c>
+      <c r="N378" t="s">
+        <v>534</v>
+      </c>
+      <c r="O378" t="s">
+        <v>20</v>
+      </c>
+      <c r="P378" t="s">
+        <v>720</v>
+      </c>
+      <c r="Q378" t="s">
+        <v>721</v>
+      </c>
+      <c r="R378" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="379" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>206</v>
+      </c>
+      <c r="B379" t="s">
+        <v>207</v>
+      </c>
+      <c r="C379" t="s">
+        <v>221</v>
+      </c>
+      <c r="D379" t="s">
+        <v>222</v>
+      </c>
+      <c r="E379" t="s">
+        <v>223</v>
+      </c>
+      <c r="F379" t="s">
+        <v>151</v>
+      </c>
+      <c r="G379" t="s">
+        <v>722</v>
+      </c>
+      <c r="H379" t="s">
+        <v>718</v>
+      </c>
+      <c r="I379" t="s">
+        <v>719</v>
+      </c>
+      <c r="J379">
+        <v>14.96</v>
+      </c>
+      <c r="K379" t="s">
+        <v>723</v>
+      </c>
+      <c r="L379" t="s">
+        <v>708</v>
+      </c>
+      <c r="M379" t="s">
+        <v>18</v>
+      </c>
+      <c r="N379" t="s">
+        <v>534</v>
+      </c>
+      <c r="O379" t="s">
+        <v>20</v>
+      </c>
+      <c r="P379" t="s">
+        <v>720</v>
+      </c>
+      <c r="Q379" t="s">
+        <v>721</v>
+      </c>
+      <c r="R379" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="380" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>206</v>
+      </c>
+      <c r="B380" t="s">
+        <v>207</v>
+      </c>
+      <c r="C380" t="s">
+        <v>215</v>
+      </c>
+      <c r="D380" t="s">
+        <v>216</v>
+      </c>
+      <c r="E380" t="s">
+        <v>32</v>
+      </c>
+      <c r="F380" t="s">
+        <v>33</v>
+      </c>
+      <c r="G380" t="s">
+        <v>715</v>
+      </c>
+      <c r="H380" t="s">
+        <v>189</v>
+      </c>
+      <c r="I380" t="s">
+        <v>190</v>
+      </c>
+      <c r="J380">
+        <v>24.89</v>
+      </c>
+      <c r="K380" t="s">
+        <v>23</v>
+      </c>
+      <c r="L380" t="s">
+        <v>708</v>
+      </c>
+      <c r="M380" t="s">
+        <v>18</v>
+      </c>
+      <c r="N380" t="s">
+        <v>534</v>
+      </c>
+      <c r="O380" t="s">
+        <v>20</v>
+      </c>
+      <c r="P380" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q380" t="s">
+        <v>724</v>
+      </c>
+      <c r="R380" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="381" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>206</v>
+      </c>
+      <c r="B381" t="s">
+        <v>207</v>
+      </c>
+      <c r="C381" t="s">
+        <v>208</v>
+      </c>
+      <c r="D381" t="s">
+        <v>209</v>
+      </c>
+      <c r="E381" t="s">
+        <v>210</v>
+      </c>
+      <c r="F381" t="s">
+        <v>118</v>
+      </c>
+      <c r="G381" t="s">
+        <v>725</v>
+      </c>
+      <c r="H381" t="s">
+        <v>189</v>
+      </c>
+      <c r="I381" t="s">
+        <v>190</v>
+      </c>
+      <c r="J381">
+        <v>24.89</v>
+      </c>
+      <c r="K381" t="s">
+        <v>23</v>
+      </c>
+      <c r="L381" t="s">
+        <v>708</v>
+      </c>
+      <c r="M381" t="s">
+        <v>18</v>
+      </c>
+      <c r="N381" t="s">
+        <v>534</v>
+      </c>
+      <c r="O381" t="s">
+        <v>20</v>
+      </c>
+      <c r="P381" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q381" t="s">
+        <v>724</v>
+      </c>
+      <c r="R381" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="382" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>206</v>
+      </c>
+      <c r="B382" t="s">
+        <v>207</v>
+      </c>
+      <c r="C382" t="s">
+        <v>215</v>
+      </c>
+      <c r="D382" t="s">
+        <v>216</v>
+      </c>
+      <c r="E382" t="s">
+        <v>32</v>
+      </c>
+      <c r="F382" t="s">
+        <v>33</v>
+      </c>
+      <c r="G382" t="s">
+        <v>715</v>
+      </c>
+      <c r="H382" t="s">
+        <v>177</v>
+      </c>
+      <c r="I382" t="s">
+        <v>178</v>
+      </c>
+      <c r="J382">
+        <v>18.71</v>
+      </c>
+      <c r="K382" t="s">
+        <v>23</v>
+      </c>
+      <c r="L382" t="s">
+        <v>708</v>
+      </c>
+      <c r="M382" t="s">
+        <v>18</v>
+      </c>
+      <c r="N382" t="s">
+        <v>534</v>
+      </c>
+      <c r="O382" t="s">
+        <v>20</v>
+      </c>
+      <c r="P382" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q382" t="s">
+        <v>726</v>
+      </c>
+      <c r="R382" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="383" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>206</v>
+      </c>
+      <c r="B383" t="s">
+        <v>207</v>
+      </c>
+      <c r="C383" t="s">
+        <v>221</v>
+      </c>
+      <c r="D383" t="s">
+        <v>222</v>
+      </c>
+      <c r="E383" t="s">
+        <v>223</v>
+      </c>
+      <c r="F383" t="s">
+        <v>151</v>
+      </c>
+      <c r="G383" t="s">
+        <v>727</v>
+      </c>
+      <c r="H383" t="s">
+        <v>728</v>
+      </c>
+      <c r="I383" t="s">
+        <v>729</v>
+      </c>
+      <c r="J383">
+        <v>19.34</v>
+      </c>
+      <c r="K383" t="s">
+        <v>23</v>
+      </c>
+      <c r="L383" t="s">
+        <v>708</v>
+      </c>
+      <c r="M383" t="s">
+        <v>18</v>
+      </c>
+      <c r="N383" t="s">
+        <v>534</v>
+      </c>
+      <c r="O383" t="s">
+        <v>20</v>
+      </c>
+      <c r="P383" t="s">
+        <v>730</v>
+      </c>
+      <c r="Q383" t="s">
+        <v>731</v>
+      </c>
+      <c r="R383" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="384" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>206</v>
+      </c>
+      <c r="B384" t="s">
+        <v>207</v>
+      </c>
+      <c r="C384" t="s">
+        <v>215</v>
+      </c>
+      <c r="D384" t="s">
+        <v>216</v>
+      </c>
+      <c r="E384" t="s">
+        <v>32</v>
+      </c>
+      <c r="F384" t="s">
+        <v>33</v>
+      </c>
+      <c r="G384" t="s">
+        <v>732</v>
+      </c>
+      <c r="H384" t="s">
+        <v>420</v>
+      </c>
+      <c r="I384" t="s">
+        <v>421</v>
+      </c>
+      <c r="J384">
+        <v>13.17</v>
+      </c>
+      <c r="K384" t="s">
+        <v>23</v>
+      </c>
+      <c r="L384" t="s">
+        <v>708</v>
+      </c>
+      <c r="M384" t="s">
+        <v>18</v>
+      </c>
+      <c r="N384" t="s">
+        <v>534</v>
+      </c>
+      <c r="O384" t="s">
+        <v>20</v>
+      </c>
+      <c r="P384" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q384" t="s">
+        <v>423</v>
+      </c>
+      <c r="R384" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="385" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>206</v>
+      </c>
+      <c r="B385" t="s">
+        <v>207</v>
+      </c>
+      <c r="C385" t="s">
+        <v>215</v>
+      </c>
+      <c r="D385" t="s">
+        <v>216</v>
+      </c>
+      <c r="E385" t="s">
+        <v>32</v>
+      </c>
+      <c r="F385" t="s">
+        <v>33</v>
+      </c>
+      <c r="G385" t="s">
+        <v>733</v>
+      </c>
+      <c r="H385" t="s">
+        <v>420</v>
+      </c>
+      <c r="I385" t="s">
+        <v>421</v>
+      </c>
+      <c r="J385">
+        <v>13.17</v>
+      </c>
+      <c r="K385" t="s">
+        <v>23</v>
+      </c>
+      <c r="L385" t="s">
+        <v>708</v>
+      </c>
+      <c r="M385" t="s">
+        <v>18</v>
+      </c>
+      <c r="N385" t="s">
+        <v>534</v>
+      </c>
+      <c r="O385" t="s">
+        <v>20</v>
+      </c>
+      <c r="P385" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q385" t="s">
+        <v>423</v>
+      </c>
+      <c r="R385" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="386" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>206</v>
+      </c>
+      <c r="B386" t="s">
+        <v>207</v>
+      </c>
+      <c r="C386" t="s">
+        <v>208</v>
+      </c>
+      <c r="D386" t="s">
+        <v>209</v>
+      </c>
+      <c r="E386" t="s">
+        <v>210</v>
+      </c>
+      <c r="F386" t="s">
+        <v>118</v>
+      </c>
+      <c r="G386" t="s">
+        <v>715</v>
+      </c>
+      <c r="H386" t="s">
+        <v>132</v>
+      </c>
+      <c r="I386" t="s">
+        <v>133</v>
+      </c>
+      <c r="J386">
+        <v>20.69</v>
+      </c>
+      <c r="K386" t="s">
+        <v>23</v>
+      </c>
+      <c r="L386" t="s">
+        <v>708</v>
+      </c>
+      <c r="M386" t="s">
+        <v>18</v>
+      </c>
+      <c r="N386" t="s">
+        <v>534</v>
+      </c>
+      <c r="O386" t="s">
+        <v>20</v>
+      </c>
+      <c r="P386" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q386" t="s">
+        <v>734</v>
+      </c>
+      <c r="R386" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="387" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>206</v>
+      </c>
+      <c r="B387" t="s">
+        <v>207</v>
+      </c>
+      <c r="C387" t="s">
+        <v>208</v>
+      </c>
+      <c r="D387" t="s">
+        <v>209</v>
+      </c>
+      <c r="E387" t="s">
+        <v>210</v>
+      </c>
+      <c r="F387" t="s">
+        <v>118</v>
+      </c>
+      <c r="G387" t="s">
+        <v>715</v>
+      </c>
+      <c r="H387" t="s">
+        <v>132</v>
+      </c>
+      <c r="I387" t="s">
+        <v>133</v>
+      </c>
+      <c r="J387">
+        <v>20.69</v>
+      </c>
+      <c r="K387" t="s">
+        <v>23</v>
+      </c>
+      <c r="L387" t="s">
+        <v>708</v>
+      </c>
+      <c r="M387" t="s">
+        <v>18</v>
+      </c>
+      <c r="N387" t="s">
+        <v>534</v>
+      </c>
+      <c r="O387" t="s">
+        <v>20</v>
+      </c>
+      <c r="P387" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q387" t="s">
+        <v>734</v>
+      </c>
+      <c r="R387" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="388" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>206</v>
+      </c>
+      <c r="B388" t="s">
+        <v>207</v>
+      </c>
+      <c r="C388" t="s">
+        <v>208</v>
+      </c>
+      <c r="D388" t="s">
+        <v>209</v>
+      </c>
+      <c r="E388" t="s">
+        <v>210</v>
+      </c>
+      <c r="F388" t="s">
+        <v>118</v>
+      </c>
+      <c r="G388" t="s">
+        <v>735</v>
+      </c>
+      <c r="H388" t="s">
+        <v>132</v>
+      </c>
+      <c r="I388" t="s">
+        <v>133</v>
+      </c>
+      <c r="J388">
+        <v>62.07</v>
+      </c>
+      <c r="K388" t="s">
+        <v>50</v>
+      </c>
+      <c r="L388" t="s">
+        <v>708</v>
+      </c>
+      <c r="M388" t="s">
+        <v>18</v>
+      </c>
+      <c r="N388" t="s">
+        <v>534</v>
+      </c>
+      <c r="O388" t="s">
+        <v>20</v>
+      </c>
+      <c r="P388" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q388" t="s">
+        <v>734</v>
+      </c>
+      <c r="R388" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="389" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>206</v>
+      </c>
+      <c r="B389" t="s">
+        <v>207</v>
+      </c>
+      <c r="C389" t="s">
+        <v>208</v>
+      </c>
+      <c r="D389" t="s">
+        <v>209</v>
+      </c>
+      <c r="E389" t="s">
+        <v>210</v>
+      </c>
+      <c r="F389" t="s">
+        <v>118</v>
+      </c>
+      <c r="G389" t="s">
+        <v>715</v>
+      </c>
+      <c r="H389" t="s">
+        <v>132</v>
+      </c>
+      <c r="I389" t="s">
+        <v>133</v>
+      </c>
+      <c r="J389">
+        <v>62.07</v>
+      </c>
+      <c r="K389" t="s">
+        <v>50</v>
+      </c>
+      <c r="L389" t="s">
+        <v>708</v>
+      </c>
+      <c r="M389" t="s">
+        <v>18</v>
+      </c>
+      <c r="N389" t="s">
+        <v>534</v>
+      </c>
+      <c r="O389" t="s">
+        <v>20</v>
+      </c>
+      <c r="P389" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q389" t="s">
+        <v>734</v>
+      </c>
+      <c r="R389" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="390" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>206</v>
+      </c>
+      <c r="B390" t="s">
+        <v>207</v>
+      </c>
+      <c r="C390" t="s">
+        <v>251</v>
+      </c>
+      <c r="D390" t="s">
+        <v>252</v>
+      </c>
+      <c r="E390" t="s">
+        <v>198</v>
+      </c>
+      <c r="F390" t="s">
+        <v>119</v>
+      </c>
+      <c r="G390" t="s">
+        <v>733</v>
+      </c>
+      <c r="H390" t="s">
+        <v>132</v>
+      </c>
+      <c r="I390" t="s">
+        <v>133</v>
+      </c>
+      <c r="J390">
+        <v>20.69</v>
+      </c>
+      <c r="K390" t="s">
+        <v>23</v>
+      </c>
+      <c r="L390" t="s">
+        <v>708</v>
+      </c>
+      <c r="M390" t="s">
+        <v>18</v>
+      </c>
+      <c r="N390" t="s">
+        <v>534</v>
+      </c>
+      <c r="O390" t="s">
+        <v>20</v>
+      </c>
+      <c r="P390" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q390" t="s">
+        <v>734</v>
+      </c>
+      <c r="R390" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="391" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>206</v>
+      </c>
+      <c r="B391" t="s">
+        <v>207</v>
+      </c>
+      <c r="C391" t="s">
+        <v>251</v>
+      </c>
+      <c r="D391" t="s">
+        <v>252</v>
+      </c>
+      <c r="E391" t="s">
+        <v>198</v>
+      </c>
+      <c r="F391" t="s">
+        <v>119</v>
+      </c>
+      <c r="G391" t="s">
+        <v>733</v>
+      </c>
+      <c r="H391" t="s">
+        <v>132</v>
+      </c>
+      <c r="I391" t="s">
+        <v>133</v>
+      </c>
+      <c r="J391">
+        <v>82.76</v>
+      </c>
+      <c r="K391" t="s">
+        <v>40</v>
+      </c>
+      <c r="L391" t="s">
+        <v>708</v>
+      </c>
+      <c r="M391" t="s">
+        <v>18</v>
+      </c>
+      <c r="N391" t="s">
+        <v>534</v>
+      </c>
+      <c r="O391" t="s">
+        <v>20</v>
+      </c>
+      <c r="P391" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q391" t="s">
+        <v>734</v>
+      </c>
+      <c r="R391" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="392" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>206</v>
+      </c>
+      <c r="B392" t="s">
+        <v>207</v>
+      </c>
+      <c r="C392" t="s">
+        <v>215</v>
+      </c>
+      <c r="D392" t="s">
+        <v>216</v>
+      </c>
+      <c r="E392" t="s">
+        <v>32</v>
+      </c>
+      <c r="F392" t="s">
+        <v>33</v>
+      </c>
+      <c r="G392" t="s">
+        <v>732</v>
+      </c>
+      <c r="H392" t="s">
+        <v>736</v>
+      </c>
+      <c r="I392" t="s">
+        <v>737</v>
+      </c>
+      <c r="J392">
+        <v>10.68</v>
+      </c>
+      <c r="K392" t="s">
+        <v>27</v>
+      </c>
+      <c r="L392" t="s">
+        <v>708</v>
+      </c>
+      <c r="M392" t="s">
+        <v>18</v>
+      </c>
+      <c r="N392" t="s">
+        <v>534</v>
+      </c>
+      <c r="O392" t="s">
+        <v>20</v>
+      </c>
+      <c r="P392" t="s">
+        <v>738</v>
+      </c>
+      <c r="Q392" t="s">
+        <v>739</v>
+      </c>
+      <c r="R392" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="393" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>206</v>
+      </c>
+      <c r="B393" t="s">
+        <v>207</v>
+      </c>
+      <c r="C393" t="s">
+        <v>212</v>
+      </c>
+      <c r="D393" t="s">
+        <v>213</v>
+      </c>
+      <c r="E393" t="s">
+        <v>214</v>
+      </c>
+      <c r="F393" t="s">
+        <v>70</v>
+      </c>
+      <c r="G393" t="s">
+        <v>707</v>
+      </c>
+      <c r="H393" t="s">
+        <v>425</v>
+      </c>
+      <c r="I393" t="s">
+        <v>426</v>
+      </c>
+      <c r="J393">
+        <v>18.28</v>
+      </c>
+      <c r="K393" t="s">
+        <v>23</v>
+      </c>
+      <c r="L393" t="s">
+        <v>708</v>
+      </c>
+      <c r="M393" t="s">
+        <v>18</v>
+      </c>
+      <c r="N393" t="s">
+        <v>534</v>
+      </c>
+      <c r="O393" t="s">
+        <v>20</v>
+      </c>
+      <c r="P393" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q393" t="s">
+        <v>740</v>
+      </c>
+      <c r="R393" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="394" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>206</v>
+      </c>
+      <c r="B394" t="s">
+        <v>207</v>
+      </c>
+      <c r="C394" t="s">
+        <v>251</v>
+      </c>
+      <c r="D394" t="s">
+        <v>252</v>
+      </c>
+      <c r="E394" t="s">
+        <v>198</v>
+      </c>
+      <c r="F394" t="s">
+        <v>119</v>
+      </c>
+      <c r="G394" t="s">
+        <v>741</v>
+      </c>
+      <c r="H394" t="s">
+        <v>98</v>
+      </c>
+      <c r="I394" t="s">
+        <v>99</v>
+      </c>
+      <c r="J394">
+        <v>39.72</v>
+      </c>
+      <c r="K394" t="s">
+        <v>23</v>
+      </c>
+      <c r="L394" t="s">
+        <v>708</v>
+      </c>
+      <c r="M394" t="s">
+        <v>18</v>
+      </c>
+      <c r="N394" t="s">
+        <v>534</v>
+      </c>
+      <c r="O394" t="s">
+        <v>20</v>
+      </c>
+      <c r="P394" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q394" t="s">
+        <v>742</v>
+      </c>
+      <c r="R394" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="395" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>206</v>
+      </c>
+      <c r="B395" t="s">
+        <v>207</v>
+      </c>
+      <c r="C395" t="s">
+        <v>208</v>
+      </c>
+      <c r="D395" t="s">
+        <v>209</v>
+      </c>
+      <c r="E395" t="s">
+        <v>210</v>
+      </c>
+      <c r="F395" t="s">
+        <v>118</v>
+      </c>
+      <c r="G395" t="s">
+        <v>710</v>
+      </c>
+      <c r="H395" t="s">
+        <v>743</v>
+      </c>
+      <c r="I395" t="s">
+        <v>744</v>
+      </c>
+      <c r="J395">
+        <v>42.69</v>
+      </c>
+      <c r="K395" t="s">
+        <v>23</v>
+      </c>
+      <c r="L395" t="s">
+        <v>708</v>
+      </c>
+      <c r="M395" t="s">
+        <v>18</v>
+      </c>
+      <c r="N395" t="s">
+        <v>534</v>
+      </c>
+      <c r="O395" t="s">
+        <v>20</v>
+      </c>
+      <c r="P395" t="s">
+        <v>745</v>
+      </c>
+      <c r="Q395" t="s">
+        <v>746</v>
+      </c>
+      <c r="R395" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="396" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>206</v>
+      </c>
+      <c r="B396" t="s">
+        <v>207</v>
+      </c>
+      <c r="C396" t="s">
+        <v>215</v>
+      </c>
+      <c r="D396" t="s">
+        <v>216</v>
+      </c>
+      <c r="E396" t="s">
+        <v>32</v>
+      </c>
+      <c r="F396" t="s">
+        <v>33</v>
+      </c>
+      <c r="G396" t="s">
+        <v>733</v>
+      </c>
+      <c r="H396" t="s">
+        <v>319</v>
+      </c>
+      <c r="I396" t="s">
+        <v>320</v>
+      </c>
+      <c r="J396">
+        <v>10.48</v>
+      </c>
+      <c r="K396" t="s">
+        <v>23</v>
+      </c>
+      <c r="L396" t="s">
+        <v>708</v>
+      </c>
+      <c r="M396" t="s">
+        <v>18</v>
+      </c>
+      <c r="N396" t="s">
+        <v>534</v>
+      </c>
+      <c r="O396" t="s">
+        <v>20</v>
+      </c>
+      <c r="P396" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q396" t="s">
+        <v>747</v>
+      </c>
+      <c r="R396" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="397" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>206</v>
+      </c>
+      <c r="B397" t="s">
+        <v>207</v>
+      </c>
+      <c r="C397" t="s">
+        <v>212</v>
+      </c>
+      <c r="D397" t="s">
+        <v>213</v>
+      </c>
+      <c r="E397" t="s">
+        <v>214</v>
+      </c>
+      <c r="F397" t="s">
+        <v>70</v>
+      </c>
+      <c r="G397" t="s">
+        <v>707</v>
+      </c>
+      <c r="H397" t="s">
+        <v>79</v>
+      </c>
+      <c r="I397" t="s">
+        <v>80</v>
+      </c>
+      <c r="J397">
+        <v>43.52</v>
+      </c>
+      <c r="K397" t="s">
+        <v>22</v>
+      </c>
+      <c r="L397" t="s">
+        <v>708</v>
+      </c>
+      <c r="M397" t="s">
+        <v>18</v>
+      </c>
+      <c r="N397" t="s">
+        <v>534</v>
+      </c>
+      <c r="O397" t="s">
+        <v>20</v>
+      </c>
+      <c r="P397" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q397" t="s">
+        <v>383</v>
+      </c>
+      <c r="R397" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="398" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>206</v>
+      </c>
+      <c r="B398" t="s">
+        <v>207</v>
+      </c>
+      <c r="C398" t="s">
+        <v>221</v>
+      </c>
+      <c r="D398" t="s">
+        <v>222</v>
+      </c>
+      <c r="E398" t="s">
+        <v>223</v>
+      </c>
+      <c r="F398" t="s">
+        <v>151</v>
+      </c>
+      <c r="G398" t="s">
+        <v>748</v>
+      </c>
+      <c r="H398" t="s">
+        <v>749</v>
+      </c>
+      <c r="I398" t="s">
+        <v>750</v>
+      </c>
+      <c r="J398">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="K398" t="s">
+        <v>23</v>
+      </c>
+      <c r="L398" t="s">
+        <v>708</v>
+      </c>
+      <c r="M398" t="s">
+        <v>18</v>
+      </c>
+      <c r="N398" t="s">
+        <v>534</v>
+      </c>
+      <c r="O398" t="s">
+        <v>20</v>
+      </c>
+      <c r="P398" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q398" t="s">
+        <v>752</v>
+      </c>
+      <c r="R398" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="399" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>206</v>
+      </c>
+      <c r="B399" t="s">
+        <v>207</v>
+      </c>
+      <c r="C399" t="s">
+        <v>221</v>
+      </c>
+      <c r="D399" t="s">
+        <v>222</v>
+      </c>
+      <c r="E399" t="s">
+        <v>223</v>
+      </c>
+      <c r="F399" t="s">
+        <v>151</v>
+      </c>
+      <c r="G399" t="s">
+        <v>717</v>
+      </c>
+      <c r="H399" t="s">
+        <v>749</v>
+      </c>
+      <c r="I399" t="s">
+        <v>750</v>
+      </c>
+      <c r="J399">
+        <v>19.829999999999998</v>
+      </c>
+      <c r="K399" t="s">
+        <v>23</v>
+      </c>
+      <c r="L399" t="s">
+        <v>708</v>
+      </c>
+      <c r="M399" t="s">
+        <v>18</v>
+      </c>
+      <c r="N399" t="s">
+        <v>534</v>
+      </c>
+      <c r="O399" t="s">
+        <v>20</v>
+      </c>
+      <c r="P399" t="s">
+        <v>751</v>
+      </c>
+      <c r="Q399" t="s">
+        <v>752</v>
+      </c>
+      <c r="R399" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="400" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>206</v>
+      </c>
+      <c r="B400" t="s">
+        <v>207</v>
+      </c>
+      <c r="C400" t="s">
+        <v>215</v>
+      </c>
+      <c r="D400" t="s">
+        <v>216</v>
+      </c>
+      <c r="E400" t="s">
+        <v>32</v>
+      </c>
+      <c r="F400" t="s">
+        <v>33</v>
+      </c>
+      <c r="G400" t="s">
+        <v>715</v>
+      </c>
+      <c r="H400" t="s">
+        <v>24</v>
+      </c>
+      <c r="I400" t="s">
+        <v>25</v>
+      </c>
+      <c r="J400">
+        <v>6.34</v>
+      </c>
+      <c r="K400" t="s">
+        <v>23</v>
+      </c>
+      <c r="L400" t="s">
+        <v>708</v>
+      </c>
+      <c r="M400" t="s">
+        <v>18</v>
+      </c>
+      <c r="N400" t="s">
+        <v>534</v>
+      </c>
+      <c r="O400" t="s">
+        <v>20</v>
+      </c>
+      <c r="P400" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q400" t="s">
+        <v>753</v>
+      </c>
+      <c r="R400" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="401" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>206</v>
+      </c>
+      <c r="B401" t="s">
+        <v>207</v>
+      </c>
+      <c r="C401" t="s">
+        <v>251</v>
+      </c>
+      <c r="D401" t="s">
+        <v>252</v>
+      </c>
+      <c r="E401" t="s">
+        <v>198</v>
+      </c>
+      <c r="F401" t="s">
+        <v>119</v>
+      </c>
+      <c r="G401" t="s">
+        <v>754</v>
+      </c>
+      <c r="H401" t="s">
+        <v>613</v>
+      </c>
+      <c r="I401" t="s">
+        <v>614</v>
+      </c>
+      <c r="J401">
+        <v>8.91</v>
+      </c>
+      <c r="K401" t="s">
+        <v>23</v>
+      </c>
+      <c r="L401" t="s">
+        <v>708</v>
+      </c>
+      <c r="M401" t="s">
+        <v>18</v>
+      </c>
+      <c r="N401" t="s">
+        <v>534</v>
+      </c>
+      <c r="O401" t="s">
+        <v>20</v>
+      </c>
+      <c r="P401" t="s">
+        <v>615</v>
+      </c>
+      <c r="Q401" t="s">
+        <v>755</v>
+      </c>
+      <c r="R401" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="402" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>206</v>
+      </c>
+      <c r="B402" t="s">
+        <v>207</v>
+      </c>
+      <c r="C402" t="s">
+        <v>215</v>
+      </c>
+      <c r="D402" t="s">
+        <v>216</v>
+      </c>
+      <c r="E402" t="s">
+        <v>32</v>
+      </c>
+      <c r="F402" t="s">
+        <v>33</v>
+      </c>
+      <c r="G402" t="s">
+        <v>732</v>
+      </c>
+      <c r="H402" t="s">
+        <v>756</v>
+      </c>
+      <c r="I402" t="s">
+        <v>757</v>
+      </c>
+      <c r="J402">
+        <v>27.4</v>
+      </c>
+      <c r="K402" t="s">
+        <v>23</v>
+      </c>
+      <c r="L402" t="s">
+        <v>708</v>
+      </c>
+      <c r="M402" t="s">
+        <v>18</v>
+      </c>
+      <c r="N402" t="s">
+        <v>534</v>
+      </c>
+      <c r="O402" t="s">
+        <v>20</v>
+      </c>
+      <c r="P402" t="s">
+        <v>758</v>
+      </c>
+      <c r="Q402" t="s">
+        <v>759</v>
+      </c>
+      <c r="R402" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="403" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>206</v>
+      </c>
+      <c r="B403" t="s">
+        <v>207</v>
+      </c>
+      <c r="C403" t="s">
+        <v>221</v>
+      </c>
+      <c r="D403" t="s">
+        <v>222</v>
+      </c>
+      <c r="E403" t="s">
+        <v>223</v>
+      </c>
+      <c r="F403" t="s">
+        <v>151</v>
+      </c>
+      <c r="G403" t="s">
+        <v>733</v>
+      </c>
+      <c r="H403" t="s">
+        <v>148</v>
+      </c>
+      <c r="I403" t="s">
+        <v>149</v>
+      </c>
+      <c r="J403">
+        <v>12.99</v>
+      </c>
+      <c r="K403" t="s">
+        <v>23</v>
+      </c>
+      <c r="L403" t="s">
+        <v>708</v>
+      </c>
+      <c r="M403" t="s">
+        <v>18</v>
+      </c>
+      <c r="N403" t="s">
+        <v>534</v>
+      </c>
+      <c r="O403" t="s">
+        <v>20</v>
+      </c>
+      <c r="P403" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q403" t="s">
+        <v>760</v>
+      </c>
+      <c r="R403" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="404" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>206</v>
+      </c>
+      <c r="B404" t="s">
+        <v>207</v>
+      </c>
+      <c r="C404" t="s">
+        <v>221</v>
+      </c>
+      <c r="D404" t="s">
+        <v>222</v>
+      </c>
+      <c r="E404" t="s">
+        <v>223</v>
+      </c>
+      <c r="F404" t="s">
+        <v>151</v>
+      </c>
+      <c r="G404" t="s">
+        <v>733</v>
+      </c>
+      <c r="H404" t="s">
+        <v>148</v>
+      </c>
+      <c r="I404" t="s">
+        <v>149</v>
+      </c>
+      <c r="J404">
+        <v>12.99</v>
+      </c>
+      <c r="K404" t="s">
+        <v>23</v>
+      </c>
+      <c r="L404" t="s">
+        <v>708</v>
+      </c>
+      <c r="M404" t="s">
+        <v>18</v>
+      </c>
+      <c r="N404" t="s">
+        <v>534</v>
+      </c>
+      <c r="O404" t="s">
+        <v>20</v>
+      </c>
+      <c r="P404" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q404" t="s">
+        <v>760</v>
+      </c>
+      <c r="R404" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="405" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>206</v>
+      </c>
+      <c r="B405" t="s">
+        <v>207</v>
+      </c>
+      <c r="C405" t="s">
+        <v>221</v>
+      </c>
+      <c r="D405" t="s">
+        <v>222</v>
+      </c>
+      <c r="E405" t="s">
+        <v>223</v>
+      </c>
+      <c r="F405" t="s">
+        <v>151</v>
+      </c>
+      <c r="G405" t="s">
+        <v>733</v>
+      </c>
+      <c r="H405" t="s">
+        <v>148</v>
+      </c>
+      <c r="I405" t="s">
+        <v>149</v>
+      </c>
+      <c r="J405">
+        <v>25.98</v>
+      </c>
+      <c r="K405" t="s">
+        <v>22</v>
+      </c>
+      <c r="L405" t="s">
+        <v>708</v>
+      </c>
+      <c r="M405" t="s">
+        <v>18</v>
+      </c>
+      <c r="N405" t="s">
+        <v>534</v>
+      </c>
+      <c r="O405" t="s">
+        <v>20</v>
+      </c>
+      <c r="P405" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q405" t="s">
+        <v>760</v>
+      </c>
+      <c r="R405" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="406" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>206</v>
+      </c>
+      <c r="B406" t="s">
+        <v>207</v>
+      </c>
+      <c r="C406" t="s">
+        <v>221</v>
+      </c>
+      <c r="D406" t="s">
+        <v>222</v>
+      </c>
+      <c r="E406" t="s">
+        <v>223</v>
+      </c>
+      <c r="F406" t="s">
+        <v>151</v>
+      </c>
+      <c r="G406" t="s">
+        <v>725</v>
+      </c>
+      <c r="H406" t="s">
+        <v>148</v>
+      </c>
+      <c r="I406" t="s">
+        <v>149</v>
+      </c>
+      <c r="J406">
+        <v>51.96</v>
+      </c>
+      <c r="K406" t="s">
+        <v>40</v>
+      </c>
+      <c r="L406" t="s">
+        <v>708</v>
+      </c>
+      <c r="M406" t="s">
+        <v>18</v>
+      </c>
+      <c r="N406" t="s">
+        <v>534</v>
+      </c>
+      <c r="O406" t="s">
+        <v>20</v>
+      </c>
+      <c r="P406" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q406" t="s">
+        <v>760</v>
+      </c>
+      <c r="R406" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="407" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>206</v>
+      </c>
+      <c r="B407" t="s">
+        <v>207</v>
+      </c>
+      <c r="C407" t="s">
+        <v>208</v>
+      </c>
+      <c r="D407" t="s">
+        <v>209</v>
+      </c>
+      <c r="E407" t="s">
+        <v>210</v>
+      </c>
+      <c r="F407" t="s">
+        <v>118</v>
+      </c>
+      <c r="G407" t="s">
+        <v>761</v>
+      </c>
+      <c r="H407" t="s">
+        <v>148</v>
+      </c>
+      <c r="I407" t="s">
+        <v>149</v>
+      </c>
+      <c r="J407">
+        <v>12.99</v>
+      </c>
+      <c r="K407" t="s">
+        <v>23</v>
+      </c>
+      <c r="L407" t="s">
+        <v>708</v>
+      </c>
+      <c r="M407" t="s">
+        <v>18</v>
+      </c>
+      <c r="N407" t="s">
+        <v>534</v>
+      </c>
+      <c r="O407" t="s">
+        <v>20</v>
+      </c>
+      <c r="P407" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q407" t="s">
+        <v>760</v>
+      </c>
+      <c r="R407" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="408" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>206</v>
+      </c>
+      <c r="B408" t="s">
+        <v>207</v>
+      </c>
+      <c r="C408" t="s">
+        <v>208</v>
+      </c>
+      <c r="D408" t="s">
+        <v>209</v>
+      </c>
+      <c r="E408" t="s">
+        <v>210</v>
+      </c>
+      <c r="F408" t="s">
+        <v>118</v>
+      </c>
+      <c r="G408" t="s">
+        <v>754</v>
+      </c>
+      <c r="H408" t="s">
+        <v>148</v>
+      </c>
+      <c r="I408" t="s">
+        <v>149</v>
+      </c>
+      <c r="J408">
+        <v>12.99</v>
+      </c>
+      <c r="K408" t="s">
+        <v>23</v>
+      </c>
+      <c r="L408" t="s">
+        <v>708</v>
+      </c>
+      <c r="M408" t="s">
+        <v>18</v>
+      </c>
+      <c r="N408" t="s">
+        <v>534</v>
+      </c>
+      <c r="O408" t="s">
+        <v>20</v>
+      </c>
+      <c r="P408" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q408" t="s">
+        <v>760</v>
+      </c>
+      <c r="R408" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="409" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>206</v>
+      </c>
+      <c r="B409" t="s">
+        <v>207</v>
+      </c>
+      <c r="C409" t="s">
+        <v>208</v>
+      </c>
+      <c r="D409" t="s">
+        <v>209</v>
+      </c>
+      <c r="E409" t="s">
+        <v>210</v>
+      </c>
+      <c r="F409" t="s">
+        <v>118</v>
+      </c>
+      <c r="G409" t="s">
+        <v>762</v>
+      </c>
+      <c r="H409" t="s">
+        <v>148</v>
+      </c>
+      <c r="I409" t="s">
+        <v>149</v>
+      </c>
+      <c r="J409">
+        <v>12.99</v>
+      </c>
+      <c r="K409" t="s">
+        <v>23</v>
+      </c>
+      <c r="L409" t="s">
+        <v>708</v>
+      </c>
+      <c r="M409" t="s">
+        <v>18</v>
+      </c>
+      <c r="N409" t="s">
+        <v>534</v>
+      </c>
+      <c r="O409" t="s">
+        <v>20</v>
+      </c>
+      <c r="P409" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q409" t="s">
+        <v>760</v>
+      </c>
+      <c r="R409" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="410" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>206</v>
+      </c>
+      <c r="B410" t="s">
+        <v>207</v>
+      </c>
+      <c r="C410" t="s">
+        <v>208</v>
+      </c>
+      <c r="D410" t="s">
+        <v>209</v>
+      </c>
+      <c r="E410" t="s">
+        <v>210</v>
+      </c>
+      <c r="F410" t="s">
+        <v>118</v>
+      </c>
+      <c r="G410" t="s">
+        <v>762</v>
+      </c>
+      <c r="H410" t="s">
+        <v>148</v>
+      </c>
+      <c r="I410" t="s">
+        <v>149</v>
+      </c>
+      <c r="J410">
+        <v>12.99</v>
+      </c>
+      <c r="K410" t="s">
+        <v>23</v>
+      </c>
+      <c r="L410" t="s">
+        <v>708</v>
+      </c>
+      <c r="M410" t="s">
+        <v>18</v>
+      </c>
+      <c r="N410" t="s">
+        <v>534</v>
+      </c>
+      <c r="O410" t="s">
+        <v>20</v>
+      </c>
+      <c r="P410" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q410" t="s">
+        <v>760</v>
+      </c>
+      <c r="R410" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="411" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>206</v>
+      </c>
+      <c r="B411" t="s">
+        <v>207</v>
+      </c>
+      <c r="C411" t="s">
+        <v>208</v>
+      </c>
+      <c r="D411" t="s">
+        <v>209</v>
+      </c>
+      <c r="E411" t="s">
+        <v>210</v>
+      </c>
+      <c r="F411" t="s">
+        <v>118</v>
+      </c>
+      <c r="G411" t="s">
+        <v>754</v>
+      </c>
+      <c r="H411" t="s">
+        <v>148</v>
+      </c>
+      <c r="I411" t="s">
+        <v>149</v>
+      </c>
+      <c r="J411">
+        <v>25.98</v>
+      </c>
+      <c r="K411" t="s">
+        <v>22</v>
+      </c>
+      <c r="L411" t="s">
+        <v>708</v>
+      </c>
+      <c r="M411" t="s">
+        <v>18</v>
+      </c>
+      <c r="N411" t="s">
+        <v>534</v>
+      </c>
+      <c r="O411" t="s">
+        <v>20</v>
+      </c>
+      <c r="P411" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q411" t="s">
+        <v>760</v>
+      </c>
+      <c r="R411" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="412" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>206</v>
+      </c>
+      <c r="B412" t="s">
+        <v>207</v>
+      </c>
+      <c r="C412" t="s">
+        <v>208</v>
+      </c>
+      <c r="D412" t="s">
+        <v>209</v>
+      </c>
+      <c r="E412" t="s">
+        <v>210</v>
+      </c>
+      <c r="F412" t="s">
+        <v>118</v>
+      </c>
+      <c r="G412" t="s">
+        <v>762</v>
+      </c>
+      <c r="H412" t="s">
+        <v>148</v>
+      </c>
+      <c r="I412" t="s">
+        <v>149</v>
+      </c>
+      <c r="J412">
+        <v>25.98</v>
+      </c>
+      <c r="K412" t="s">
+        <v>22</v>
+      </c>
+      <c r="L412" t="s">
+        <v>708</v>
+      </c>
+      <c r="M412" t="s">
+        <v>18</v>
+      </c>
+      <c r="N412" t="s">
+        <v>534</v>
+      </c>
+      <c r="O412" t="s">
+        <v>20</v>
+      </c>
+      <c r="P412" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q412" t="s">
+        <v>760</v>
+      </c>
+      <c r="R412" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="413" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>206</v>
+      </c>
+      <c r="B413" t="s">
+        <v>207</v>
+      </c>
+      <c r="C413" t="s">
+        <v>251</v>
+      </c>
+      <c r="D413" t="s">
+        <v>252</v>
+      </c>
+      <c r="E413" t="s">
+        <v>198</v>
+      </c>
+      <c r="F413" t="s">
+        <v>119</v>
+      </c>
+      <c r="G413" t="s">
+        <v>763</v>
+      </c>
+      <c r="H413" t="s">
+        <v>148</v>
+      </c>
+      <c r="I413" t="s">
+        <v>149</v>
+      </c>
+      <c r="J413">
+        <v>38.97</v>
+      </c>
+      <c r="K413" t="s">
+        <v>50</v>
+      </c>
+      <c r="L413" t="s">
+        <v>708</v>
+      </c>
+      <c r="M413" t="s">
+        <v>18</v>
+      </c>
+      <c r="N413" t="s">
+        <v>534</v>
+      </c>
+      <c r="O413" t="s">
+        <v>20</v>
+      </c>
+      <c r="P413" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q413" t="s">
+        <v>760</v>
+      </c>
+      <c r="R413" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="414" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>206</v>
+      </c>
+      <c r="B414" t="s">
+        <v>207</v>
+      </c>
+      <c r="C414" t="s">
+        <v>466</v>
+      </c>
+      <c r="D414" t="s">
+        <v>222</v>
+      </c>
+      <c r="E414" t="s">
+        <v>467</v>
+      </c>
+      <c r="F414" t="s">
+        <v>110</v>
+      </c>
+      <c r="G414" t="s">
+        <v>761</v>
+      </c>
+      <c r="H414" t="s">
+        <v>148</v>
+      </c>
+      <c r="I414" t="s">
+        <v>149</v>
+      </c>
+      <c r="J414">
+        <v>25.98</v>
+      </c>
+      <c r="K414" t="s">
+        <v>22</v>
+      </c>
+      <c r="L414" t="s">
+        <v>708</v>
+      </c>
+      <c r="M414" t="s">
+        <v>18</v>
+      </c>
+      <c r="N414" t="s">
+        <v>534</v>
+      </c>
+      <c r="O414" t="s">
+        <v>20</v>
+      </c>
+      <c r="P414" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q414" t="s">
+        <v>760</v>
+      </c>
+      <c r="R414" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="415" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>206</v>
+      </c>
+      <c r="B415" t="s">
+        <v>207</v>
+      </c>
+      <c r="C415" t="s">
+        <v>215</v>
+      </c>
+      <c r="D415" t="s">
+        <v>216</v>
+      </c>
+      <c r="E415" t="s">
+        <v>32</v>
+      </c>
+      <c r="F415" t="s">
+        <v>33</v>
+      </c>
+      <c r="G415" t="s">
+        <v>715</v>
+      </c>
+      <c r="H415" t="s">
+        <v>57</v>
+      </c>
+      <c r="I415" t="s">
+        <v>58</v>
+      </c>
+      <c r="J415">
+        <v>31.56</v>
+      </c>
+      <c r="K415" t="s">
+        <v>23</v>
+      </c>
+      <c r="L415" t="s">
+        <v>708</v>
+      </c>
+      <c r="M415" t="s">
+        <v>18</v>
+      </c>
+      <c r="N415" t="s">
+        <v>534</v>
+      </c>
+      <c r="O415" t="s">
+        <v>20</v>
+      </c>
+      <c r="P415" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q415" t="s">
+        <v>764</v>
+      </c>
+      <c r="R415" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="416" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>206</v>
+      </c>
+      <c r="B416" t="s">
+        <v>207</v>
+      </c>
+      <c r="C416" t="s">
+        <v>208</v>
+      </c>
+      <c r="D416" t="s">
+        <v>209</v>
+      </c>
+      <c r="E416" t="s">
+        <v>210</v>
+      </c>
+      <c r="F416" t="s">
+        <v>118</v>
+      </c>
+      <c r="G416" t="s">
+        <v>707</v>
+      </c>
+      <c r="H416" t="s">
+        <v>57</v>
+      </c>
+      <c r="I416" t="s">
+        <v>58</v>
+      </c>
+      <c r="J416">
+        <v>31.56</v>
+      </c>
+      <c r="K416" t="s">
+        <v>23</v>
+      </c>
+      <c r="L416" t="s">
+        <v>708</v>
+      </c>
+      <c r="M416" t="s">
+        <v>18</v>
+      </c>
+      <c r="N416" t="s">
+        <v>534</v>
+      </c>
+      <c r="O416" t="s">
+        <v>20</v>
+      </c>
+      <c r="P416" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q416" t="s">
+        <v>764</v>
+      </c>
+      <c r="R416" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="417" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>206</v>
+      </c>
+      <c r="B417" t="s">
+        <v>207</v>
+      </c>
+      <c r="C417" t="s">
+        <v>212</v>
+      </c>
+      <c r="D417" t="s">
+        <v>213</v>
+      </c>
+      <c r="E417" t="s">
+        <v>214</v>
+      </c>
+      <c r="F417" t="s">
+        <v>70</v>
+      </c>
+      <c r="G417" t="s">
+        <v>707</v>
+      </c>
+      <c r="H417" t="s">
+        <v>57</v>
+      </c>
+      <c r="I417" t="s">
+        <v>58</v>
+      </c>
+      <c r="J417">
+        <v>31.56</v>
+      </c>
+      <c r="K417" t="s">
+        <v>23</v>
+      </c>
+      <c r="L417" t="s">
+        <v>708</v>
+      </c>
+      <c r="M417" t="s">
+        <v>18</v>
+      </c>
+      <c r="N417" t="s">
+        <v>534</v>
+      </c>
+      <c r="O417" t="s">
+        <v>20</v>
+      </c>
+      <c r="P417" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q417" t="s">
+        <v>764</v>
+      </c>
+      <c r="R417" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="418" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>206</v>
+      </c>
+      <c r="B418" t="s">
+        <v>207</v>
+      </c>
+      <c r="C418" t="s">
+        <v>233</v>
+      </c>
+      <c r="D418" t="s">
+        <v>222</v>
+      </c>
+      <c r="E418" t="s">
+        <v>234</v>
+      </c>
+      <c r="F418" t="s">
+        <v>110</v>
+      </c>
+      <c r="G418" t="s">
+        <v>710</v>
+      </c>
+      <c r="H418" t="s">
+        <v>57</v>
+      </c>
+      <c r="I418" t="s">
+        <v>58</v>
+      </c>
+      <c r="J418">
+        <v>63.12</v>
+      </c>
+      <c r="K418" t="s">
+        <v>22</v>
+      </c>
+      <c r="L418" t="s">
+        <v>708</v>
+      </c>
+      <c r="M418" t="s">
+        <v>18</v>
+      </c>
+      <c r="N418" t="s">
+        <v>534</v>
+      </c>
+      <c r="O418" t="s">
+        <v>20</v>
+      </c>
+      <c r="P418" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q418" t="s">
+        <v>764</v>
+      </c>
+      <c r="R418" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="419" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>206</v>
+      </c>
+      <c r="B419" t="s">
+        <v>207</v>
+      </c>
+      <c r="C419" t="s">
+        <v>215</v>
+      </c>
+      <c r="D419" t="s">
+        <v>216</v>
+      </c>
+      <c r="E419" t="s">
+        <v>32</v>
+      </c>
+      <c r="F419" t="s">
+        <v>33</v>
+      </c>
+      <c r="G419" t="s">
+        <v>715</v>
+      </c>
+      <c r="H419" t="s">
+        <v>73</v>
+      </c>
+      <c r="I419" t="s">
+        <v>74</v>
+      </c>
+      <c r="J419">
+        <v>68.2</v>
+      </c>
+      <c r="K419" t="s">
+        <v>40</v>
+      </c>
+      <c r="L419" t="s">
+        <v>708</v>
+      </c>
+      <c r="M419" t="s">
+        <v>18</v>
+      </c>
+      <c r="N419" t="s">
+        <v>534</v>
+      </c>
+      <c r="O419" t="s">
+        <v>20</v>
+      </c>
+      <c r="P419" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q419" t="s">
+        <v>765</v>
+      </c>
+      <c r="R419" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="420" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>206</v>
+      </c>
+      <c r="B420" t="s">
+        <v>207</v>
+      </c>
+      <c r="C420" t="s">
+        <v>208</v>
+      </c>
+      <c r="D420" t="s">
+        <v>209</v>
+      </c>
+      <c r="E420" t="s">
+        <v>210</v>
+      </c>
+      <c r="F420" t="s">
+        <v>118</v>
+      </c>
+      <c r="G420" t="s">
+        <v>707</v>
+      </c>
+      <c r="H420" t="s">
+        <v>73</v>
+      </c>
+      <c r="I420" t="s">
+        <v>74</v>
+      </c>
+      <c r="J420">
+        <v>17.05</v>
+      </c>
+      <c r="K420" t="s">
+        <v>23</v>
+      </c>
+      <c r="L420" t="s">
+        <v>708</v>
+      </c>
+      <c r="M420" t="s">
+        <v>18</v>
+      </c>
+      <c r="N420" t="s">
+        <v>534</v>
+      </c>
+      <c r="O420" t="s">
+        <v>20</v>
+      </c>
+      <c r="P420" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q420" t="s">
+        <v>765</v>
+      </c>
+      <c r="R420" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="421" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>206</v>
+      </c>
+      <c r="B421" t="s">
+        <v>207</v>
+      </c>
+      <c r="C421" t="s">
+        <v>212</v>
+      </c>
+      <c r="D421" t="s">
+        <v>213</v>
+      </c>
+      <c r="E421" t="s">
+        <v>214</v>
+      </c>
+      <c r="F421" t="s">
+        <v>70</v>
+      </c>
+      <c r="G421" t="s">
+        <v>707</v>
+      </c>
+      <c r="H421" t="s">
+        <v>73</v>
+      </c>
+      <c r="I421" t="s">
+        <v>74</v>
+      </c>
+      <c r="J421">
+        <v>51.15</v>
+      </c>
+      <c r="K421" t="s">
+        <v>50</v>
+      </c>
+      <c r="L421" t="s">
+        <v>708</v>
+      </c>
+      <c r="M421" t="s">
+        <v>18</v>
+      </c>
+      <c r="N421" t="s">
+        <v>534</v>
+      </c>
+      <c r="O421" t="s">
+        <v>20</v>
+      </c>
+      <c r="P421" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q421" t="s">
+        <v>765</v>
+      </c>
+      <c r="R421" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="422" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>206</v>
+      </c>
+      <c r="B422" t="s">
+        <v>207</v>
+      </c>
+      <c r="C422" t="s">
+        <v>233</v>
+      </c>
+      <c r="D422" t="s">
+        <v>222</v>
+      </c>
+      <c r="E422" t="s">
+        <v>234</v>
+      </c>
+      <c r="F422" t="s">
+        <v>110</v>
+      </c>
+      <c r="G422" t="s">
+        <v>754</v>
+      </c>
+      <c r="H422" t="s">
+        <v>73</v>
+      </c>
+      <c r="I422" t="s">
+        <v>74</v>
+      </c>
+      <c r="J422">
+        <v>34.1</v>
+      </c>
+      <c r="K422" t="s">
+        <v>22</v>
+      </c>
+      <c r="L422" t="s">
+        <v>708</v>
+      </c>
+      <c r="M422" t="s">
+        <v>18</v>
+      </c>
+      <c r="N422" t="s">
+        <v>534</v>
+      </c>
+      <c r="O422" t="s">
+        <v>20</v>
+      </c>
+      <c r="P422" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q422" t="s">
+        <v>765</v>
+      </c>
+      <c r="R422" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="423" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>206</v>
+      </c>
+      <c r="B423" t="s">
+        <v>207</v>
+      </c>
+      <c r="C423" t="s">
+        <v>233</v>
+      </c>
+      <c r="D423" t="s">
+        <v>222</v>
+      </c>
+      <c r="E423" t="s">
+        <v>234</v>
+      </c>
+      <c r="F423" t="s">
+        <v>110</v>
+      </c>
+      <c r="G423" t="s">
+        <v>735</v>
+      </c>
+      <c r="H423" t="s">
+        <v>73</v>
+      </c>
+      <c r="I423" t="s">
+        <v>74</v>
+      </c>
+      <c r="J423">
+        <v>51.15</v>
+      </c>
+      <c r="K423" t="s">
+        <v>50</v>
+      </c>
+      <c r="L423" t="s">
+        <v>708</v>
+      </c>
+      <c r="M423" t="s">
+        <v>18</v>
+      </c>
+      <c r="N423" t="s">
+        <v>534</v>
+      </c>
+      <c r="O423" t="s">
+        <v>20</v>
+      </c>
+      <c r="P423" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q423" t="s">
+        <v>765</v>
+      </c>
+      <c r="R423" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="424" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>206</v>
+      </c>
+      <c r="B424" t="s">
+        <v>207</v>
+      </c>
+      <c r="C424" t="s">
+        <v>215</v>
+      </c>
+      <c r="D424" t="s">
+        <v>216</v>
+      </c>
+      <c r="E424" t="s">
+        <v>32</v>
+      </c>
+      <c r="F424" t="s">
+        <v>33</v>
+      </c>
+      <c r="G424" t="s">
+        <v>715</v>
+      </c>
+      <c r="H424" t="s">
+        <v>85</v>
+      </c>
+      <c r="I424" t="s">
+        <v>86</v>
+      </c>
+      <c r="J424">
+        <v>16.54</v>
+      </c>
+      <c r="K424" t="s">
+        <v>22</v>
+      </c>
+      <c r="L424" t="s">
+        <v>708</v>
+      </c>
+      <c r="M424" t="s">
+        <v>18</v>
+      </c>
+      <c r="N424" t="s">
+        <v>534</v>
+      </c>
+      <c r="O424" t="s">
+        <v>20</v>
+      </c>
+      <c r="P424" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q424" t="s">
+        <v>766</v>
+      </c>
+      <c r="R424" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="425" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>206</v>
+      </c>
+      <c r="B425" t="s">
+        <v>207</v>
+      </c>
+      <c r="C425" t="s">
+        <v>208</v>
+      </c>
+      <c r="D425" t="s">
+        <v>209</v>
+      </c>
+      <c r="E425" t="s">
+        <v>210</v>
+      </c>
+      <c r="F425" t="s">
+        <v>118</v>
+      </c>
+      <c r="G425" t="s">
+        <v>707</v>
+      </c>
+      <c r="H425" t="s">
+        <v>85</v>
+      </c>
+      <c r="I425" t="s">
+        <v>86</v>
+      </c>
+      <c r="J425">
+        <v>8.27</v>
+      </c>
+      <c r="K425" t="s">
+        <v>23</v>
+      </c>
+      <c r="L425" t="s">
+        <v>708</v>
+      </c>
+      <c r="M425" t="s">
+        <v>18</v>
+      </c>
+      <c r="N425" t="s">
+        <v>534</v>
+      </c>
+      <c r="O425" t="s">
+        <v>20</v>
+      </c>
+      <c r="P425" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q425" t="s">
+        <v>766</v>
+      </c>
+      <c r="R425" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="426" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>206</v>
+      </c>
+      <c r="B426" t="s">
+        <v>207</v>
+      </c>
+      <c r="C426" t="s">
+        <v>215</v>
+      </c>
+      <c r="D426" t="s">
+        <v>216</v>
+      </c>
+      <c r="E426" t="s">
+        <v>32</v>
+      </c>
+      <c r="F426" t="s">
+        <v>33</v>
+      </c>
+      <c r="G426" t="s">
+        <v>732</v>
+      </c>
+      <c r="H426" t="s">
+        <v>767</v>
+      </c>
+      <c r="I426" t="s">
+        <v>768</v>
+      </c>
+      <c r="J426">
+        <v>21.49</v>
+      </c>
+      <c r="K426" t="s">
+        <v>23</v>
+      </c>
+      <c r="L426" t="s">
+        <v>708</v>
+      </c>
+      <c r="M426" t="s">
+        <v>18</v>
+      </c>
+      <c r="N426" t="s">
+        <v>534</v>
+      </c>
+      <c r="O426" t="s">
+        <v>20</v>
+      </c>
+      <c r="P426" t="s">
+        <v>769</v>
+      </c>
+      <c r="Q426" t="s">
+        <v>770</v>
+      </c>
+      <c r="R426" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="427" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>206</v>
+      </c>
+      <c r="B427" t="s">
+        <v>207</v>
+      </c>
+      <c r="C427" t="s">
+        <v>212</v>
+      </c>
+      <c r="D427" t="s">
+        <v>213</v>
+      </c>
+      <c r="E427" t="s">
+        <v>214</v>
+      </c>
+      <c r="F427" t="s">
+        <v>70</v>
+      </c>
+      <c r="G427" t="s">
+        <v>710</v>
+      </c>
+      <c r="H427" t="s">
+        <v>771</v>
+      </c>
+      <c r="I427" t="s">
+        <v>772</v>
+      </c>
+      <c r="J427">
+        <v>19.63</v>
+      </c>
+      <c r="K427" t="s">
+        <v>23</v>
+      </c>
+      <c r="L427" t="s">
+        <v>708</v>
+      </c>
+      <c r="M427" t="s">
+        <v>18</v>
+      </c>
+      <c r="N427" t="s">
+        <v>534</v>
+      </c>
+      <c r="O427" t="s">
+        <v>20</v>
+      </c>
+      <c r="P427" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q427" t="s">
+        <v>774</v>
+      </c>
+      <c r="R427" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="428" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>206</v>
+      </c>
+      <c r="B428" t="s">
+        <v>207</v>
+      </c>
+      <c r="C428" t="s">
+        <v>221</v>
+      </c>
+      <c r="D428" t="s">
+        <v>222</v>
+      </c>
+      <c r="E428" t="s">
+        <v>223</v>
+      </c>
+      <c r="F428" t="s">
+        <v>151</v>
+      </c>
+      <c r="G428" t="s">
+        <v>735</v>
+      </c>
+      <c r="H428" t="s">
+        <v>107</v>
+      </c>
+      <c r="I428" t="s">
+        <v>108</v>
+      </c>
+      <c r="J428">
+        <v>19.14</v>
+      </c>
+      <c r="K428" t="s">
+        <v>23</v>
+      </c>
+      <c r="L428" t="s">
+        <v>708</v>
+      </c>
+      <c r="M428" t="s">
+        <v>18</v>
+      </c>
+      <c r="N428" t="s">
+        <v>534</v>
+      </c>
+      <c r="O428" t="s">
+        <v>20</v>
+      </c>
+      <c r="P428" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q428" t="s">
+        <v>775</v>
+      </c>
+      <c r="R428" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="429" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>206</v>
+      </c>
+      <c r="B429" t="s">
+        <v>207</v>
+      </c>
+      <c r="C429" t="s">
+        <v>208</v>
+      </c>
+      <c r="D429" t="s">
+        <v>209</v>
+      </c>
+      <c r="E429" t="s">
+        <v>210</v>
+      </c>
+      <c r="F429" t="s">
+        <v>118</v>
+      </c>
+      <c r="G429" t="s">
+        <v>707</v>
+      </c>
+      <c r="H429" t="s">
+        <v>38</v>
+      </c>
+      <c r="I429" t="s">
+        <v>39</v>
+      </c>
+      <c r="J429">
+        <v>19.62</v>
+      </c>
+      <c r="K429" t="s">
+        <v>23</v>
+      </c>
+      <c r="L429" t="s">
+        <v>708</v>
+      </c>
+      <c r="M429" t="s">
+        <v>18</v>
+      </c>
+      <c r="N429" t="s">
+        <v>534</v>
+      </c>
+      <c r="O429" t="s">
+        <v>20</v>
+      </c>
+      <c r="P429" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q429" t="s">
+        <v>776</v>
+      </c>
+      <c r="R429" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="430" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>206</v>
+      </c>
+      <c r="B430" t="s">
+        <v>207</v>
+      </c>
+      <c r="C430" t="s">
+        <v>221</v>
+      </c>
+      <c r="D430" t="s">
+        <v>222</v>
+      </c>
+      <c r="E430" t="s">
+        <v>223</v>
+      </c>
+      <c r="F430" t="s">
+        <v>151</v>
+      </c>
+      <c r="G430" t="s">
+        <v>762</v>
+      </c>
+      <c r="H430" t="s">
+        <v>579</v>
+      </c>
+      <c r="I430" t="s">
+        <v>580</v>
+      </c>
+      <c r="J430">
+        <v>16.77</v>
+      </c>
+      <c r="K430" t="s">
+        <v>23</v>
+      </c>
+      <c r="L430" t="s">
+        <v>708</v>
+      </c>
+      <c r="M430" t="s">
+        <v>18</v>
+      </c>
+      <c r="N430" t="s">
+        <v>534</v>
+      </c>
+      <c r="O430" t="s">
+        <v>20</v>
+      </c>
+      <c r="P430" t="s">
+        <v>582</v>
+      </c>
+      <c r="Q430" t="s">
+        <v>777</v>
+      </c>
+      <c r="R430" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="431" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>206</v>
+      </c>
+      <c r="B431" t="s">
+        <v>207</v>
+      </c>
+      <c r="C431" t="s">
+        <v>208</v>
+      </c>
+      <c r="D431" t="s">
+        <v>209</v>
+      </c>
+      <c r="E431" t="s">
+        <v>210</v>
+      </c>
+      <c r="F431" t="s">
+        <v>118</v>
+      </c>
+      <c r="G431" t="s">
+        <v>707</v>
+      </c>
+      <c r="H431" t="s">
+        <v>180</v>
+      </c>
+      <c r="I431" t="s">
+        <v>181</v>
+      </c>
+      <c r="J431">
+        <v>49.98</v>
+      </c>
+      <c r="K431" t="s">
+        <v>22</v>
+      </c>
+      <c r="L431" t="s">
+        <v>708</v>
+      </c>
+      <c r="M431" t="s">
+        <v>18</v>
+      </c>
+      <c r="N431" t="s">
+        <v>534</v>
+      </c>
+      <c r="O431" t="s">
+        <v>20</v>
+      </c>
+      <c r="P431" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q431" t="s">
+        <v>778</v>
+      </c>
+      <c r="R431" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="432" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>206</v>
+      </c>
+      <c r="B432" t="s">
+        <v>207</v>
+      </c>
+      <c r="C432" t="s">
+        <v>215</v>
+      </c>
+      <c r="D432" t="s">
+        <v>216</v>
+      </c>
+      <c r="E432" t="s">
+        <v>32</v>
+      </c>
+      <c r="F432" t="s">
+        <v>33</v>
+      </c>
+      <c r="G432" t="s">
+        <v>715</v>
+      </c>
+      <c r="H432" t="s">
+        <v>483</v>
+      </c>
+      <c r="I432" t="s">
+        <v>484</v>
+      </c>
+      <c r="J432">
+        <v>20.34</v>
+      </c>
+      <c r="K432" t="s">
+        <v>23</v>
+      </c>
+      <c r="L432" t="s">
+        <v>708</v>
+      </c>
+      <c r="M432" t="s">
+        <v>18</v>
+      </c>
+      <c r="N432" t="s">
+        <v>534</v>
+      </c>
+      <c r="O432" t="s">
+        <v>20</v>
+      </c>
+      <c r="P432" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q432" t="s">
+        <v>779</v>
+      </c>
+      <c r="R432" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="433" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>206</v>
+      </c>
+      <c r="B433" t="s">
+        <v>207</v>
+      </c>
+      <c r="C433" t="s">
+        <v>215</v>
+      </c>
+      <c r="D433" t="s">
+        <v>216</v>
+      </c>
+      <c r="E433" t="s">
+        <v>32</v>
+      </c>
+      <c r="F433" t="s">
+        <v>33</v>
+      </c>
+      <c r="G433" t="s">
+        <v>715</v>
+      </c>
+      <c r="H433" t="s">
+        <v>43</v>
+      </c>
+      <c r="I433" t="s">
+        <v>44</v>
+      </c>
+      <c r="J433">
+        <v>13.58</v>
+      </c>
+      <c r="K433" t="s">
+        <v>23</v>
+      </c>
+      <c r="L433" t="s">
+        <v>708</v>
+      </c>
+      <c r="M433" t="s">
+        <v>18</v>
+      </c>
+      <c r="N433" t="s">
+        <v>534</v>
+      </c>
+      <c r="O433" t="s">
+        <v>20</v>
+      </c>
+      <c r="P433" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q433" t="s">
+        <v>780</v>
+      </c>
+      <c r="R433" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="434" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>206</v>
+      </c>
+      <c r="B434" t="s">
+        <v>207</v>
+      </c>
+      <c r="C434" t="s">
+        <v>208</v>
+      </c>
+      <c r="D434" t="s">
+        <v>209</v>
+      </c>
+      <c r="E434" t="s">
+        <v>210</v>
+      </c>
+      <c r="F434" t="s">
+        <v>118</v>
+      </c>
+      <c r="G434" t="s">
+        <v>725</v>
+      </c>
+      <c r="H434" t="s">
+        <v>43</v>
+      </c>
+      <c r="I434" t="s">
+        <v>44</v>
+      </c>
+      <c r="J434">
+        <v>-13.58</v>
+      </c>
+      <c r="K434" t="s">
+        <v>581</v>
+      </c>
+      <c r="L434" t="s">
+        <v>708</v>
+      </c>
+      <c r="M434" t="s">
+        <v>18</v>
+      </c>
+      <c r="N434" t="s">
+        <v>534</v>
+      </c>
+      <c r="O434" t="s">
+        <v>20</v>
+      </c>
+      <c r="P434" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q434" t="s">
+        <v>780</v>
+      </c>
+      <c r="R434" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="435" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>206</v>
+      </c>
+      <c r="B435" t="s">
+        <v>207</v>
+      </c>
+      <c r="C435" t="s">
+        <v>208</v>
+      </c>
+      <c r="D435" t="s">
+        <v>209</v>
+      </c>
+      <c r="E435" t="s">
+        <v>210</v>
+      </c>
+      <c r="F435" t="s">
+        <v>118</v>
+      </c>
+      <c r="G435" t="s">
+        <v>707</v>
+      </c>
+      <c r="H435" t="s">
+        <v>43</v>
+      </c>
+      <c r="I435" t="s">
+        <v>44</v>
+      </c>
+      <c r="J435">
+        <v>13.58</v>
+      </c>
+      <c r="K435" t="s">
+        <v>23</v>
+      </c>
+      <c r="L435" t="s">
+        <v>708</v>
+      </c>
+      <c r="M435" t="s">
+        <v>18</v>
+      </c>
+      <c r="N435" t="s">
+        <v>534</v>
+      </c>
+      <c r="O435" t="s">
+        <v>20</v>
+      </c>
+      <c r="P435" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q435" t="s">
+        <v>780</v>
+      </c>
+      <c r="R435" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="436" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>206</v>
+      </c>
+      <c r="B436" t="s">
+        <v>207</v>
+      </c>
+      <c r="C436" t="s">
+        <v>251</v>
+      </c>
+      <c r="D436" t="s">
+        <v>252</v>
+      </c>
+      <c r="E436" t="s">
+        <v>198</v>
+      </c>
+      <c r="F436" t="s">
+        <v>119</v>
+      </c>
+      <c r="G436" t="s">
+        <v>732</v>
+      </c>
+      <c r="H436" t="s">
+        <v>43</v>
+      </c>
+      <c r="I436" t="s">
+        <v>44</v>
+      </c>
+      <c r="J436">
+        <v>13.58</v>
+      </c>
+      <c r="K436" t="s">
+        <v>23</v>
+      </c>
+      <c r="L436" t="s">
+        <v>708</v>
+      </c>
+      <c r="M436" t="s">
+        <v>18</v>
+      </c>
+      <c r="N436" t="s">
+        <v>534</v>
+      </c>
+      <c r="O436" t="s">
+        <v>20</v>
+      </c>
+      <c r="P436" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q436" t="s">
+        <v>780</v>
+      </c>
+      <c r="R436" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="437" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>206</v>
+      </c>
+      <c r="B437" t="s">
+        <v>207</v>
+      </c>
+      <c r="C437" t="s">
+        <v>208</v>
+      </c>
+      <c r="D437" t="s">
+        <v>209</v>
+      </c>
+      <c r="E437" t="s">
+        <v>210</v>
+      </c>
+      <c r="F437" t="s">
+        <v>118</v>
+      </c>
+      <c r="G437" t="s">
+        <v>735</v>
+      </c>
+      <c r="H437" t="s">
+        <v>359</v>
+      </c>
+      <c r="I437" t="s">
+        <v>360</v>
+      </c>
+      <c r="J437">
+        <v>13.65</v>
+      </c>
+      <c r="K437" t="s">
+        <v>23</v>
+      </c>
+      <c r="L437" t="s">
+        <v>708</v>
+      </c>
+      <c r="M437" t="s">
+        <v>18</v>
+      </c>
+      <c r="N437" t="s">
+        <v>534</v>
+      </c>
+      <c r="O437" t="s">
+        <v>20</v>
+      </c>
+      <c r="P437" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q437" t="s">
+        <v>781</v>
+      </c>
+      <c r="R437" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="438" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>206</v>
+      </c>
+      <c r="B438" t="s">
+        <v>207</v>
+      </c>
+      <c r="C438" t="s">
+        <v>251</v>
+      </c>
+      <c r="D438" t="s">
+        <v>252</v>
+      </c>
+      <c r="E438" t="s">
+        <v>198</v>
+      </c>
+      <c r="F438" t="s">
+        <v>119</v>
+      </c>
+      <c r="G438" t="s">
+        <v>735</v>
+      </c>
+      <c r="H438" t="s">
+        <v>359</v>
+      </c>
+      <c r="I438" t="s">
+        <v>360</v>
+      </c>
+      <c r="J438">
+        <v>-27.3</v>
+      </c>
+      <c r="K438" t="s">
+        <v>782</v>
+      </c>
+      <c r="L438" t="s">
+        <v>708</v>
+      </c>
+      <c r="M438" t="s">
+        <v>18</v>
+      </c>
+      <c r="N438" t="s">
+        <v>534</v>
+      </c>
+      <c r="O438" t="s">
+        <v>20</v>
+      </c>
+      <c r="P438" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q438" t="s">
+        <v>781</v>
+      </c>
+      <c r="R438" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="439" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>206</v>
+      </c>
+      <c r="B439" t="s">
+        <v>207</v>
+      </c>
+      <c r="C439" t="s">
+        <v>215</v>
+      </c>
+      <c r="D439" t="s">
+        <v>216</v>
+      </c>
+      <c r="E439" t="s">
+        <v>32</v>
+      </c>
+      <c r="F439" t="s">
+        <v>33</v>
+      </c>
+      <c r="G439" t="s">
+        <v>727</v>
+      </c>
+      <c r="H439" t="s">
+        <v>658</v>
+      </c>
+      <c r="I439" t="s">
+        <v>659</v>
+      </c>
+      <c r="J439">
+        <v>118.08</v>
+      </c>
+      <c r="K439" t="s">
+        <v>783</v>
+      </c>
+      <c r="L439" t="s">
+        <v>708</v>
+      </c>
+      <c r="M439" t="s">
+        <v>18</v>
+      </c>
+      <c r="N439" t="s">
+        <v>534</v>
+      </c>
+      <c r="O439" t="s">
+        <v>20</v>
+      </c>
+      <c r="P439" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q439" t="s">
+        <v>661</v>
+      </c>
+      <c r="R439" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="440" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>206</v>
+      </c>
+      <c r="B440" t="s">
+        <v>207</v>
+      </c>
+      <c r="C440" t="s">
+        <v>208</v>
+      </c>
+      <c r="D440" t="s">
+        <v>209</v>
+      </c>
+      <c r="E440" t="s">
+        <v>210</v>
+      </c>
+      <c r="F440" t="s">
+        <v>118</v>
+      </c>
+      <c r="G440" t="s">
+        <v>710</v>
+      </c>
+      <c r="H440" t="s">
+        <v>658</v>
+      </c>
+      <c r="I440" t="s">
+        <v>659</v>
+      </c>
+      <c r="J440">
+        <v>39.36</v>
+      </c>
+      <c r="K440" t="s">
+        <v>27</v>
+      </c>
+      <c r="L440" t="s">
+        <v>708</v>
+      </c>
+      <c r="M440" t="s">
+        <v>18</v>
+      </c>
+      <c r="N440" t="s">
+        <v>534</v>
+      </c>
+      <c r="O440" t="s">
+        <v>20</v>
+      </c>
+      <c r="P440" t="s">
+        <v>660</v>
+      </c>
+      <c r="Q440" t="s">
+        <v>661</v>
+      </c>
+      <c r="R440" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="441" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>206</v>
+      </c>
+      <c r="B441" t="s">
+        <v>207</v>
+      </c>
+      <c r="C441" t="s">
+        <v>215</v>
+      </c>
+      <c r="D441" t="s">
+        <v>216</v>
+      </c>
+      <c r="E441" t="s">
+        <v>32</v>
+      </c>
+      <c r="F441" t="s">
+        <v>33</v>
+      </c>
+      <c r="G441" t="s">
+        <v>715</v>
+      </c>
+      <c r="H441" t="s">
+        <v>153</v>
+      </c>
+      <c r="I441" t="s">
+        <v>154</v>
+      </c>
+      <c r="J441">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="K441" t="s">
+        <v>23</v>
+      </c>
+      <c r="L441" t="s">
+        <v>708</v>
+      </c>
+      <c r="M441" t="s">
+        <v>18</v>
+      </c>
+      <c r="N441" t="s">
+        <v>534</v>
+      </c>
+      <c r="O441" t="s">
+        <v>20</v>
+      </c>
+      <c r="P441" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q441" t="s">
+        <v>784</v>
+      </c>
+      <c r="R441" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="442" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>206</v>
+      </c>
+      <c r="B442" t="s">
+        <v>207</v>
+      </c>
+      <c r="C442" t="s">
+        <v>251</v>
+      </c>
+      <c r="D442" t="s">
+        <v>252</v>
+      </c>
+      <c r="E442" t="s">
+        <v>198</v>
+      </c>
+      <c r="F442" t="s">
+        <v>119</v>
+      </c>
+      <c r="G442" t="s">
+        <v>735</v>
+      </c>
+      <c r="H442" t="s">
+        <v>368</v>
+      </c>
+      <c r="I442" t="s">
+        <v>369</v>
+      </c>
+      <c r="J442">
+        <v>-19.46</v>
+      </c>
+      <c r="K442" t="s">
+        <v>581</v>
+      </c>
+      <c r="L442" t="s">
+        <v>708</v>
+      </c>
+      <c r="M442" t="s">
+        <v>18</v>
+      </c>
+      <c r="N442" t="s">
+        <v>534</v>
+      </c>
+      <c r="O442" t="s">
+        <v>20</v>
+      </c>
+      <c r="P442" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q442" t="s">
+        <v>785</v>
+      </c>
+      <c r="R442" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="443" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>206</v>
+      </c>
+      <c r="B443" t="s">
+        <v>207</v>
+      </c>
+      <c r="C443" t="s">
+        <v>208</v>
+      </c>
+      <c r="D443" t="s">
+        <v>209</v>
+      </c>
+      <c r="E443" t="s">
+        <v>210</v>
+      </c>
+      <c r="F443" t="s">
+        <v>118</v>
+      </c>
+      <c r="G443" t="s">
+        <v>733</v>
+      </c>
+      <c r="H443" t="s">
+        <v>786</v>
+      </c>
+      <c r="I443" t="s">
+        <v>787</v>
+      </c>
+      <c r="J443">
+        <v>77.760000000000005</v>
+      </c>
+      <c r="K443" t="s">
+        <v>23</v>
+      </c>
+      <c r="L443" t="s">
+        <v>708</v>
+      </c>
+      <c r="M443" t="s">
+        <v>18</v>
+      </c>
+      <c r="N443" t="s">
+        <v>534</v>
+      </c>
+      <c r="O443" t="s">
+        <v>20</v>
+      </c>
+      <c r="P443" t="s">
+        <v>788</v>
+      </c>
+      <c r="Q443" t="s">
+        <v>789</v>
+      </c>
+      <c r="R443" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="444" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>206</v>
+      </c>
+      <c r="B444" t="s">
+        <v>207</v>
+      </c>
+      <c r="C444" t="s">
+        <v>208</v>
+      </c>
+      <c r="D444" t="s">
+        <v>209</v>
+      </c>
+      <c r="E444" t="s">
+        <v>210</v>
+      </c>
+      <c r="F444" t="s">
+        <v>118</v>
+      </c>
+      <c r="G444" t="s">
+        <v>733</v>
+      </c>
+      <c r="H444" t="s">
+        <v>790</v>
+      </c>
+      <c r="I444" t="s">
+        <v>791</v>
+      </c>
+      <c r="J444">
+        <v>112</v>
+      </c>
+      <c r="K444" t="s">
+        <v>23</v>
+      </c>
+      <c r="L444" t="s">
+        <v>708</v>
+      </c>
+      <c r="M444" t="s">
+        <v>18</v>
+      </c>
+      <c r="N444" t="s">
+        <v>534</v>
+      </c>
+      <c r="O444" t="s">
+        <v>20</v>
+      </c>
+      <c r="P444" t="s">
+        <v>792</v>
+      </c>
+      <c r="Q444" t="s">
+        <v>793</v>
+      </c>
+      <c r="R444" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="445" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>206</v>
+      </c>
+      <c r="B445" t="s">
+        <v>207</v>
+      </c>
+      <c r="C445" t="s">
+        <v>251</v>
+      </c>
+      <c r="D445" t="s">
+        <v>252</v>
+      </c>
+      <c r="E445" t="s">
+        <v>198</v>
+      </c>
+      <c r="F445" t="s">
+        <v>119</v>
+      </c>
+      <c r="G445" t="s">
+        <v>722</v>
+      </c>
+      <c r="H445" t="s">
+        <v>662</v>
+      </c>
+      <c r="I445" t="s">
+        <v>663</v>
+      </c>
+      <c r="J445">
+        <v>13.4</v>
+      </c>
+      <c r="K445" t="s">
+        <v>23</v>
+      </c>
+      <c r="L445" t="s">
+        <v>708</v>
+      </c>
+      <c r="M445" t="s">
+        <v>18</v>
+      </c>
+      <c r="N445" t="s">
+        <v>534</v>
+      </c>
+      <c r="O445" t="s">
+        <v>20</v>
+      </c>
+      <c r="P445" t="s">
+        <v>664</v>
+      </c>
+      <c r="Q445" t="s">
+        <v>665</v>
+      </c>
+      <c r="R445" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="446" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>206</v>
+      </c>
+      <c r="B446" t="s">
+        <v>207</v>
+      </c>
+      <c r="C446" t="s">
+        <v>212</v>
+      </c>
+      <c r="D446" t="s">
+        <v>213</v>
+      </c>
+      <c r="E446" t="s">
+        <v>214</v>
+      </c>
+      <c r="F446" t="s">
+        <v>70</v>
+      </c>
+      <c r="G446" t="s">
+        <v>707</v>
+      </c>
+      <c r="H446" t="s">
+        <v>156</v>
+      </c>
+      <c r="I446" t="s">
+        <v>157</v>
+      </c>
+      <c r="J446">
+        <v>28.19</v>
+      </c>
+      <c r="K446" t="s">
+        <v>23</v>
+      </c>
+      <c r="L446" t="s">
+        <v>708</v>
+      </c>
+      <c r="M446" t="s">
+        <v>18</v>
+      </c>
+      <c r="N446" t="s">
+        <v>534</v>
+      </c>
+      <c r="O446" t="s">
+        <v>20</v>
+      </c>
+      <c r="P446" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q446" t="s">
+        <v>794</v>
+      </c>
+      <c r="R446" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="447" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>206</v>
+      </c>
+      <c r="B447" t="s">
+        <v>207</v>
+      </c>
+      <c r="C447" t="s">
+        <v>251</v>
+      </c>
+      <c r="D447" t="s">
+        <v>252</v>
+      </c>
+      <c r="E447" t="s">
+        <v>198</v>
+      </c>
+      <c r="F447" t="s">
+        <v>119</v>
+      </c>
+      <c r="G447" t="s">
+        <v>754</v>
+      </c>
+      <c r="H447" t="s">
+        <v>123</v>
+      </c>
+      <c r="I447" t="s">
+        <v>124</v>
+      </c>
+      <c r="J447">
+        <v>28.17</v>
+      </c>
+      <c r="K447" t="s">
+        <v>23</v>
+      </c>
+      <c r="L447" t="s">
+        <v>708</v>
+      </c>
+      <c r="M447" t="s">
+        <v>18</v>
+      </c>
+      <c r="N447" t="s">
+        <v>534</v>
+      </c>
+      <c r="O447" t="s">
+        <v>20</v>
+      </c>
+      <c r="P447" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q447" t="s">
+        <v>795</v>
+      </c>
+      <c r="R447" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="448" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>206</v>
+      </c>
+      <c r="B448" t="s">
+        <v>207</v>
+      </c>
+      <c r="C448" t="s">
+        <v>208</v>
+      </c>
+      <c r="D448" t="s">
+        <v>209</v>
+      </c>
+      <c r="E448" t="s">
+        <v>210</v>
+      </c>
+      <c r="F448" t="s">
+        <v>118</v>
+      </c>
+      <c r="G448" t="s">
+        <v>707</v>
+      </c>
+      <c r="H448" t="s">
+        <v>159</v>
+      </c>
+      <c r="I448" t="s">
+        <v>160</v>
+      </c>
+      <c r="J448">
+        <v>28.22</v>
+      </c>
+      <c r="K448" t="s">
+        <v>23</v>
+      </c>
+      <c r="L448" t="s">
+        <v>708</v>
+      </c>
+      <c r="M448" t="s">
+        <v>18</v>
+      </c>
+      <c r="N448" t="s">
+        <v>534</v>
+      </c>
+      <c r="O448" t="s">
+        <v>20</v>
+      </c>
+      <c r="P448" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q448" t="s">
+        <v>410</v>
+      </c>
+      <c r="R448" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="449" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>206</v>
+      </c>
+      <c r="B449" t="s">
+        <v>207</v>
+      </c>
+      <c r="C449" t="s">
+        <v>208</v>
+      </c>
+      <c r="D449" t="s">
+        <v>209</v>
+      </c>
+      <c r="E449" t="s">
+        <v>210</v>
+      </c>
+      <c r="F449" t="s">
+        <v>118</v>
+      </c>
+      <c r="G449" t="s">
+        <v>796</v>
+      </c>
+      <c r="H449" t="s">
+        <v>159</v>
+      </c>
+      <c r="I449" t="s">
+        <v>160</v>
+      </c>
+      <c r="J449">
+        <v>28.22</v>
+      </c>
+      <c r="K449" t="s">
+        <v>23</v>
+      </c>
+      <c r="L449" t="s">
+        <v>708</v>
+      </c>
+      <c r="M449" t="s">
+        <v>18</v>
+      </c>
+      <c r="N449" t="s">
+        <v>534</v>
+      </c>
+      <c r="O449" t="s">
+        <v>20</v>
+      </c>
+      <c r="P449" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q449" t="s">
+        <v>410</v>
+      </c>
+      <c r="R449" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="450" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>206</v>
+      </c>
+      <c r="B450" t="s">
+        <v>207</v>
+      </c>
+      <c r="C450" t="s">
+        <v>215</v>
+      </c>
+      <c r="D450" t="s">
+        <v>216</v>
+      </c>
+      <c r="E450" t="s">
+        <v>32</v>
+      </c>
+      <c r="F450" t="s">
+        <v>33</v>
+      </c>
+      <c r="G450" t="s">
+        <v>715</v>
+      </c>
+      <c r="H450" t="s">
+        <v>126</v>
+      </c>
+      <c r="I450" t="s">
+        <v>127</v>
+      </c>
+      <c r="J450">
+        <v>28.04</v>
+      </c>
+      <c r="K450" t="s">
+        <v>23</v>
+      </c>
+      <c r="L450" t="s">
+        <v>708</v>
+      </c>
+      <c r="M450" t="s">
+        <v>18</v>
+      </c>
+      <c r="N450" t="s">
+        <v>534</v>
+      </c>
+      <c r="O450" t="s">
+        <v>20</v>
+      </c>
+      <c r="P450" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q450" t="s">
+        <v>797</v>
+      </c>
+      <c r="R450" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="451" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>206</v>
+      </c>
+      <c r="B451" t="s">
+        <v>207</v>
+      </c>
+      <c r="C451" t="s">
+        <v>212</v>
+      </c>
+      <c r="D451" t="s">
+        <v>213</v>
+      </c>
+      <c r="E451" t="s">
+        <v>214</v>
+      </c>
+      <c r="F451" t="s">
+        <v>70</v>
+      </c>
+      <c r="G451" t="s">
+        <v>707</v>
+      </c>
+      <c r="H451" t="s">
+        <v>126</v>
+      </c>
+      <c r="I451" t="s">
+        <v>127</v>
+      </c>
+      <c r="J451">
+        <v>56.08</v>
+      </c>
+      <c r="K451" t="s">
+        <v>22</v>
+      </c>
+      <c r="L451" t="s">
+        <v>708</v>
+      </c>
+      <c r="M451" t="s">
+        <v>18</v>
+      </c>
+      <c r="N451" t="s">
+        <v>534</v>
+      </c>
+      <c r="O451" t="s">
+        <v>20</v>
+      </c>
+      <c r="P451" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q451" t="s">
+        <v>797</v>
+      </c>
+      <c r="R451" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="452" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>206</v>
+      </c>
+      <c r="B452" t="s">
+        <v>207</v>
+      </c>
+      <c r="C452" t="s">
+        <v>215</v>
+      </c>
+      <c r="D452" t="s">
+        <v>216</v>
+      </c>
+      <c r="E452" t="s">
+        <v>32</v>
+      </c>
+      <c r="F452" t="s">
+        <v>33</v>
+      </c>
+      <c r="G452" t="s">
+        <v>715</v>
+      </c>
+      <c r="H452" t="s">
+        <v>186</v>
+      </c>
+      <c r="I452" t="s">
+        <v>187</v>
+      </c>
+      <c r="J452">
+        <v>31.13</v>
+      </c>
+      <c r="K452" t="s">
+        <v>23</v>
+      </c>
+      <c r="L452" t="s">
+        <v>708</v>
+      </c>
+      <c r="M452" t="s">
+        <v>18</v>
+      </c>
+      <c r="N452" t="s">
+        <v>534</v>
+      </c>
+      <c r="O452" t="s">
+        <v>20</v>
+      </c>
+      <c r="P452" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q452" t="s">
+        <v>798</v>
+      </c>
+      <c r="R452" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="453" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>206</v>
+      </c>
+      <c r="B453" t="s">
+        <v>207</v>
+      </c>
+      <c r="C453" t="s">
+        <v>212</v>
+      </c>
+      <c r="D453" t="s">
+        <v>213</v>
+      </c>
+      <c r="E453" t="s">
+        <v>214</v>
+      </c>
+      <c r="F453" t="s">
+        <v>70</v>
+      </c>
+      <c r="G453" t="s">
+        <v>707</v>
+      </c>
+      <c r="H453" t="s">
+        <v>186</v>
+      </c>
+      <c r="I453" t="s">
+        <v>187</v>
+      </c>
+      <c r="J453">
+        <v>31.13</v>
+      </c>
+      <c r="K453" t="s">
+        <v>23</v>
+      </c>
+      <c r="L453" t="s">
+        <v>708</v>
+      </c>
+      <c r="M453" t="s">
+        <v>18</v>
+      </c>
+      <c r="N453" t="s">
+        <v>534</v>
+      </c>
+      <c r="O453" t="s">
+        <v>20</v>
+      </c>
+      <c r="P453" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q453" t="s">
+        <v>798</v>
+      </c>
+      <c r="R453" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="454" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>206</v>
+      </c>
+      <c r="B454" t="s">
+        <v>207</v>
+      </c>
+      <c r="C454" t="s">
+        <v>215</v>
+      </c>
+      <c r="D454" t="s">
+        <v>216</v>
+      </c>
+      <c r="E454" t="s">
+        <v>32</v>
+      </c>
+      <c r="F454" t="s">
+        <v>33</v>
+      </c>
+      <c r="G454" t="s">
+        <v>715</v>
+      </c>
+      <c r="H454" t="s">
+        <v>507</v>
+      </c>
+      <c r="I454" t="s">
+        <v>508</v>
+      </c>
+      <c r="J454">
+        <v>31.05</v>
+      </c>
+      <c r="K454" t="s">
+        <v>23</v>
+      </c>
+      <c r="L454" t="s">
+        <v>708</v>
+      </c>
+      <c r="M454" t="s">
+        <v>18</v>
+      </c>
+      <c r="N454" t="s">
+        <v>534</v>
+      </c>
+      <c r="O454" t="s">
+        <v>20</v>
+      </c>
+      <c r="P454" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q454" t="s">
+        <v>799</v>
+      </c>
+      <c r="R454" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="455" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>206</v>
+      </c>
+      <c r="B455" t="s">
+        <v>207</v>
+      </c>
+      <c r="C455" t="s">
+        <v>251</v>
+      </c>
+      <c r="D455" t="s">
+        <v>252</v>
+      </c>
+      <c r="E455" t="s">
+        <v>198</v>
+      </c>
+      <c r="F455" t="s">
+        <v>119</v>
+      </c>
+      <c r="G455" t="s">
+        <v>796</v>
+      </c>
+      <c r="H455" t="s">
+        <v>511</v>
+      </c>
+      <c r="I455" t="s">
+        <v>512</v>
+      </c>
+      <c r="J455">
+        <v>15.28</v>
+      </c>
+      <c r="K455" t="s">
+        <v>22</v>
+      </c>
+      <c r="L455" t="s">
+        <v>708</v>
+      </c>
+      <c r="M455" t="s">
+        <v>18</v>
+      </c>
+      <c r="N455" t="s">
+        <v>534</v>
+      </c>
+      <c r="O455" t="s">
+        <v>20</v>
+      </c>
+      <c r="P455" t="s">
+        <v>513</v>
+      </c>
+      <c r="Q455" t="s">
+        <v>800</v>
+      </c>
+      <c r="R455" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="456" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>206</v>
+      </c>
+      <c r="B456" t="s">
+        <v>207</v>
+      </c>
+      <c r="C456" t="s">
+        <v>212</v>
+      </c>
+      <c r="D456" t="s">
+        <v>213</v>
+      </c>
+      <c r="E456" t="s">
+        <v>214</v>
+      </c>
+      <c r="F456" t="s">
+        <v>70</v>
+      </c>
+      <c r="G456" t="s">
+        <v>707</v>
+      </c>
+      <c r="H456" t="s">
+        <v>687</v>
+      </c>
+      <c r="I456" t="s">
+        <v>688</v>
+      </c>
+      <c r="J456">
+        <v>30.53</v>
+      </c>
+      <c r="K456" t="s">
+        <v>23</v>
+      </c>
+      <c r="L456" t="s">
+        <v>708</v>
+      </c>
+      <c r="M456" t="s">
+        <v>18</v>
+      </c>
+      <c r="N456" t="s">
+        <v>534</v>
+      </c>
+      <c r="O456" t="s">
+        <v>20</v>
+      </c>
+      <c r="P456" t="s">
+        <v>689</v>
+      </c>
+      <c r="Q456" t="s">
+        <v>801</v>
+      </c>
+      <c r="R456" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="457" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>206</v>
+      </c>
+      <c r="B457" t="s">
+        <v>207</v>
+      </c>
+      <c r="C457" t="s">
+        <v>215</v>
+      </c>
+      <c r="D457" t="s">
+        <v>216</v>
+      </c>
+      <c r="E457" t="s">
+        <v>32</v>
+      </c>
+      <c r="F457" t="s">
+        <v>33</v>
+      </c>
+      <c r="G457" t="s">
+        <v>715</v>
+      </c>
+      <c r="H457" t="s">
+        <v>195</v>
+      </c>
+      <c r="I457" t="s">
+        <v>196</v>
+      </c>
+      <c r="J457">
+        <v>26.93</v>
+      </c>
+      <c r="K457" t="s">
+        <v>23</v>
+      </c>
+      <c r="L457" t="s">
+        <v>708</v>
+      </c>
+      <c r="M457" t="s">
+        <v>18</v>
+      </c>
+      <c r="N457" t="s">
+        <v>534</v>
+      </c>
+      <c r="O457" t="s">
+        <v>20</v>
+      </c>
+      <c r="P457" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q457" t="s">
+        <v>699</v>
+      </c>
+      <c r="R457" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="458" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>206</v>
+      </c>
+      <c r="B458" t="s">
+        <v>207</v>
+      </c>
+      <c r="C458" t="s">
+        <v>215</v>
+      </c>
+      <c r="D458" t="s">
+        <v>216</v>
+      </c>
+      <c r="E458" t="s">
+        <v>32</v>
+      </c>
+      <c r="F458" t="s">
+        <v>33</v>
+      </c>
+      <c r="G458" t="s">
+        <v>715</v>
+      </c>
+      <c r="H458" t="s">
+        <v>82</v>
+      </c>
+      <c r="I458" t="s">
+        <v>83</v>
+      </c>
+      <c r="J458">
+        <v>22.12</v>
+      </c>
+      <c r="K458" t="s">
+        <v>23</v>
+      </c>
+      <c r="L458" t="s">
+        <v>708</v>
+      </c>
+      <c r="M458" t="s">
+        <v>18</v>
+      </c>
+      <c r="N458" t="s">
+        <v>534</v>
+      </c>
+      <c r="O458" t="s">
+        <v>20</v>
+      </c>
+      <c r="P458" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q458" t="s">
+        <v>802</v>
+      </c>
+      <c r="R458" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="459" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>206</v>
+      </c>
+      <c r="B459" t="s">
+        <v>207</v>
+      </c>
+      <c r="C459" t="s">
+        <v>251</v>
+      </c>
+      <c r="D459" t="s">
+        <v>252</v>
+      </c>
+      <c r="E459" t="s">
+        <v>198</v>
+      </c>
+      <c r="F459" t="s">
+        <v>119</v>
+      </c>
+      <c r="G459" t="s">
+        <v>796</v>
+      </c>
+      <c r="H459" t="s">
+        <v>82</v>
+      </c>
+      <c r="I459" t="s">
+        <v>83</v>
+      </c>
+      <c r="J459">
+        <v>22.12</v>
+      </c>
+      <c r="K459" t="s">
+        <v>23</v>
+      </c>
+      <c r="L459" t="s">
+        <v>708</v>
+      </c>
+      <c r="M459" t="s">
+        <v>18</v>
+      </c>
+      <c r="N459" t="s">
+        <v>534</v>
+      </c>
+      <c r="O459" t="s">
+        <v>20</v>
+      </c>
+      <c r="P459" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q459" t="s">
+        <v>802</v>
+      </c>
+      <c r="R459" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="460" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>206</v>
+      </c>
+      <c r="B460" t="s">
+        <v>207</v>
+      </c>
+      <c r="C460" t="s">
+        <v>212</v>
+      </c>
+      <c r="D460" t="s">
+        <v>213</v>
+      </c>
+      <c r="E460" t="s">
+        <v>214</v>
+      </c>
+      <c r="F460" t="s">
+        <v>70</v>
+      </c>
+      <c r="G460" t="s">
+        <v>707</v>
+      </c>
+      <c r="H460" t="s">
+        <v>82</v>
+      </c>
+      <c r="I460" t="s">
+        <v>83</v>
+      </c>
+      <c r="J460">
+        <v>22.12</v>
+      </c>
+      <c r="K460" t="s">
+        <v>23</v>
+      </c>
+      <c r="L460" t="s">
+        <v>708</v>
+      </c>
+      <c r="M460" t="s">
+        <v>18</v>
+      </c>
+      <c r="N460" t="s">
+        <v>534</v>
+      </c>
+      <c r="O460" t="s">
+        <v>20</v>
+      </c>
+      <c r="P460" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q460" t="s">
+        <v>802</v>
+      </c>
+      <c r="R460" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="461" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>206</v>
+      </c>
+      <c r="B461" t="s">
+        <v>207</v>
+      </c>
+      <c r="C461" t="s">
+        <v>215</v>
+      </c>
+      <c r="D461" t="s">
+        <v>216</v>
+      </c>
+      <c r="E461" t="s">
+        <v>32</v>
+      </c>
+      <c r="F461" t="s">
+        <v>33</v>
+      </c>
+      <c r="G461" t="s">
+        <v>715</v>
+      </c>
+      <c r="H461" t="s">
+        <v>28</v>
+      </c>
+      <c r="I461" t="s">
+        <v>29</v>
+      </c>
+      <c r="J461">
+        <v>22.15</v>
+      </c>
+      <c r="K461" t="s">
+        <v>23</v>
+      </c>
+      <c r="L461" t="s">
+        <v>708</v>
+      </c>
+      <c r="M461" t="s">
+        <v>18</v>
+      </c>
+      <c r="N461" t="s">
+        <v>534</v>
+      </c>
+      <c r="O461" t="s">
+        <v>20</v>
+      </c>
+      <c r="P461" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q461" t="s">
+        <v>803</v>
+      </c>
+      <c r="R461" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="462" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>206</v>
+      </c>
+      <c r="B462" t="s">
+        <v>207</v>
+      </c>
+      <c r="C462" t="s">
+        <v>212</v>
+      </c>
+      <c r="D462" t="s">
+        <v>213</v>
+      </c>
+      <c r="E462" t="s">
+        <v>214</v>
+      </c>
+      <c r="F462" t="s">
+        <v>70</v>
+      </c>
+      <c r="G462" t="s">
+        <v>707</v>
+      </c>
+      <c r="H462" t="s">
+        <v>28</v>
+      </c>
+      <c r="I462" t="s">
+        <v>29</v>
+      </c>
+      <c r="J462">
+        <v>22.15</v>
+      </c>
+      <c r="K462" t="s">
+        <v>23</v>
+      </c>
+      <c r="L462" t="s">
+        <v>708</v>
+      </c>
+      <c r="M462" t="s">
+        <v>18</v>
+      </c>
+      <c r="N462" t="s">
+        <v>534</v>
+      </c>
+      <c r="O462" t="s">
+        <v>20</v>
+      </c>
+      <c r="P462" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q462" t="s">
+        <v>803</v>
+      </c>
+      <c r="R462" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="463" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>206</v>
+      </c>
+      <c r="B463" t="s">
+        <v>207</v>
+      </c>
+      <c r="C463" t="s">
+        <v>212</v>
+      </c>
+      <c r="D463" t="s">
+        <v>213</v>
+      </c>
+      <c r="E463" t="s">
+        <v>214</v>
+      </c>
+      <c r="F463" t="s">
+        <v>70</v>
+      </c>
+      <c r="G463" t="s">
+        <v>707</v>
+      </c>
+      <c r="H463" t="s">
+        <v>64</v>
+      </c>
+      <c r="I463" t="s">
+        <v>65</v>
+      </c>
+      <c r="J463">
+        <v>22.16</v>
+      </c>
+      <c r="K463" t="s">
+        <v>23</v>
+      </c>
+      <c r="L463" t="s">
+        <v>708</v>
+      </c>
+      <c r="M463" t="s">
+        <v>18</v>
+      </c>
+      <c r="N463" t="s">
+        <v>534</v>
+      </c>
+      <c r="O463" t="s">
+        <v>20</v>
+      </c>
+      <c r="P463" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q463" t="s">
+        <v>804</v>
+      </c>
+      <c r="R463" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="464" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>206</v>
+      </c>
+      <c r="B464" t="s">
+        <v>207</v>
+      </c>
+      <c r="C464" t="s">
+        <v>208</v>
+      </c>
+      <c r="D464" t="s">
+        <v>209</v>
+      </c>
+      <c r="E464" t="s">
+        <v>210</v>
+      </c>
+      <c r="F464" t="s">
+        <v>118</v>
+      </c>
+      <c r="G464" t="s">
+        <v>710</v>
+      </c>
+      <c r="H464" t="s">
+        <v>805</v>
+      </c>
+      <c r="I464" t="s">
+        <v>806</v>
+      </c>
+      <c r="J464">
+        <v>22.87</v>
+      </c>
+      <c r="K464" t="s">
+        <v>23</v>
+      </c>
+      <c r="L464" t="s">
+        <v>708</v>
+      </c>
+      <c r="M464" t="s">
+        <v>18</v>
+      </c>
+      <c r="N464" t="s">
+        <v>534</v>
+      </c>
+      <c r="O464" t="s">
+        <v>20</v>
+      </c>
+      <c r="P464" t="s">
+        <v>807</v>
+      </c>
+      <c r="Q464" t="s">
+        <v>808</v>
+      </c>
+      <c r="R464" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="465" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>206</v>
+      </c>
+      <c r="B465" t="s">
+        <v>207</v>
+      </c>
+      <c r="C465" t="s">
+        <v>251</v>
+      </c>
+      <c r="D465" t="s">
+        <v>252</v>
+      </c>
+      <c r="E465" t="s">
+        <v>198</v>
+      </c>
+      <c r="F465" t="s">
+        <v>119</v>
+      </c>
+      <c r="G465" t="s">
+        <v>732</v>
+      </c>
+      <c r="H465" t="s">
+        <v>809</v>
+      </c>
+      <c r="I465" t="s">
+        <v>810</v>
+      </c>
+      <c r="J465">
+        <v>57.14</v>
+      </c>
+      <c r="K465" t="s">
+        <v>22</v>
+      </c>
+      <c r="L465" t="s">
+        <v>708</v>
+      </c>
+      <c r="M465" t="s">
+        <v>18</v>
+      </c>
+      <c r="N465" t="s">
+        <v>534</v>
+      </c>
+      <c r="O465" t="s">
+        <v>20</v>
+      </c>
+      <c r="P465" t="s">
+        <v>811</v>
+      </c>
+      <c r="Q465" t="s">
+        <v>812</v>
+      </c>
+      <c r="R465" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="466" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>206</v>
+      </c>
+      <c r="B466" t="s">
+        <v>207</v>
+      </c>
+      <c r="C466" t="s">
+        <v>212</v>
+      </c>
+      <c r="D466" t="s">
+        <v>213</v>
+      </c>
+      <c r="E466" t="s">
+        <v>214</v>
+      </c>
+      <c r="F466" t="s">
+        <v>70</v>
+      </c>
+      <c r="G466" t="s">
+        <v>710</v>
+      </c>
+      <c r="H466" t="s">
+        <v>813</v>
+      </c>
+      <c r="I466" t="s">
+        <v>814</v>
+      </c>
+      <c r="J466">
+        <v>33.19</v>
+      </c>
+      <c r="K466" t="s">
+        <v>23</v>
+      </c>
+      <c r="L466" t="s">
+        <v>708</v>
+      </c>
+      <c r="M466" t="s">
+        <v>18</v>
+      </c>
+      <c r="N466" t="s">
+        <v>534</v>
+      </c>
+      <c r="O466" t="s">
+        <v>20</v>
+      </c>
+      <c r="P466" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q466" t="s">
+        <v>816</v>
+      </c>
+      <c r="R466" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="467" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>206</v>
+      </c>
+      <c r="B467" t="s">
+        <v>207</v>
+      </c>
+      <c r="C467" t="s">
+        <v>215</v>
+      </c>
+      <c r="D467" t="s">
+        <v>216</v>
+      </c>
+      <c r="E467" t="s">
+        <v>32</v>
+      </c>
+      <c r="F467" t="s">
+        <v>33</v>
+      </c>
+      <c r="G467" t="s">
+        <v>732</v>
+      </c>
+      <c r="H467" t="s">
+        <v>817</v>
+      </c>
+      <c r="I467" t="s">
+        <v>818</v>
+      </c>
+      <c r="J467">
+        <v>5.72</v>
+      </c>
+      <c r="K467" t="s">
+        <v>23</v>
+      </c>
+      <c r="L467" t="s">
+        <v>708</v>
+      </c>
+      <c r="M467" t="s">
+        <v>18</v>
+      </c>
+      <c r="N467" t="s">
+        <v>534</v>
+      </c>
+      <c r="O467" t="s">
+        <v>20</v>
+      </c>
+      <c r="P467" t="s">
+        <v>819</v>
+      </c>
+      <c r="Q467" t="s">
+        <v>820</v>
+      </c>
+      <c r="R467" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="468" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>206</v>
+      </c>
+      <c r="B468" t="s">
+        <v>207</v>
+      </c>
+      <c r="C468" t="s">
+        <v>215</v>
+      </c>
+      <c r="D468" t="s">
+        <v>216</v>
+      </c>
+      <c r="E468" t="s">
+        <v>32</v>
+      </c>
+      <c r="F468" t="s">
+        <v>33</v>
+      </c>
+      <c r="G468" t="s">
+        <v>715</v>
+      </c>
+      <c r="H468" t="s">
+        <v>633</v>
+      </c>
+      <c r="I468" t="s">
+        <v>634</v>
+      </c>
+      <c r="J468">
+        <v>13.72</v>
+      </c>
+      <c r="K468" t="s">
+        <v>23</v>
+      </c>
+      <c r="L468" t="s">
+        <v>708</v>
+      </c>
+      <c r="M468" t="s">
+        <v>18</v>
+      </c>
+      <c r="N468" t="s">
+        <v>534</v>
+      </c>
+      <c r="O468" t="s">
+        <v>20</v>
+      </c>
+      <c r="P468" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q468" t="s">
+        <v>637</v>
+      </c>
+      <c r="R468" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="469" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>206</v>
+      </c>
+      <c r="B469" t="s">
+        <v>207</v>
+      </c>
+      <c r="C469" t="s">
+        <v>212</v>
+      </c>
+      <c r="D469" t="s">
+        <v>213</v>
+      </c>
+      <c r="E469" t="s">
+        <v>214</v>
+      </c>
+      <c r="F469" t="s">
+        <v>70</v>
+      </c>
+      <c r="G469" t="s">
+        <v>707</v>
+      </c>
+      <c r="H469" t="s">
+        <v>171</v>
+      </c>
+      <c r="I469" t="s">
+        <v>172</v>
+      </c>
+      <c r="J469">
+        <v>39.21</v>
+      </c>
+      <c r="K469" t="s">
+        <v>50</v>
+      </c>
+      <c r="L469" t="s">
+        <v>708</v>
+      </c>
+      <c r="M469" t="s">
+        <v>18</v>
+      </c>
+      <c r="N469" t="s">
+        <v>534</v>
+      </c>
+      <c r="O469" t="s">
+        <v>20</v>
+      </c>
+      <c r="P469" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q469" t="s">
+        <v>821</v>
+      </c>
+      <c r="R469" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="470" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>206</v>
+      </c>
+      <c r="B470" t="s">
+        <v>207</v>
+      </c>
+      <c r="C470" t="s">
+        <v>215</v>
+      </c>
+      <c r="D470" t="s">
+        <v>216</v>
+      </c>
+      <c r="E470" t="s">
+        <v>32</v>
+      </c>
+      <c r="F470" t="s">
+        <v>33</v>
+      </c>
+      <c r="G470" t="s">
+        <v>715</v>
+      </c>
+      <c r="H470" t="s">
+        <v>46</v>
+      </c>
+      <c r="I470" t="s">
+        <v>47</v>
+      </c>
+      <c r="J470">
+        <v>33.24</v>
+      </c>
+      <c r="K470" t="s">
+        <v>23</v>
+      </c>
+      <c r="L470" t="s">
+        <v>708</v>
+      </c>
+      <c r="M470" t="s">
+        <v>18</v>
+      </c>
+      <c r="N470" t="s">
+        <v>534</v>
+      </c>
+      <c r="O470" t="s">
+        <v>20</v>
+      </c>
+      <c r="P470" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q470" t="s">
+        <v>822</v>
+      </c>
+      <c r="R470" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="471" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>206</v>
+      </c>
+      <c r="B471" t="s">
+        <v>207</v>
+      </c>
+      <c r="C471" t="s">
+        <v>208</v>
+      </c>
+      <c r="D471" t="s">
+        <v>209</v>
+      </c>
+      <c r="E471" t="s">
+        <v>210</v>
+      </c>
+      <c r="F471" t="s">
+        <v>118</v>
+      </c>
+      <c r="G471" t="s">
+        <v>735</v>
+      </c>
+      <c r="H471" t="s">
+        <v>46</v>
+      </c>
+      <c r="I471" t="s">
+        <v>47</v>
+      </c>
+      <c r="J471">
+        <v>-33.24</v>
+      </c>
+      <c r="K471" t="s">
+        <v>581</v>
+      </c>
+      <c r="L471" t="s">
+        <v>708</v>
+      </c>
+      <c r="M471" t="s">
+        <v>18</v>
+      </c>
+      <c r="N471" t="s">
+        <v>534</v>
+      </c>
+      <c r="O471" t="s">
+        <v>20</v>
+      </c>
+      <c r="P471" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q471" t="s">
+        <v>822</v>
+      </c>
+      <c r="R471" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="472" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>206</v>
+      </c>
+      <c r="B472" t="s">
+        <v>207</v>
+      </c>
+      <c r="C472" t="s">
+        <v>208</v>
+      </c>
+      <c r="D472" t="s">
+        <v>209</v>
+      </c>
+      <c r="E472" t="s">
+        <v>210</v>
+      </c>
+      <c r="F472" t="s">
+        <v>118</v>
+      </c>
+      <c r="G472" t="s">
+        <v>732</v>
+      </c>
+      <c r="H472" t="s">
+        <v>823</v>
+      </c>
+      <c r="I472" t="s">
+        <v>824</v>
+      </c>
+      <c r="J472">
+        <v>180.61</v>
+      </c>
+      <c r="K472" t="s">
+        <v>23</v>
+      </c>
+      <c r="L472" t="s">
+        <v>708</v>
+      </c>
+      <c r="M472" t="s">
+        <v>18</v>
+      </c>
+      <c r="N472" t="s">
+        <v>534</v>
+      </c>
+      <c r="O472" t="s">
+        <v>20</v>
+      </c>
+      <c r="P472" t="s">
+        <v>825</v>
+      </c>
+      <c r="Q472" t="s">
+        <v>826</v>
+      </c>
+      <c r="R472" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="473" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>206</v>
+      </c>
+      <c r="B473" t="s">
+        <v>207</v>
+      </c>
+      <c r="C473" t="s">
+        <v>215</v>
+      </c>
+      <c r="D473" t="s">
+        <v>216</v>
+      </c>
+      <c r="E473" t="s">
+        <v>32</v>
+      </c>
+      <c r="F473" t="s">
+        <v>33</v>
+      </c>
+      <c r="G473" t="s">
+        <v>732</v>
+      </c>
+      <c r="H473" t="s">
+        <v>34</v>
+      </c>
+      <c r="I473" t="s">
+        <v>35</v>
+      </c>
+      <c r="J473">
+        <v>34.020000000000003</v>
+      </c>
+      <c r="K473" t="s">
+        <v>50</v>
+      </c>
+      <c r="L473" t="s">
+        <v>708</v>
+      </c>
+      <c r="M473" t="s">
+        <v>18</v>
+      </c>
+      <c r="N473" t="s">
+        <v>534</v>
+      </c>
+      <c r="O473" t="s">
+        <v>20</v>
+      </c>
+      <c r="P473" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q473" t="s">
+        <v>827</v>
+      </c>
+      <c r="R473" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="474" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>206</v>
+      </c>
+      <c r="B474" t="s">
+        <v>207</v>
+      </c>
+      <c r="C474" t="s">
+        <v>212</v>
+      </c>
+      <c r="D474" t="s">
+        <v>213</v>
+      </c>
+      <c r="E474" t="s">
+        <v>214</v>
+      </c>
+      <c r="F474" t="s">
+        <v>70</v>
+      </c>
+      <c r="G474" t="s">
+        <v>828</v>
+      </c>
+      <c r="H474" t="s">
+        <v>389</v>
+      </c>
+      <c r="I474" t="s">
+        <v>390</v>
+      </c>
+      <c r="J474">
+        <v>21.3</v>
+      </c>
+      <c r="K474" t="s">
+        <v>22</v>
+      </c>
+      <c r="L474" t="s">
+        <v>708</v>
+      </c>
+      <c r="M474" t="s">
+        <v>18</v>
+      </c>
+      <c r="N474" t="s">
+        <v>534</v>
+      </c>
+      <c r="O474" t="s">
+        <v>20</v>
+      </c>
+      <c r="P474" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q474" t="s">
+        <v>391</v>
+      </c>
+      <c r="R474" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="475" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>206</v>
+      </c>
+      <c r="B475" t="s">
+        <v>207</v>
+      </c>
+      <c r="C475" t="s">
+        <v>221</v>
+      </c>
+      <c r="D475" t="s">
+        <v>222</v>
+      </c>
+      <c r="E475" t="s">
+        <v>223</v>
+      </c>
+      <c r="F475" t="s">
+        <v>151</v>
+      </c>
+      <c r="G475" t="s">
+        <v>829</v>
+      </c>
+      <c r="H475" t="s">
+        <v>95</v>
+      </c>
+      <c r="I475" t="s">
+        <v>96</v>
+      </c>
+      <c r="J475">
+        <v>31.95</v>
+      </c>
+      <c r="K475" t="s">
+        <v>50</v>
+      </c>
+      <c r="L475" t="s">
+        <v>708</v>
+      </c>
+      <c r="M475" t="s">
+        <v>18</v>
+      </c>
+      <c r="N475" t="s">
+        <v>534</v>
+      </c>
+      <c r="O475" t="s">
+        <v>20</v>
+      </c>
+      <c r="P475" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q475" t="s">
+        <v>391</v>
+      </c>
+      <c r="R475" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="476" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>206</v>
+      </c>
+      <c r="B476" t="s">
+        <v>207</v>
+      </c>
+      <c r="C476" t="s">
+        <v>221</v>
+      </c>
+      <c r="D476" t="s">
+        <v>222</v>
+      </c>
+      <c r="E476" t="s">
+        <v>223</v>
+      </c>
+      <c r="F476" t="s">
+        <v>151</v>
+      </c>
+      <c r="G476" t="s">
+        <v>754</v>
+      </c>
+      <c r="H476" t="s">
+        <v>95</v>
+      </c>
+      <c r="I476" t="s">
+        <v>96</v>
+      </c>
+      <c r="J476">
+        <v>31.95</v>
+      </c>
+      <c r="K476" t="s">
+        <v>50</v>
+      </c>
+      <c r="L476" t="s">
+        <v>708</v>
+      </c>
+      <c r="M476" t="s">
+        <v>18</v>
+      </c>
+      <c r="N476" t="s">
+        <v>534</v>
+      </c>
+      <c r="O476" t="s">
+        <v>20</v>
+      </c>
+      <c r="P476" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q476" t="s">
+        <v>391</v>
+      </c>
+      <c r="R476" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="477" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>206</v>
+      </c>
+      <c r="B477" t="s">
+        <v>207</v>
+      </c>
+      <c r="C477" t="s">
+        <v>221</v>
+      </c>
+      <c r="D477" t="s">
+        <v>222</v>
+      </c>
+      <c r="E477" t="s">
+        <v>223</v>
+      </c>
+      <c r="F477" t="s">
+        <v>151</v>
+      </c>
+      <c r="G477" t="s">
+        <v>722</v>
+      </c>
+      <c r="H477" t="s">
+        <v>95</v>
+      </c>
+      <c r="I477" t="s">
+        <v>96</v>
+      </c>
+      <c r="J477">
+        <v>53.25</v>
+      </c>
+      <c r="K477" t="s">
+        <v>329</v>
+      </c>
+      <c r="L477" t="s">
+        <v>708</v>
+      </c>
+      <c r="M477" t="s">
+        <v>18</v>
+      </c>
+      <c r="N477" t="s">
+        <v>534</v>
+      </c>
+      <c r="O477" t="s">
+        <v>20</v>
+      </c>
+      <c r="P477" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q477" t="s">
+        <v>391</v>
+      </c>
+      <c r="R477" t="s">
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -24236,12 +30376,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24383,15 +30520,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24415,10 +30556,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572CA61F-FEEA-42AE-BDCD-4177C47A2D3E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFCE63C2-9EDB-4C06-BCC1-92BC6FE21478}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>